--- a/Data_Files/Laps_Completed.xlsx
+++ b/Data_Files/Laps_Completed.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9E077E-5D79-4489-BF5C-7117727A2EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{474E3EBB-62DD-494D-9BBE-EB5328806C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="1500" windowWidth="16410" windowHeight="14145" firstSheet="2" activeTab="8" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28695" yWindow="1500" windowWidth="16410" windowHeight="14145" firstSheet="1" activeTab="8" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Laps_Completed" sheetId="1" r:id="rId1"/>
@@ -13202,8 +13202,10 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -13268,7 +13270,7 @@
       </c>
       <c r="B2">
         <f>SUM(C2:R2)</f>
-        <v>78</v>
+        <v>921</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -13277,7 +13279,46 @@
         <v>72</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>72</v>
+      </c>
+      <c r="F2">
+        <v>62</v>
+      </c>
+      <c r="G2">
+        <v>65</v>
+      </c>
+      <c r="H2">
+        <v>76</v>
+      </c>
+      <c r="I2">
+        <v>69</v>
+      </c>
+      <c r="J2">
+        <v>71</v>
+      </c>
+      <c r="K2">
+        <v>60</v>
+      </c>
+      <c r="L2">
+        <v>71</v>
+      </c>
+      <c r="M2">
+        <v>45</v>
+      </c>
+      <c r="N2">
+        <v>77</v>
+      </c>
+      <c r="O2">
+        <v>25</v>
+      </c>
+      <c r="P2">
+        <v>53</v>
+      </c>
+      <c r="Q2">
+        <v>67</v>
+      </c>
+      <c r="R2">
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -13286,7 +13327,7 @@
       </c>
       <c r="B3">
         <f t="shared" ref="B3:B14" si="0">SUM(C3:R3)</f>
-        <v>57</v>
+        <v>609</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -13295,7 +13336,46 @@
         <v>56</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>70</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>64</v>
+      </c>
+      <c r="H3">
+        <v>11</v>
+      </c>
+      <c r="I3">
+        <v>69</v>
+      </c>
+      <c r="J3">
+        <v>69</v>
+      </c>
+      <c r="K3">
+        <v>39</v>
+      </c>
+      <c r="L3">
+        <v>8</v>
+      </c>
+      <c r="M3">
+        <v>27</v>
+      </c>
+      <c r="N3">
+        <v>54</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>52</v>
+      </c>
+      <c r="Q3">
+        <v>65</v>
+      </c>
+      <c r="R3">
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -13304,7 +13384,7 @@
       </c>
       <c r="B4">
         <f t="shared" si="0"/>
-        <v>131</v>
+        <v>837</v>
       </c>
       <c r="C4">
         <v>58</v>
@@ -13313,7 +13393,46 @@
         <v>72</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>72</v>
+      </c>
+      <c r="F4">
+        <v>62</v>
+      </c>
+      <c r="G4">
+        <v>65</v>
+      </c>
+      <c r="H4">
+        <v>17</v>
+      </c>
+      <c r="I4">
+        <v>18</v>
+      </c>
+      <c r="J4">
+        <v>70</v>
+      </c>
+      <c r="K4">
+        <v>37</v>
+      </c>
+      <c r="L4">
+        <v>71</v>
+      </c>
+      <c r="M4">
+        <v>45</v>
+      </c>
+      <c r="N4">
+        <v>77</v>
+      </c>
+      <c r="O4">
+        <v>39</v>
+      </c>
+      <c r="P4">
+        <v>16</v>
+      </c>
+      <c r="Q4">
+        <v>67</v>
+      </c>
+      <c r="R4">
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -13322,7 +13441,7 @@
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>672</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -13331,7 +13450,46 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="F5">
+        <v>60</v>
+      </c>
+      <c r="G5">
+        <v>63</v>
+      </c>
+      <c r="H5">
+        <v>44</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>68</v>
+      </c>
+      <c r="K5">
+        <v>59</v>
+      </c>
+      <c r="L5">
+        <v>71</v>
+      </c>
+      <c r="M5">
+        <v>45</v>
+      </c>
+      <c r="N5">
+        <v>76</v>
+      </c>
+      <c r="O5">
+        <v>44</v>
+      </c>
+      <c r="P5">
+        <v>53</v>
+      </c>
+      <c r="Q5">
+        <v>53</v>
+      </c>
+      <c r="R5">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -13340,7 +13498,7 @@
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
-        <v>129</v>
+        <v>939</v>
       </c>
       <c r="C6">
         <v>57</v>
@@ -13349,7 +13507,46 @@
         <v>71</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>52</v>
+      </c>
+      <c r="F6">
+        <v>62</v>
+      </c>
+      <c r="G6">
+        <v>64</v>
+      </c>
+      <c r="H6">
+        <v>77</v>
+      </c>
+      <c r="I6">
+        <v>63</v>
+      </c>
+      <c r="J6">
+        <v>71</v>
+      </c>
+      <c r="K6">
+        <v>59</v>
+      </c>
+      <c r="L6">
+        <v>71</v>
+      </c>
+      <c r="M6">
+        <v>45</v>
+      </c>
+      <c r="N6">
+        <v>77</v>
+      </c>
+      <c r="O6">
+        <v>16</v>
+      </c>
+      <c r="P6">
+        <v>37</v>
+      </c>
+      <c r="Q6">
+        <v>66</v>
+      </c>
+      <c r="R6">
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -13358,7 +13555,7 @@
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
-        <v>121</v>
+        <v>746</v>
       </c>
       <c r="C7">
         <v>57</v>
@@ -13367,7 +13564,46 @@
         <v>63</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>65</v>
+      </c>
+      <c r="F7">
+        <v>56</v>
+      </c>
+      <c r="G7">
+        <v>60</v>
+      </c>
+      <c r="H7">
+        <v>49</v>
+      </c>
+      <c r="I7">
+        <v>39</v>
+      </c>
+      <c r="J7">
+        <v>69</v>
+      </c>
+      <c r="K7">
+        <v>40</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>44</v>
+      </c>
+      <c r="N7">
+        <v>74</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>15</v>
+      </c>
+      <c r="Q7">
+        <v>65</v>
+      </c>
+      <c r="R7">
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -13376,7 +13612,7 @@
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>646</v>
       </c>
       <c r="C8">
         <v>26</v>
@@ -13385,7 +13621,46 @@
         <v>17</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>70</v>
+      </c>
+      <c r="F8">
+        <v>34</v>
+      </c>
+      <c r="G8">
+        <v>63</v>
+      </c>
+      <c r="H8">
+        <v>56</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>55</v>
+      </c>
+      <c r="K8">
+        <v>37</v>
+      </c>
+      <c r="L8">
+        <v>70</v>
+      </c>
+      <c r="M8">
+        <v>44</v>
+      </c>
+      <c r="N8">
+        <v>28</v>
+      </c>
+      <c r="O8">
+        <v>42</v>
+      </c>
+      <c r="P8">
+        <v>50</v>
+      </c>
+      <c r="Q8">
+        <v>6</v>
+      </c>
+      <c r="R8">
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -13394,7 +13669,7 @@
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
-        <v>115</v>
+        <v>845</v>
       </c>
       <c r="C9">
         <v>43</v>
@@ -13403,7 +13678,46 @@
         <v>71</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>72</v>
+      </c>
+      <c r="F9">
+        <v>17</v>
+      </c>
+      <c r="G9">
+        <v>28</v>
+      </c>
+      <c r="H9">
+        <v>78</v>
+      </c>
+      <c r="I9">
+        <v>69</v>
+      </c>
+      <c r="J9">
+        <v>70</v>
+      </c>
+      <c r="K9">
+        <v>59</v>
+      </c>
+      <c r="L9">
+        <v>21</v>
+      </c>
+      <c r="M9">
+        <v>45</v>
+      </c>
+      <c r="N9">
+        <v>76</v>
+      </c>
+      <c r="O9">
+        <v>26</v>
+      </c>
+      <c r="P9">
+        <v>52</v>
+      </c>
+      <c r="Q9">
+        <v>67</v>
+      </c>
+      <c r="R9">
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -13412,7 +13726,7 @@
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
-        <v>129</v>
+        <v>893</v>
       </c>
       <c r="C10">
         <v>57</v>
@@ -13421,7 +13735,46 @@
         <v>71</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>72</v>
+      </c>
+      <c r="F10">
+        <v>62</v>
+      </c>
+      <c r="G10">
+        <v>28</v>
+      </c>
+      <c r="H10">
+        <v>78</v>
+      </c>
+      <c r="I10">
+        <v>69</v>
+      </c>
+      <c r="J10">
+        <v>71</v>
+      </c>
+      <c r="K10">
+        <v>60</v>
+      </c>
+      <c r="L10">
+        <v>71</v>
+      </c>
+      <c r="M10">
+        <v>45</v>
+      </c>
+      <c r="N10">
+        <v>13</v>
+      </c>
+      <c r="O10">
+        <v>25</v>
+      </c>
+      <c r="P10">
+        <v>53</v>
+      </c>
+      <c r="Q10">
+        <v>67</v>
+      </c>
+      <c r="R10">
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -13430,7 +13783,7 @@
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
-        <v>129</v>
+        <v>788</v>
       </c>
       <c r="C11">
         <v>57</v>
@@ -13439,7 +13792,46 @@
         <v>71</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>71</v>
+      </c>
+      <c r="F11">
+        <v>62</v>
+      </c>
+      <c r="G11">
+        <v>63</v>
+      </c>
+      <c r="H11">
+        <v>9</v>
+      </c>
+      <c r="I11">
+        <v>20</v>
+      </c>
+      <c r="J11">
+        <v>68</v>
+      </c>
+      <c r="K11">
+        <v>15</v>
+      </c>
+      <c r="L11">
+        <v>16</v>
+      </c>
+      <c r="M11">
+        <v>45</v>
+      </c>
+      <c r="N11">
+        <v>77</v>
+      </c>
+      <c r="O11">
+        <v>44</v>
+      </c>
+      <c r="P11">
+        <v>52</v>
+      </c>
+      <c r="Q11">
+        <v>67</v>
+      </c>
+      <c r="R11">
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -13448,7 +13840,7 @@
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>506</v>
       </c>
       <c r="C12">
         <v>23</v>
@@ -13457,7 +13849,46 @@
         <v>18</v>
       </c>
       <c r="E12">
+        <v>18</v>
+      </c>
+      <c r="F12">
+        <v>60</v>
+      </c>
+      <c r="G12">
+        <v>21</v>
+      </c>
+      <c r="H12">
+        <v>78</v>
+      </c>
+      <c r="I12">
+        <v>18</v>
+      </c>
+      <c r="J12">
+        <v>69</v>
+      </c>
+      <c r="K12">
+        <v>27</v>
+      </c>
+      <c r="L12">
         <v>1</v>
+      </c>
+      <c r="M12">
+        <v>44</v>
+      </c>
+      <c r="N12">
+        <v>18</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>32</v>
+      </c>
+      <c r="Q12">
+        <v>65</v>
+      </c>
+      <c r="R12">
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -13466,7 +13897,7 @@
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -13476,6 +13907,45 @@
       </c>
       <c r="E13">
         <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>69</v>
+      </c>
+      <c r="K13">
+        <v>38</v>
+      </c>
+      <c r="L13">
+        <v>51</v>
+      </c>
+      <c r="M13">
+        <v>24</v>
+      </c>
+      <c r="N13">
+        <v>74</v>
+      </c>
+      <c r="O13">
+        <v>8</v>
+      </c>
+      <c r="P13">
+        <v>39</v>
+      </c>
+      <c r="Q13">
+        <v>65</v>
+      </c>
+      <c r="R13">
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -13484,7 +13954,7 @@
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
-        <v>130</v>
+        <v>848</v>
       </c>
       <c r="C14">
         <v>57</v>
@@ -13493,7 +13963,46 @@
         <v>72</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>72</v>
+      </c>
+      <c r="F14">
+        <v>17</v>
+      </c>
+      <c r="G14">
+        <v>65</v>
+      </c>
+      <c r="H14">
+        <v>42</v>
+      </c>
+      <c r="I14">
+        <v>69</v>
+      </c>
+      <c r="J14">
+        <v>70</v>
+      </c>
+      <c r="K14">
+        <v>59</v>
+      </c>
+      <c r="L14">
+        <v>70</v>
+      </c>
+      <c r="M14">
+        <v>45</v>
+      </c>
+      <c r="N14">
+        <v>69</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>24</v>
+      </c>
+      <c r="Q14">
+        <v>67</v>
+      </c>
+      <c r="R14">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Files/Laps_Completed.xlsx
+++ b/Data_Files/Laps_Completed.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{474E3EBB-62DD-494D-9BBE-EB5328806C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="1500" windowWidth="16410" windowHeight="14145" firstSheet="1" activeTab="8" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28695" yWindow="-12540" windowWidth="16410" windowHeight="14145" firstSheet="1" activeTab="8" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Laps_Completed" sheetId="1" r:id="rId1"/>

--- a/Data_Files/Laps_Completed.xlsx
+++ b/Data_Files/Laps_Completed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{474E3EBB-62DD-494D-9BBE-EB5328806C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C606660C-5ACD-4D06-A671-9DFC3C4F0915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-12540" windowWidth="16410" windowHeight="14145" firstSheet="1" activeTab="8" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Laps_Completed" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="153">
   <si>
     <t>Driver</t>
   </si>
@@ -1725,6 +1725,12 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="AD2">
+        <v>543</v>
+      </c>
+      <c r="AE2">
+        <v>921</v>
+      </c>
       <c r="AF2">
         <v>874</v>
       </c>
@@ -1751,6 +1757,12 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
+      <c r="AD3">
+        <v>850</v>
+      </c>
+      <c r="AE3">
+        <v>609</v>
+      </c>
       <c r="AF3">
         <v>591</v>
       </c>
@@ -1778,9 +1790,15 @@
         <v>3</v>
       </c>
       <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-      <c r="AF4" s="1"/>
+      <c r="AD4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="1">
+        <v>0</v>
+      </c>
       <c r="AG4" s="1">
         <v>0</v>
       </c>
@@ -1804,6 +1822,12 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
+      <c r="AD5">
+        <v>716</v>
+      </c>
+      <c r="AE5">
+        <v>837</v>
+      </c>
       <c r="AF5">
         <v>788</v>
       </c>
@@ -1831,8 +1855,12 @@
         <v>5</v>
       </c>
       <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
+      <c r="AD6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>0</v>
+      </c>
       <c r="AF6" s="1">
         <v>0</v>
       </c>
@@ -1859,6 +1887,12 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
+      <c r="AD7">
+        <v>828</v>
+      </c>
+      <c r="AE7">
+        <v>672</v>
+      </c>
       <c r="AF7">
         <v>697</v>
       </c>
@@ -1887,8 +1921,12 @@
       </c>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
-      <c r="AD8" s="1"/>
-      <c r="AE8" s="1"/>
+      <c r="AD8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>0</v>
+      </c>
       <c r="AF8" s="1">
         <v>0</v>
       </c>
@@ -1915,8 +1953,12 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="AD9" s="1"/>
-      <c r="AE9" s="1"/>
+      <c r="AD9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0</v>
+      </c>
       <c r="AF9" s="1">
         <v>0</v>
       </c>
@@ -1943,6 +1985,12 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
+      <c r="AD10">
+        <v>573</v>
+      </c>
+      <c r="AE10">
+        <v>939</v>
+      </c>
       <c r="AF10">
         <v>810</v>
       </c>
@@ -1969,6 +2017,12 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
+      <c r="AD11">
+        <v>782</v>
+      </c>
+      <c r="AE11">
+        <v>746</v>
+      </c>
       <c r="AF11">
         <v>558</v>
       </c>
@@ -1995,8 +2049,12 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
+      <c r="AD12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>0</v>
+      </c>
       <c r="AF12" s="1">
         <v>0</v>
       </c>
@@ -2023,6 +2081,12 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
+      <c r="AD13">
+        <v>617</v>
+      </c>
+      <c r="AE13">
+        <v>646</v>
+      </c>
       <c r="AF13">
         <v>701</v>
       </c>
@@ -2051,8 +2115,12 @@
       </c>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
-      <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
+      <c r="AD14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>0</v>
+      </c>
       <c r="AF14" s="1">
         <v>0</v>
       </c>
@@ -2079,6 +2147,12 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
+      <c r="AD15">
+        <v>787</v>
+      </c>
+      <c r="AE15">
+        <v>845</v>
+      </c>
       <c r="AF15">
         <v>851</v>
       </c>
@@ -2105,7 +2179,12 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="AE16" s="1"/>
+      <c r="AD16">
+        <v>653</v>
+      </c>
+      <c r="AE16" s="1">
+        <v>0</v>
+      </c>
       <c r="AF16" s="1">
         <v>0</v>
       </c>
@@ -2132,6 +2211,12 @@
       <c r="A17" t="s">
         <v>16</v>
       </c>
+      <c r="AD17">
+        <v>983</v>
+      </c>
+      <c r="AE17">
+        <v>893</v>
+      </c>
       <c r="AF17">
         <v>800</v>
       </c>
@@ -2160,8 +2245,12 @@
       </c>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
-      <c r="AD18" s="1"/>
-      <c r="AE18" s="1"/>
+      <c r="AD18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="1">
+        <v>0</v>
+      </c>
       <c r="AF18" s="1">
         <v>0</v>
       </c>
@@ -2190,8 +2279,12 @@
       </c>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
-      <c r="AD19" s="1"/>
-      <c r="AE19" s="1"/>
+      <c r="AD19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="1">
+        <v>0</v>
+      </c>
       <c r="AF19" s="1">
         <v>0</v>
       </c>
@@ -2219,8 +2312,12 @@
         <v>18</v>
       </c>
       <c r="AC20" s="1"/>
-      <c r="AD20" s="1"/>
-      <c r="AE20" s="1"/>
+      <c r="AD20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="1">
+        <v>0</v>
+      </c>
       <c r="AF20" s="1">
         <v>0</v>
       </c>
@@ -2248,8 +2345,12 @@
         <v>19</v>
       </c>
       <c r="AC21" s="1"/>
-      <c r="AD21" s="1"/>
-      <c r="AE21" s="1"/>
+      <c r="AD21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="1">
+        <v>0</v>
+      </c>
       <c r="AF21" s="1">
         <v>0</v>
       </c>
@@ -2276,6 +2377,12 @@
       <c r="A22" t="s">
         <v>55</v>
       </c>
+      <c r="AD22">
+        <v>915</v>
+      </c>
+      <c r="AE22">
+        <v>788</v>
+      </c>
       <c r="AF22">
         <v>810</v>
       </c>
@@ -2302,6 +2409,12 @@
       <c r="A23" t="s">
         <v>21</v>
       </c>
+      <c r="AD23">
+        <v>490</v>
+      </c>
+      <c r="AE23">
+        <v>506</v>
+      </c>
       <c r="AF23">
         <v>903</v>
       </c>
@@ -2330,8 +2443,12 @@
       </c>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
-      <c r="AD24" s="1"/>
-      <c r="AE24" s="1"/>
+      <c r="AD24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="1">
+        <v>0</v>
+      </c>
       <c r="AF24" s="1">
         <v>0</v>
       </c>
@@ -2359,8 +2476,12 @@
         <v>44</v>
       </c>
       <c r="AC25" s="1"/>
-      <c r="AD25" s="1"/>
-      <c r="AE25" s="1"/>
+      <c r="AD25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="1">
+        <v>0</v>
+      </c>
       <c r="AF25" s="1">
         <v>0</v>
       </c>
@@ -2390,8 +2511,12 @@
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
-      <c r="AD26" s="1"/>
-      <c r="AE26" s="1"/>
+      <c r="AD26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="1">
+        <v>0</v>
+      </c>
       <c r="AF26" s="1">
         <v>0</v>
       </c>
@@ -2421,8 +2546,12 @@
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
-      <c r="AD27" s="1"/>
-      <c r="AE27" s="1"/>
+      <c r="AD27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="1">
+        <v>0</v>
+      </c>
       <c r="AF27" s="1">
         <v>0</v>
       </c>
@@ -2449,6 +2578,12 @@
       <c r="A28" t="s">
         <v>47</v>
       </c>
+      <c r="AD28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>389</v>
+      </c>
       <c r="AF28">
         <v>781</v>
       </c>
@@ -2478,8 +2613,12 @@
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
-      <c r="AD29" s="1"/>
-      <c r="AE29" s="1"/>
+      <c r="AD29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="1">
+        <v>0</v>
+      </c>
       <c r="AF29" s="1">
         <v>0</v>
       </c>
@@ -2509,8 +2648,12 @@
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
-      <c r="AD30" s="1"/>
-      <c r="AE30" s="1"/>
+      <c r="AD30" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="1">
+        <v>0</v>
+      </c>
       <c r="AF30" s="1">
         <v>0</v>
       </c>
@@ -2538,8 +2681,12 @@
         <v>54</v>
       </c>
       <c r="AC31" s="1"/>
-      <c r="AD31" s="1"/>
-      <c r="AE31" s="1"/>
+      <c r="AD31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="1">
+        <v>0</v>
+      </c>
       <c r="AF31" s="1">
         <v>0</v>
       </c>
@@ -2569,8 +2716,12 @@
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
-      <c r="AD32" s="1"/>
-      <c r="AE32" s="1"/>
+      <c r="AD32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="1">
+        <v>0</v>
+      </c>
       <c r="AF32" s="1">
         <v>0</v>
       </c>
@@ -2597,7 +2748,12 @@
       <c r="A33" t="s">
         <v>53</v>
       </c>
-      <c r="AE33" s="1"/>
+      <c r="AD33">
+        <v>712</v>
+      </c>
+      <c r="AE33" s="1">
+        <v>0</v>
+      </c>
       <c r="AF33" s="1">
         <v>0</v>
       </c>
@@ -2627,8 +2783,12 @@
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
-      <c r="AD34" s="1"/>
-      <c r="AE34" s="1"/>
+      <c r="AD34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="1">
+        <v>0</v>
+      </c>
       <c r="AF34" s="1">
         <v>0</v>
       </c>
@@ -2658,8 +2818,12 @@
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
-      <c r="AD35" s="1"/>
-      <c r="AE35" s="1"/>
+      <c r="AD35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="1">
+        <v>0</v>
+      </c>
       <c r="AF35" s="1">
         <v>0</v>
       </c>
@@ -2689,8 +2853,12 @@
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
-      <c r="AD36" s="1"/>
-      <c r="AE36" s="1"/>
+      <c r="AD36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="1">
+        <v>0</v>
+      </c>
       <c r="AF36" s="1">
         <v>0</v>
       </c>
@@ -2720,8 +2888,12 @@
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
-      <c r="AD37" s="1"/>
-      <c r="AE37" s="1"/>
+      <c r="AD37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="1">
+        <v>0</v>
+      </c>
       <c r="AF37" s="1">
         <v>0</v>
       </c>
@@ -2751,8 +2923,12 @@
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
-      <c r="AD38" s="1"/>
-      <c r="AE38" s="1"/>
+      <c r="AD38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="1">
+        <v>0</v>
+      </c>
       <c r="AF38" s="1">
         <v>0</v>
       </c>
@@ -2783,8 +2959,12 @@
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
-      <c r="AD39" s="1"/>
-      <c r="AE39" s="1"/>
+      <c r="AD39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="1">
+        <v>0</v>
+      </c>
       <c r="AF39" s="1">
         <v>0</v>
       </c>
@@ -2815,8 +2995,12 @@
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
-      <c r="AD40" s="1"/>
-      <c r="AE40" s="1"/>
+      <c r="AD40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="1">
+        <v>0</v>
+      </c>
       <c r="AF40" s="1">
         <v>0</v>
       </c>
@@ -2843,7 +3027,12 @@
       <c r="A41" t="s">
         <v>64</v>
       </c>
-      <c r="AE41" s="1"/>
+      <c r="AD41">
+        <v>502</v>
+      </c>
+      <c r="AE41" s="1">
+        <v>0</v>
+      </c>
       <c r="AF41" s="1">
         <v>0</v>
       </c>
@@ -2874,8 +3063,12 @@
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
-      <c r="AD42" s="1"/>
-      <c r="AE42" s="1"/>
+      <c r="AD42" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="1">
+        <v>0</v>
+      </c>
       <c r="AF42" s="1">
         <v>0</v>
       </c>
@@ -2906,8 +3099,12 @@
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
-      <c r="AD43" s="1"/>
-      <c r="AE43" s="1"/>
+      <c r="AD43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="1">
+        <v>0</v>
+      </c>
       <c r="AF43" s="1">
         <v>0</v>
       </c>
@@ -2939,8 +3136,12 @@
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
-      <c r="AD44" s="1"/>
-      <c r="AE44" s="1"/>
+      <c r="AD44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="1">
+        <v>0</v>
+      </c>
       <c r="AF44" s="1">
         <v>0</v>
       </c>
@@ -2966,6 +3167,12 @@
     <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>68</v>
+      </c>
+      <c r="AD45">
+        <v>685</v>
+      </c>
+      <c r="AE45">
+        <v>848</v>
       </c>
       <c r="AF45">
         <v>154</v>
@@ -2998,8 +3205,12 @@
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
-      <c r="AD46" s="1"/>
-      <c r="AE46" s="1"/>
+      <c r="AD46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="1">
+        <v>0</v>
+      </c>
       <c r="AF46" s="1">
         <v>0</v>
       </c>
@@ -3031,8 +3242,12 @@
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
-      <c r="AD47" s="1"/>
-      <c r="AE47" s="1"/>
+      <c r="AD47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="1">
+        <v>0</v>
+      </c>
       <c r="AF47" s="1">
         <v>0</v>
       </c>
@@ -3064,8 +3279,12 @@
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
-      <c r="AD48" s="1"/>
-      <c r="AE48" s="1"/>
+      <c r="AD48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="1">
+        <v>0</v>
+      </c>
       <c r="AF48" s="1">
         <v>0</v>
       </c>
@@ -3097,8 +3316,12 @@
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
-      <c r="AD49" s="1"/>
-      <c r="AE49" s="1"/>
+      <c r="AD49" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="1">
+        <v>0</v>
+      </c>
       <c r="AF49" s="1">
         <v>0</v>
       </c>
@@ -3130,8 +3353,12 @@
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
-      <c r="AD50" s="1"/>
-      <c r="AE50" s="1"/>
+      <c r="AD50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="1">
+        <v>0</v>
+      </c>
       <c r="AF50" s="1">
         <v>0</v>
       </c>
@@ -3164,8 +3391,12 @@
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
-      <c r="AD51" s="1"/>
-      <c r="AE51" s="1"/>
+      <c r="AD51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="1">
+        <v>0</v>
+      </c>
       <c r="AF51" s="1">
         <v>0</v>
       </c>
@@ -3198,8 +3429,12 @@
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
-      <c r="AD52" s="1"/>
-      <c r="AE52" s="1"/>
+      <c r="AD52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="1">
+        <v>0</v>
+      </c>
       <c r="AF52" s="1">
         <v>0</v>
       </c>
@@ -3232,8 +3467,12 @@
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
-      <c r="AD53" s="1"/>
-      <c r="AE53" s="1"/>
+      <c r="AD53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="1">
+        <v>0</v>
+      </c>
       <c r="AF53" s="1">
         <v>0</v>
       </c>
@@ -3266,8 +3505,12 @@
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
-      <c r="AD54" s="1"/>
-      <c r="AE54" s="1"/>
+      <c r="AD54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="1">
+        <v>0</v>
+      </c>
       <c r="AF54" s="1">
         <v>0</v>
       </c>
@@ -3300,8 +3543,12 @@
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
-      <c r="AD55" s="1"/>
-      <c r="AE55" s="1"/>
+      <c r="AD55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="1">
+        <v>0</v>
+      </c>
       <c r="AF55" s="1">
         <v>0</v>
       </c>
@@ -3334,8 +3581,12 @@
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
-      <c r="AD56" s="1"/>
-      <c r="AE56" s="1"/>
+      <c r="AD56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="1">
+        <v>0</v>
+      </c>
       <c r="AF56" s="1">
         <v>0</v>
       </c>
@@ -3369,8 +3620,12 @@
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
-      <c r="AD57" s="1"/>
-      <c r="AE57" s="1"/>
+      <c r="AD57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="1">
+        <v>0</v>
+      </c>
       <c r="AF57" s="1">
         <v>0</v>
       </c>
@@ -3404,8 +3659,12 @@
       <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
       <c r="AC58" s="1"/>
-      <c r="AD58" s="1"/>
-      <c r="AE58" s="1"/>
+      <c r="AD58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="1">
+        <v>0</v>
+      </c>
       <c r="AF58" s="1">
         <v>0</v>
       </c>
@@ -3439,8 +3698,12 @@
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
-      <c r="AD59" s="1"/>
-      <c r="AE59" s="1"/>
+      <c r="AD59" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="1">
+        <v>0</v>
+      </c>
       <c r="AF59" s="1">
         <v>0</v>
       </c>
@@ -3474,8 +3737,12 @@
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
-      <c r="AD60" s="1"/>
-      <c r="AE60" s="1"/>
+      <c r="AD60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="1">
+        <v>0</v>
+      </c>
       <c r="AF60" s="1">
         <v>0</v>
       </c>
@@ -3509,8 +3776,12 @@
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
-      <c r="AD61" s="1"/>
-      <c r="AE61" s="1"/>
+      <c r="AD61" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="1">
+        <v>0</v>
+      </c>
       <c r="AF61" s="1">
         <v>0</v>
       </c>
@@ -3545,8 +3816,12 @@
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
-      <c r="AD62" s="1"/>
-      <c r="AE62" s="1"/>
+      <c r="AD62" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="1">
+        <v>0</v>
+      </c>
       <c r="AF62" s="1">
         <v>0</v>
       </c>
@@ -3581,8 +3856,12 @@
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
-      <c r="AD63" s="1"/>
-      <c r="AE63" s="1"/>
+      <c r="AD63" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="1">
+        <v>0</v>
+      </c>
       <c r="AF63" s="1">
         <v>0</v>
       </c>
@@ -3618,8 +3897,12 @@
       <c r="AA64" s="1"/>
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
-      <c r="AD64" s="1"/>
-      <c r="AE64" s="1"/>
+      <c r="AD64" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="1">
+        <v>0</v>
+      </c>
       <c r="AF64" s="1">
         <v>0</v>
       </c>
@@ -3655,8 +3938,12 @@
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
-      <c r="AD65" s="1"/>
-      <c r="AE65" s="1"/>
+      <c r="AD65" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="1">
+        <v>0</v>
+      </c>
       <c r="AF65" s="1">
         <v>0</v>
       </c>
@@ -3692,8 +3979,12 @@
       <c r="AA66" s="1"/>
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
-      <c r="AD66" s="1"/>
-      <c r="AE66" s="1"/>
+      <c r="AD66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE66" s="1">
+        <v>0</v>
+      </c>
       <c r="AF66" s="1">
         <v>0</v>
       </c>
@@ -3729,8 +4020,12 @@
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
-      <c r="AD67" s="1"/>
-      <c r="AE67" s="1"/>
+      <c r="AD67" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE67" s="1">
+        <v>0</v>
+      </c>
       <c r="AF67" s="1">
         <v>0</v>
       </c>
@@ -3757,7 +4052,39 @@
       <c r="A68" t="s">
         <v>92</v>
       </c>
-      <c r="AE68" s="1"/>
+      <c r="U68" s="1">
+        <v>0</v>
+      </c>
+      <c r="V68" s="1">
+        <v>0</v>
+      </c>
+      <c r="W68" s="1">
+        <v>0</v>
+      </c>
+      <c r="X68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD68">
+        <v>659</v>
+      </c>
+      <c r="AE68" s="1">
+        <v>0</v>
+      </c>
       <c r="AF68" s="1">
         <v>0</v>
       </c>
@@ -3794,8 +4121,12 @@
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
-      <c r="AD69" s="1"/>
-      <c r="AE69" s="1"/>
+      <c r="AD69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="1">
+        <v>0</v>
+      </c>
       <c r="AF69" s="1">
         <v>0</v>
       </c>
@@ -3832,8 +4163,12 @@
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
-      <c r="AD70" s="1"/>
-      <c r="AE70" s="1"/>
+      <c r="AD70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="1">
+        <v>0</v>
+      </c>
       <c r="AF70" s="1">
         <v>0</v>
       </c>
@@ -3870,8 +4205,12 @@
       <c r="AA71" s="1"/>
       <c r="AB71" s="1"/>
       <c r="AC71" s="1"/>
-      <c r="AD71" s="1"/>
-      <c r="AE71" s="1"/>
+      <c r="AD71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="1">
+        <v>0</v>
+      </c>
       <c r="AF71" s="1">
         <v>0</v>
       </c>
@@ -3908,8 +4247,12 @@
       <c r="AA72" s="1"/>
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
-      <c r="AD72" s="1"/>
-      <c r="AE72" s="1"/>
+      <c r="AD72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE72" s="1">
+        <v>0</v>
+      </c>
       <c r="AF72" s="1">
         <v>0</v>
       </c>
@@ -3946,8 +4289,12 @@
       <c r="AA73" s="1"/>
       <c r="AB73" s="1"/>
       <c r="AC73" s="1"/>
-      <c r="AD73" s="1"/>
-      <c r="AE73" s="1"/>
+      <c r="AD73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="1">
+        <v>0</v>
+      </c>
       <c r="AF73" s="1">
         <v>0</v>
       </c>
@@ -3985,8 +4332,12 @@
       <c r="AA74" s="1"/>
       <c r="AB74" s="1"/>
       <c r="AC74" s="1"/>
-      <c r="AD74" s="1"/>
-      <c r="AE74" s="1"/>
+      <c r="AD74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="1">
+        <v>0</v>
+      </c>
       <c r="AF74" s="1">
         <v>0</v>
       </c>
@@ -4024,8 +4375,12 @@
       <c r="AA75" s="1"/>
       <c r="AB75" s="1"/>
       <c r="AC75" s="1"/>
-      <c r="AD75" s="1"/>
-      <c r="AE75" s="1"/>
+      <c r="AD75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="1">
+        <v>0</v>
+      </c>
       <c r="AF75" s="1">
         <v>0</v>
       </c>
@@ -4063,8 +4418,12 @@
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
-      <c r="AD76" s="1"/>
-      <c r="AE76" s="1"/>
+      <c r="AD76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="1">
+        <v>0</v>
+      </c>
       <c r="AF76" s="1">
         <v>0</v>
       </c>
@@ -4102,8 +4461,12 @@
       <c r="AA77" s="1"/>
       <c r="AB77" s="1"/>
       <c r="AC77" s="1"/>
-      <c r="AD77" s="1"/>
-      <c r="AE77" s="1"/>
+      <c r="AD77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="1">
+        <v>0</v>
+      </c>
       <c r="AF77" s="1">
         <v>0</v>
       </c>
@@ -4141,8 +4504,12 @@
       <c r="AA78" s="1"/>
       <c r="AB78" s="1"/>
       <c r="AC78" s="1"/>
-      <c r="AD78" s="1"/>
-      <c r="AE78" s="1"/>
+      <c r="AD78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE78" s="1">
+        <v>0</v>
+      </c>
       <c r="AF78" s="1">
         <v>0</v>
       </c>
@@ -4181,8 +4548,12 @@
       <c r="AA79" s="1"/>
       <c r="AB79" s="1"/>
       <c r="AC79" s="1"/>
-      <c r="AD79" s="1"/>
-      <c r="AE79" s="1"/>
+      <c r="AD79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE79" s="1">
+        <v>0</v>
+      </c>
       <c r="AF79" s="1">
         <v>0</v>
       </c>
@@ -4221,8 +4592,12 @@
       <c r="AA80" s="1"/>
       <c r="AB80" s="1"/>
       <c r="AC80" s="1"/>
-      <c r="AD80" s="1"/>
-      <c r="AE80" s="1"/>
+      <c r="AD80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="1">
+        <v>0</v>
+      </c>
       <c r="AF80" s="1">
         <v>0</v>
       </c>
@@ -4262,8 +4637,12 @@
       <c r="AA81" s="1"/>
       <c r="AB81" s="1"/>
       <c r="AC81" s="1"/>
-      <c r="AD81" s="1"/>
-      <c r="AE81" s="1"/>
+      <c r="AD81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="1">
+        <v>0</v>
+      </c>
       <c r="AF81" s="1">
         <v>0</v>
       </c>
@@ -4303,8 +4682,12 @@
       <c r="AA82" s="1"/>
       <c r="AB82" s="1"/>
       <c r="AC82" s="1"/>
-      <c r="AD82" s="1"/>
-      <c r="AE82" s="1"/>
+      <c r="AD82" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE82" s="1">
+        <v>0</v>
+      </c>
       <c r="AF82" s="1">
         <v>0</v>
       </c>
@@ -4344,8 +4727,12 @@
       <c r="AA83" s="1"/>
       <c r="AB83" s="1"/>
       <c r="AC83" s="1"/>
-      <c r="AD83" s="1"/>
-      <c r="AE83" s="1"/>
+      <c r="AD83" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="1">
+        <v>0</v>
+      </c>
       <c r="AF83" s="1">
         <v>0</v>
       </c>
@@ -4385,8 +4772,12 @@
       <c r="AA84" s="1"/>
       <c r="AB84" s="1"/>
       <c r="AC84" s="1"/>
-      <c r="AD84" s="1"/>
-      <c r="AE84" s="1"/>
+      <c r="AD84" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="1">
+        <v>0</v>
+      </c>
       <c r="AF84" s="1">
         <v>0</v>
       </c>
@@ -4426,8 +4817,12 @@
       <c r="AA85" s="1"/>
       <c r="AB85" s="1"/>
       <c r="AC85" s="1"/>
-      <c r="AD85" s="1"/>
-      <c r="AE85" s="1"/>
+      <c r="AD85" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="1">
+        <v>0</v>
+      </c>
       <c r="AF85" s="1">
         <v>0</v>
       </c>
@@ -4468,8 +4863,12 @@
       <c r="AA86" s="1"/>
       <c r="AB86" s="1"/>
       <c r="AC86" s="1"/>
-      <c r="AD86" s="1"/>
-      <c r="AE86" s="1"/>
+      <c r="AD86" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="1">
+        <v>0</v>
+      </c>
       <c r="AF86" s="1">
         <v>0</v>
       </c>
@@ -4510,8 +4909,12 @@
       <c r="AA87" s="1"/>
       <c r="AB87" s="1"/>
       <c r="AC87" s="1"/>
-      <c r="AD87" s="1"/>
-      <c r="AE87" s="1"/>
+      <c r="AD87" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="1">
+        <v>0</v>
+      </c>
       <c r="AF87" s="1">
         <v>0</v>
       </c>
@@ -4552,8 +4955,12 @@
       <c r="AA88" s="1"/>
       <c r="AB88" s="1"/>
       <c r="AC88" s="1"/>
-      <c r="AD88" s="1"/>
-      <c r="AE88" s="1"/>
+      <c r="AD88" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="1">
+        <v>0</v>
+      </c>
       <c r="AF88" s="1">
         <v>0</v>
       </c>
@@ -4594,8 +5001,12 @@
       <c r="AA89" s="1"/>
       <c r="AB89" s="1"/>
       <c r="AC89" s="1"/>
-      <c r="AD89" s="1"/>
-      <c r="AE89" s="1"/>
+      <c r="AD89" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="1">
+        <v>0</v>
+      </c>
       <c r="AF89" s="1">
         <v>0</v>
       </c>
@@ -4637,8 +5048,12 @@
       <c r="AA90" s="1"/>
       <c r="AB90" s="1"/>
       <c r="AC90" s="1"/>
-      <c r="AD90" s="1"/>
-      <c r="AE90" s="1"/>
+      <c r="AD90" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="1">
+        <v>0</v>
+      </c>
       <c r="AF90" s="1">
         <v>0</v>
       </c>
@@ -4680,8 +5095,12 @@
       <c r="AA91" s="1"/>
       <c r="AB91" s="1"/>
       <c r="AC91" s="1"/>
-      <c r="AD91" s="1"/>
-      <c r="AE91" s="1"/>
+      <c r="AD91" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="1">
+        <v>0</v>
+      </c>
       <c r="AF91" s="1">
         <v>0</v>
       </c>
@@ -4723,8 +5142,12 @@
       <c r="AA92" s="1"/>
       <c r="AB92" s="1"/>
       <c r="AC92" s="1"/>
-      <c r="AD92" s="1"/>
-      <c r="AE92" s="1"/>
+      <c r="AD92" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="1">
+        <v>0</v>
+      </c>
       <c r="AF92" s="1">
         <v>0</v>
       </c>
@@ -4766,8 +5189,12 @@
       <c r="AA93" s="1"/>
       <c r="AB93" s="1"/>
       <c r="AC93" s="1"/>
-      <c r="AD93" s="1"/>
-      <c r="AE93" s="1"/>
+      <c r="AD93" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="1">
+        <v>0</v>
+      </c>
       <c r="AF93" s="1">
         <v>0</v>
       </c>
@@ -4809,8 +5236,12 @@
       <c r="AA94" s="1"/>
       <c r="AB94" s="1"/>
       <c r="AC94" s="1"/>
-      <c r="AD94" s="1"/>
-      <c r="AE94" s="1"/>
+      <c r="AD94" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="1">
+        <v>0</v>
+      </c>
       <c r="AF94" s="1">
         <v>0</v>
       </c>
@@ -4853,8 +5284,12 @@
       <c r="AA95" s="1"/>
       <c r="AB95" s="1"/>
       <c r="AC95" s="1"/>
-      <c r="AD95" s="1"/>
-      <c r="AE95" s="1"/>
+      <c r="AD95" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE95" s="1">
+        <v>0</v>
+      </c>
       <c r="AF95" s="1">
         <v>0</v>
       </c>
@@ -4897,8 +5332,12 @@
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
       <c r="AC96" s="1"/>
-      <c r="AD96" s="1"/>
-      <c r="AE96" s="1"/>
+      <c r="AD96" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="1">
+        <v>0</v>
+      </c>
       <c r="AF96" s="1">
         <v>0</v>
       </c>
@@ -4941,8 +5380,12 @@
       <c r="AA97" s="1"/>
       <c r="AB97" s="1"/>
       <c r="AC97" s="1"/>
-      <c r="AD97" s="1"/>
-      <c r="AE97" s="1"/>
+      <c r="AD97" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="1">
+        <v>0</v>
+      </c>
       <c r="AF97" s="1">
         <v>0</v>
       </c>
@@ -4985,8 +5428,12 @@
       <c r="AA98" s="1"/>
       <c r="AB98" s="1"/>
       <c r="AC98" s="1"/>
-      <c r="AD98" s="1"/>
-      <c r="AE98" s="1"/>
+      <c r="AD98" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="1">
+        <v>0</v>
+      </c>
       <c r="AF98" s="1">
         <v>0</v>
       </c>
@@ -5029,8 +5476,12 @@
       <c r="AA99" s="1"/>
       <c r="AB99" s="1"/>
       <c r="AC99" s="1"/>
-      <c r="AD99" s="1"/>
-      <c r="AE99" s="1"/>
+      <c r="AD99" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="1">
+        <v>0</v>
+      </c>
       <c r="AF99" s="1">
         <v>0</v>
       </c>
@@ -5074,8 +5525,12 @@
       <c r="AA100" s="1"/>
       <c r="AB100" s="1"/>
       <c r="AC100" s="1"/>
-      <c r="AD100" s="1"/>
-      <c r="AE100" s="1"/>
+      <c r="AD100" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="1">
+        <v>0</v>
+      </c>
       <c r="AF100" s="1">
         <v>0</v>
       </c>
@@ -5119,8 +5574,12 @@
       <c r="AA101" s="1"/>
       <c r="AB101" s="1"/>
       <c r="AC101" s="1"/>
-      <c r="AD101" s="1"/>
-      <c r="AE101" s="1"/>
+      <c r="AD101" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="1">
+        <v>0</v>
+      </c>
       <c r="AF101" s="1">
         <v>0</v>
       </c>
@@ -5164,8 +5623,12 @@
       <c r="AA102" s="1"/>
       <c r="AB102" s="1"/>
       <c r="AC102" s="1"/>
-      <c r="AD102" s="1"/>
-      <c r="AE102" s="1"/>
+      <c r="AD102" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="1">
+        <v>0</v>
+      </c>
       <c r="AF102" s="1">
         <v>0</v>
       </c>
@@ -5209,8 +5672,12 @@
       <c r="AA103" s="1"/>
       <c r="AB103" s="1"/>
       <c r="AC103" s="1"/>
-      <c r="AD103" s="1"/>
-      <c r="AE103" s="1"/>
+      <c r="AD103" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="1">
+        <v>0</v>
+      </c>
       <c r="AF103" s="1">
         <v>0</v>
       </c>
@@ -5255,8 +5722,12 @@
       <c r="AA104" s="1"/>
       <c r="AB104" s="1"/>
       <c r="AC104" s="1"/>
-      <c r="AD104" s="1"/>
-      <c r="AE104" s="1"/>
+      <c r="AD104" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE104" s="1">
+        <v>0</v>
+      </c>
       <c r="AF104" s="1">
         <v>0</v>
       </c>
@@ -5301,8 +5772,12 @@
       <c r="AA105" s="1"/>
       <c r="AB105" s="1"/>
       <c r="AC105" s="1"/>
-      <c r="AD105" s="1"/>
-      <c r="AE105" s="1"/>
+      <c r="AD105" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE105" s="1">
+        <v>0</v>
+      </c>
       <c r="AF105" s="1">
         <v>0</v>
       </c>
@@ -5348,8 +5823,12 @@
       <c r="AA106" s="1"/>
       <c r="AB106" s="1"/>
       <c r="AC106" s="1"/>
-      <c r="AD106" s="1"/>
-      <c r="AE106" s="1"/>
+      <c r="AD106" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE106" s="1">
+        <v>0</v>
+      </c>
       <c r="AF106" s="1">
         <v>0</v>
       </c>
@@ -5395,8 +5874,12 @@
       <c r="AA107" s="1"/>
       <c r="AB107" s="1"/>
       <c r="AC107" s="1"/>
-      <c r="AD107" s="1"/>
-      <c r="AE107" s="1"/>
+      <c r="AD107" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE107" s="1">
+        <v>0</v>
+      </c>
       <c r="AF107" s="1">
         <v>0</v>
       </c>
@@ -5442,8 +5925,12 @@
       <c r="AA108" s="1"/>
       <c r="AB108" s="1"/>
       <c r="AC108" s="1"/>
-      <c r="AD108" s="1"/>
-      <c r="AE108" s="1"/>
+      <c r="AD108" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE108" s="1">
+        <v>0</v>
+      </c>
       <c r="AF108" s="1">
         <v>0</v>
       </c>
@@ -5490,8 +5977,12 @@
       <c r="AA109" s="1"/>
       <c r="AB109" s="1"/>
       <c r="AC109" s="1"/>
-      <c r="AD109" s="1"/>
-      <c r="AE109" s="1"/>
+      <c r="AD109" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE109" s="1">
+        <v>0</v>
+      </c>
       <c r="AF109" s="1">
         <v>0</v>
       </c>
@@ -5538,8 +6029,12 @@
       <c r="AA110" s="1"/>
       <c r="AB110" s="1"/>
       <c r="AC110" s="1"/>
-      <c r="AD110" s="1"/>
-      <c r="AE110" s="1"/>
+      <c r="AD110" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE110" s="1">
+        <v>0</v>
+      </c>
       <c r="AF110" s="1">
         <v>0</v>
       </c>
@@ -5586,8 +6081,12 @@
       <c r="AA111" s="1"/>
       <c r="AB111" s="1"/>
       <c r="AC111" s="1"/>
-      <c r="AD111" s="1"/>
-      <c r="AE111" s="1"/>
+      <c r="AD111" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="1">
+        <v>0</v>
+      </c>
       <c r="AF111" s="1">
         <v>0</v>
       </c>
@@ -5635,8 +6134,12 @@
       <c r="AA112" s="1"/>
       <c r="AB112" s="1"/>
       <c r="AC112" s="1"/>
-      <c r="AD112" s="1"/>
-      <c r="AE112" s="1"/>
+      <c r="AD112" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE112" s="1">
+        <v>0</v>
+      </c>
       <c r="AF112" s="1">
         <v>0</v>
       </c>
@@ -5684,8 +6187,12 @@
       <c r="AA113" s="1"/>
       <c r="AB113" s="1"/>
       <c r="AC113" s="1"/>
-      <c r="AD113" s="1"/>
-      <c r="AE113" s="1"/>
+      <c r="AD113" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE113" s="1">
+        <v>0</v>
+      </c>
       <c r="AF113" s="1">
         <v>0</v>
       </c>
@@ -5733,8 +6240,12 @@
       <c r="AA114" s="1"/>
       <c r="AB114" s="1"/>
       <c r="AC114" s="1"/>
-      <c r="AD114" s="1"/>
-      <c r="AE114" s="1"/>
+      <c r="AD114" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE114" s="1">
+        <v>0</v>
+      </c>
       <c r="AF114" s="1">
         <v>0</v>
       </c>
@@ -5783,8 +6294,12 @@
       <c r="AA115" s="1"/>
       <c r="AB115" s="1"/>
       <c r="AC115" s="1"/>
-      <c r="AD115" s="1"/>
-      <c r="AE115" s="1"/>
+      <c r="AD115" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE115" s="1">
+        <v>0</v>
+      </c>
       <c r="AF115" s="1">
         <v>0</v>
       </c>
@@ -5833,8 +6348,12 @@
       <c r="AA116" s="1"/>
       <c r="AB116" s="1"/>
       <c r="AC116" s="1"/>
-      <c r="AD116" s="1"/>
-      <c r="AE116" s="1"/>
+      <c r="AD116" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE116" s="1">
+        <v>0</v>
+      </c>
       <c r="AF116" s="1">
         <v>0</v>
       </c>
@@ -5884,8 +6403,12 @@
       <c r="AA117" s="1"/>
       <c r="AB117" s="1"/>
       <c r="AC117" s="1"/>
-      <c r="AD117" s="1"/>
-      <c r="AE117" s="1"/>
+      <c r="AD117" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE117" s="1">
+        <v>0</v>
+      </c>
       <c r="AF117" s="1">
         <v>0</v>
       </c>
@@ -5935,8 +6458,12 @@
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
       <c r="AC118" s="1"/>
-      <c r="AD118" s="1"/>
-      <c r="AE118" s="1"/>
+      <c r="AD118" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE118" s="1">
+        <v>0</v>
+      </c>
       <c r="AF118" s="1">
         <v>0</v>
       </c>
@@ -5986,8 +6513,12 @@
       <c r="AA119" s="1"/>
       <c r="AB119" s="1"/>
       <c r="AC119" s="1"/>
-      <c r="AD119" s="1"/>
-      <c r="AE119" s="1"/>
+      <c r="AD119" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE119" s="1">
+        <v>0</v>
+      </c>
       <c r="AF119" s="1">
         <v>0</v>
       </c>
@@ -6038,8 +6569,12 @@
       <c r="AA120" s="1"/>
       <c r="AB120" s="1"/>
       <c r="AC120" s="1"/>
-      <c r="AD120" s="1"/>
-      <c r="AE120" s="1"/>
+      <c r="AD120" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE120" s="1">
+        <v>0</v>
+      </c>
       <c r="AF120" s="1">
         <v>0</v>
       </c>
@@ -6090,8 +6625,12 @@
       <c r="AA121" s="1"/>
       <c r="AB121" s="1"/>
       <c r="AC121" s="1"/>
-      <c r="AD121" s="1"/>
-      <c r="AE121" s="1"/>
+      <c r="AD121" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE121" s="1">
+        <v>0</v>
+      </c>
       <c r="AF121" s="1">
         <v>0</v>
       </c>
@@ -6142,8 +6681,12 @@
       <c r="AA122" s="1"/>
       <c r="AB122" s="1"/>
       <c r="AC122" s="1"/>
-      <c r="AD122" s="1"/>
-      <c r="AE122" s="1"/>
+      <c r="AD122" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE122" s="1">
+        <v>0</v>
+      </c>
       <c r="AF122" s="1">
         <v>0</v>
       </c>
@@ -6195,8 +6738,12 @@
       <c r="AA123" s="1"/>
       <c r="AB123" s="1"/>
       <c r="AC123" s="1"/>
-      <c r="AD123" s="1"/>
-      <c r="AE123" s="1"/>
+      <c r="AD123" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE123" s="1">
+        <v>0</v>
+      </c>
       <c r="AF123" s="1">
         <v>0</v>
       </c>
@@ -6248,8 +6795,12 @@
       <c r="AA124" s="1"/>
       <c r="AB124" s="1"/>
       <c r="AC124" s="1"/>
-      <c r="AD124" s="1"/>
-      <c r="AE124" s="1"/>
+      <c r="AD124" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE124" s="1">
+        <v>0</v>
+      </c>
       <c r="AF124" s="1">
         <v>0</v>
       </c>
@@ -6301,8 +6852,12 @@
       <c r="AA125" s="1"/>
       <c r="AB125" s="1"/>
       <c r="AC125" s="1"/>
-      <c r="AD125" s="1"/>
-      <c r="AE125" s="1"/>
+      <c r="AD125" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE125" s="1">
+        <v>0</v>
+      </c>
       <c r="AF125" s="1">
         <v>0</v>
       </c>
@@ -6355,8 +6910,12 @@
       <c r="AA126" s="1"/>
       <c r="AB126" s="1"/>
       <c r="AC126" s="1"/>
-      <c r="AD126" s="1"/>
-      <c r="AE126" s="1"/>
+      <c r="AD126" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE126" s="1">
+        <v>0</v>
+      </c>
       <c r="AF126" s="1">
         <v>0</v>
       </c>
@@ -6387,10 +6946,997 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A672F957-1D62-4580-B7C6-2DFEBD8C86A9}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>SUM(C2:R2)</f>
+        <v>543</v>
+      </c>
+      <c r="C2">
+        <v>56</v>
+      </c>
+      <c r="D2">
+        <v>72</v>
+      </c>
+      <c r="E2">
+        <v>62</v>
+      </c>
+      <c r="F2">
+        <v>78</v>
+      </c>
+      <c r="G2">
+        <v>65</v>
+      </c>
+      <c r="H2">
+        <v>29</v>
+      </c>
+      <c r="I2">
+        <v>72</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>56</v>
+      </c>
+      <c r="R2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B17" si="0">SUM(C3:R3)</f>
+        <v>850</v>
+      </c>
+      <c r="C3">
+        <v>57</v>
+      </c>
+      <c r="D3">
+        <v>42</v>
+      </c>
+      <c r="E3">
+        <v>61</v>
+      </c>
+      <c r="F3">
+        <v>71</v>
+      </c>
+      <c r="G3">
+        <v>64</v>
+      </c>
+      <c r="H3">
+        <v>14</v>
+      </c>
+      <c r="I3">
+        <v>72</v>
+      </c>
+      <c r="J3">
+        <v>60</v>
+      </c>
+      <c r="K3">
+        <v>55</v>
+      </c>
+      <c r="L3">
+        <v>6</v>
+      </c>
+      <c r="M3">
+        <v>77</v>
+      </c>
+      <c r="N3">
+        <v>44</v>
+      </c>
+      <c r="O3">
+        <v>53</v>
+      </c>
+      <c r="P3">
+        <v>66</v>
+      </c>
+      <c r="Q3">
+        <v>56</v>
+      </c>
+      <c r="R3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>716</v>
+      </c>
+      <c r="C4">
+        <v>13</v>
+      </c>
+      <c r="D4">
+        <v>22</v>
+      </c>
+      <c r="E4">
+        <v>62</v>
+      </c>
+      <c r="F4">
+        <v>36</v>
+      </c>
+      <c r="G4">
+        <v>65</v>
+      </c>
+      <c r="H4">
+        <v>69</v>
+      </c>
+      <c r="I4">
+        <v>9</v>
+      </c>
+      <c r="J4">
+        <v>60</v>
+      </c>
+      <c r="K4">
+        <v>71</v>
+      </c>
+      <c r="L4">
+        <v>45</v>
+      </c>
+      <c r="M4">
+        <v>77</v>
+      </c>
+      <c r="N4">
+        <v>44</v>
+      </c>
+      <c r="O4">
+        <v>53</v>
+      </c>
+      <c r="P4">
+        <v>37</v>
+      </c>
+      <c r="Q4">
+        <v>14</v>
+      </c>
+      <c r="R4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>828</v>
+      </c>
+      <c r="C5">
+        <v>57</v>
+      </c>
+      <c r="D5">
+        <v>71</v>
+      </c>
+      <c r="E5">
+        <v>28</v>
+      </c>
+      <c r="F5">
+        <v>54</v>
+      </c>
+      <c r="G5">
+        <v>65</v>
+      </c>
+      <c r="H5">
+        <v>69</v>
+      </c>
+      <c r="I5">
+        <v>72</v>
+      </c>
+      <c r="J5">
+        <v>60</v>
+      </c>
+      <c r="K5">
+        <v>8</v>
+      </c>
+      <c r="L5">
+        <v>45</v>
+      </c>
+      <c r="M5">
+        <v>76</v>
+      </c>
+      <c r="N5">
+        <v>44</v>
+      </c>
+      <c r="O5">
+        <v>53</v>
+      </c>
+      <c r="P5">
+        <v>66</v>
+      </c>
+      <c r="Q5">
+        <v>7</v>
+      </c>
+      <c r="R5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>573</v>
+      </c>
+      <c r="C6">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>49</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>32</v>
+      </c>
+      <c r="G6">
+        <v>40</v>
+      </c>
+      <c r="H6">
+        <v>34</v>
+      </c>
+      <c r="I6">
+        <v>25</v>
+      </c>
+      <c r="J6">
+        <v>29</v>
+      </c>
+      <c r="K6">
+        <v>34</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>60</v>
+      </c>
+      <c r="N6">
+        <v>43</v>
+      </c>
+      <c r="O6">
+        <v>53</v>
+      </c>
+      <c r="P6">
+        <v>61</v>
+      </c>
+      <c r="Q6">
+        <v>48</v>
+      </c>
+      <c r="R6">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>782</v>
+      </c>
+      <c r="C7">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>71</v>
+      </c>
+      <c r="E7">
+        <v>48</v>
+      </c>
+      <c r="F7">
+        <v>40</v>
+      </c>
+      <c r="G7">
+        <v>24</v>
+      </c>
+      <c r="H7">
+        <v>68</v>
+      </c>
+      <c r="I7">
+        <v>72</v>
+      </c>
+      <c r="J7">
+        <v>60</v>
+      </c>
+      <c r="K7">
+        <v>70</v>
+      </c>
+      <c r="L7">
+        <v>45</v>
+      </c>
+      <c r="M7">
+        <v>76</v>
+      </c>
+      <c r="N7">
+        <v>44</v>
+      </c>
+      <c r="O7">
+        <v>52</v>
+      </c>
+      <c r="P7">
+        <v>65</v>
+      </c>
+      <c r="Q7">
+        <v>5</v>
+      </c>
+      <c r="R7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>617</v>
+      </c>
+      <c r="C8">
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <v>21</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>77</v>
+      </c>
+      <c r="G8">
+        <v>64</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>72</v>
+      </c>
+      <c r="J8">
+        <v>60</v>
+      </c>
+      <c r="K8">
+        <v>70</v>
+      </c>
+      <c r="L8">
+        <v>10</v>
+      </c>
+      <c r="M8">
+        <v>76</v>
+      </c>
+      <c r="N8">
+        <v>44</v>
+      </c>
+      <c r="O8">
+        <v>29</v>
+      </c>
+      <c r="P8">
+        <v>66</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>787</v>
+      </c>
+      <c r="C9">
+        <v>57</v>
+      </c>
+      <c r="D9">
+        <v>38</v>
+      </c>
+      <c r="E9">
+        <v>61</v>
+      </c>
+      <c r="F9">
+        <v>77</v>
+      </c>
+      <c r="G9">
+        <v>64</v>
+      </c>
+      <c r="H9">
+        <v>69</v>
+      </c>
+      <c r="I9">
+        <v>42</v>
+      </c>
+      <c r="J9">
+        <v>60</v>
+      </c>
+      <c r="K9">
+        <v>68</v>
+      </c>
+      <c r="L9">
+        <v>7</v>
+      </c>
+      <c r="M9">
+        <v>52</v>
+      </c>
+      <c r="N9">
+        <v>44</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>48</v>
+      </c>
+      <c r="Q9">
+        <v>52</v>
+      </c>
+      <c r="R9">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>653</v>
+      </c>
+      <c r="C10">
+        <v>57</v>
+      </c>
+      <c r="D10">
+        <v>52</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10">
+        <v>30</v>
+      </c>
+      <c r="G10">
+        <v>63</v>
+      </c>
+      <c r="H10">
+        <v>22</v>
+      </c>
+      <c r="I10">
+        <v>71</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>38</v>
+      </c>
+      <c r="L10">
+        <v>37</v>
+      </c>
+      <c r="M10">
+        <v>75</v>
+      </c>
+      <c r="N10">
+        <v>35</v>
+      </c>
+      <c r="O10">
+        <v>35</v>
+      </c>
+      <c r="P10">
+        <v>52</v>
+      </c>
+      <c r="Q10">
+        <v>30</v>
+      </c>
+      <c r="R10">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>983</v>
+      </c>
+      <c r="C11">
+        <v>57</v>
+      </c>
+      <c r="D11">
+        <v>71</v>
+      </c>
+      <c r="E11">
+        <v>46</v>
+      </c>
+      <c r="F11">
+        <v>78</v>
+      </c>
+      <c r="G11">
+        <v>65</v>
+      </c>
+      <c r="H11">
+        <v>69</v>
+      </c>
+      <c r="I11">
+        <v>72</v>
+      </c>
+      <c r="J11">
+        <v>60</v>
+      </c>
+      <c r="K11">
+        <v>71</v>
+      </c>
+      <c r="L11">
+        <v>45</v>
+      </c>
+      <c r="M11">
+        <v>77</v>
+      </c>
+      <c r="N11">
+        <v>44</v>
+      </c>
+      <c r="O11">
+        <v>53</v>
+      </c>
+      <c r="P11">
+        <v>66</v>
+      </c>
+      <c r="Q11">
+        <v>56</v>
+      </c>
+      <c r="R11">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>915</v>
+      </c>
+      <c r="C12">
+        <v>57</v>
+      </c>
+      <c r="D12">
+        <v>71</v>
+      </c>
+      <c r="E12">
+        <v>46</v>
+      </c>
+      <c r="F12">
+        <v>78</v>
+      </c>
+      <c r="G12">
+        <v>35</v>
+      </c>
+      <c r="H12">
+        <v>65</v>
+      </c>
+      <c r="I12">
+        <v>72</v>
+      </c>
+      <c r="J12">
+        <v>60</v>
+      </c>
+      <c r="K12">
+        <v>71</v>
+      </c>
+      <c r="L12">
+        <v>45</v>
+      </c>
+      <c r="M12">
+        <v>77</v>
+      </c>
+      <c r="N12">
+        <v>44</v>
+      </c>
+      <c r="O12">
+        <v>53</v>
+      </c>
+      <c r="P12">
+        <v>32</v>
+      </c>
+      <c r="Q12">
+        <v>56</v>
+      </c>
+      <c r="R12">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>59</v>
+      </c>
+      <c r="F13">
+        <v>36</v>
+      </c>
+      <c r="G13">
+        <v>64</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>70</v>
+      </c>
+      <c r="L13">
+        <v>45</v>
+      </c>
+      <c r="M13">
+        <v>75</v>
+      </c>
+      <c r="N13">
+        <v>44</v>
+      </c>
+      <c r="O13">
+        <v>53</v>
+      </c>
+      <c r="P13">
+        <v>44</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>712</v>
+      </c>
+      <c r="C14">
+        <v>25</v>
+      </c>
+      <c r="D14">
+        <v>69</v>
+      </c>
+      <c r="E14">
+        <v>59</v>
+      </c>
+      <c r="F14">
+        <v>24</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>68</v>
+      </c>
+      <c r="I14">
+        <v>25</v>
+      </c>
+      <c r="J14">
+        <v>58</v>
+      </c>
+      <c r="K14">
+        <v>70</v>
+      </c>
+      <c r="L14">
+        <v>45</v>
+      </c>
+      <c r="M14">
+        <v>74</v>
+      </c>
+      <c r="N14">
+        <v>43</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>66</v>
+      </c>
+      <c r="Q14">
+        <v>55</v>
+      </c>
+      <c r="R14">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>502</v>
+      </c>
+      <c r="C15">
+        <v>48</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15">
+        <v>72</v>
+      </c>
+      <c r="J15">
+        <v>41</v>
+      </c>
+      <c r="K15">
+        <v>63</v>
+      </c>
+      <c r="L15">
+        <v>20</v>
+      </c>
+      <c r="M15">
+        <v>75</v>
+      </c>
+      <c r="N15">
+        <v>33</v>
+      </c>
+      <c r="O15">
+        <v>25</v>
+      </c>
+      <c r="P15">
+        <v>65</v>
+      </c>
+      <c r="Q15">
+        <v>6</v>
+      </c>
+      <c r="R15">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>685</v>
+      </c>
+      <c r="C16">
+        <v>28</v>
+      </c>
+      <c r="D16">
+        <v>70</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+      <c r="F16">
+        <v>77</v>
+      </c>
+      <c r="G16">
+        <v>64</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>25</v>
+      </c>
+      <c r="J16">
+        <v>60</v>
+      </c>
+      <c r="K16">
+        <v>71</v>
+      </c>
+      <c r="L16">
+        <v>45</v>
+      </c>
+      <c r="M16">
+        <v>77</v>
+      </c>
+      <c r="N16">
+        <v>44</v>
+      </c>
+      <c r="O16">
+        <v>11</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>56</v>
+      </c>
+      <c r="R16">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="C17">
+        <v>42</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>59</v>
+      </c>
+      <c r="F17">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>50</v>
+      </c>
+      <c r="H17">
+        <v>67</v>
+      </c>
+      <c r="I17">
+        <v>71</v>
+      </c>
+      <c r="J17">
+        <v>6</v>
+      </c>
+      <c r="K17">
+        <v>68</v>
+      </c>
+      <c r="L17">
+        <v>44</v>
+      </c>
+      <c r="M17">
+        <v>75</v>
+      </c>
+      <c r="N17">
+        <v>33</v>
+      </c>
+      <c r="O17">
+        <v>23</v>
+      </c>
+      <c r="P17">
+        <v>53</v>
+      </c>
+      <c r="Q17">
+        <v>15</v>
+      </c>
+      <c r="R17">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Data_Files/Laps_Completed.xlsx
+++ b/Data_Files/Laps_Completed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C606660C-5ACD-4D06-A671-9DFC3C4F0915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB049C59-6027-4A44-A9EB-E0B7BED583B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28695" yWindow="1500" windowWidth="16410" windowHeight="14145" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Laps_Completed" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="153">
   <si>
     <t>Driver</t>
   </si>
@@ -1725,6 +1725,9 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="AC2">
+        <v>921</v>
+      </c>
       <c r="AD2">
         <v>543</v>
       </c>
@@ -1757,6 +1760,9 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
+      <c r="AC3">
+        <v>939</v>
+      </c>
       <c r="AD3">
         <v>850</v>
       </c>
@@ -1822,6 +1828,9 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
+      <c r="AC5">
+        <v>973</v>
+      </c>
       <c r="AD5">
         <v>716</v>
       </c>
@@ -1887,6 +1896,9 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
+      <c r="AC7">
+        <v>913</v>
+      </c>
       <c r="AD7">
         <v>828</v>
       </c>
@@ -1953,6 +1965,9 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
+      <c r="AC9">
+        <v>625</v>
+      </c>
       <c r="AD9" s="1">
         <v>0</v>
       </c>
@@ -1985,6 +2000,9 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
+      <c r="AC10">
+        <v>900</v>
+      </c>
       <c r="AD10">
         <v>573</v>
       </c>
@@ -2017,6 +2035,9 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
+      <c r="AC11" s="1">
+        <v>0</v>
+      </c>
       <c r="AD11">
         <v>782</v>
       </c>
@@ -2049,6 +2070,9 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
+      <c r="AC12">
+        <v>789</v>
+      </c>
       <c r="AD12" s="1">
         <v>0</v>
       </c>
@@ -2081,6 +2105,9 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
+      <c r="AC13">
+        <v>709</v>
+      </c>
       <c r="AD13">
         <v>617</v>
       </c>
@@ -2114,7 +2141,9 @@
         <v>13</v>
       </c>
       <c r="AB14" s="1"/>
-      <c r="AC14" s="1"/>
+      <c r="AC14" s="1">
+        <v>0</v>
+      </c>
       <c r="AD14" s="1">
         <v>0</v>
       </c>
@@ -2147,6 +2176,9 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
+      <c r="AC15">
+        <v>389</v>
+      </c>
       <c r="AD15">
         <v>787</v>
       </c>
@@ -2179,6 +2211,9 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
+      <c r="AC16">
+        <v>600</v>
+      </c>
       <c r="AD16">
         <v>653</v>
       </c>
@@ -2211,6 +2246,9 @@
       <c r="A17" t="s">
         <v>16</v>
       </c>
+      <c r="AC17">
+        <v>799</v>
+      </c>
       <c r="AD17">
         <v>983</v>
       </c>
@@ -2244,7 +2282,9 @@
         <v>17</v>
       </c>
       <c r="AB18" s="1"/>
-      <c r="AC18" s="1"/>
+      <c r="AC18" s="1">
+        <v>0</v>
+      </c>
       <c r="AD18" s="1">
         <v>0</v>
       </c>
@@ -2278,7 +2318,9 @@
         <v>85</v>
       </c>
       <c r="AB19" s="1"/>
-      <c r="AC19" s="1"/>
+      <c r="AC19" s="1">
+        <v>0</v>
+      </c>
       <c r="AD19" s="1">
         <v>0</v>
       </c>
@@ -2311,7 +2353,9 @@
       <c r="A20" t="s">
         <v>18</v>
       </c>
-      <c r="AC20" s="1"/>
+      <c r="AC20" s="1">
+        <v>0</v>
+      </c>
       <c r="AD20" s="1">
         <v>0</v>
       </c>
@@ -2344,7 +2388,9 @@
       <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="AC21" s="1"/>
+      <c r="AC21" s="1">
+        <v>0</v>
+      </c>
       <c r="AD21" s="1">
         <v>0</v>
       </c>
@@ -2377,6 +2423,9 @@
       <c r="A22" t="s">
         <v>55</v>
       </c>
+      <c r="AC22">
+        <v>681</v>
+      </c>
       <c r="AD22">
         <v>915</v>
       </c>
@@ -2409,6 +2458,9 @@
       <c r="A23" t="s">
         <v>21</v>
       </c>
+      <c r="AC23">
+        <v>814</v>
+      </c>
       <c r="AD23">
         <v>490</v>
       </c>
@@ -2442,7 +2494,9 @@
         <v>22</v>
       </c>
       <c r="AB24" s="1"/>
-      <c r="AC24" s="1"/>
+      <c r="AC24" s="1">
+        <v>0</v>
+      </c>
       <c r="AD24" s="1">
         <v>0</v>
       </c>
@@ -2475,7 +2529,9 @@
       <c r="A25" t="s">
         <v>44</v>
       </c>
-      <c r="AC25" s="1"/>
+      <c r="AC25" s="1">
+        <v>0</v>
+      </c>
       <c r="AD25" s="1">
         <v>0</v>
       </c>
@@ -2510,7 +2566,9 @@
       </c>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
-      <c r="AC26" s="1"/>
+      <c r="AC26" s="1">
+        <v>0</v>
+      </c>
       <c r="AD26" s="1">
         <v>0</v>
       </c>
@@ -2545,7 +2603,9 @@
       </c>
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
-      <c r="AC27" s="1"/>
+      <c r="AC27" s="1">
+        <v>0</v>
+      </c>
       <c r="AD27" s="1">
         <v>0</v>
       </c>
@@ -2578,6 +2638,9 @@
       <c r="A28" t="s">
         <v>47</v>
       </c>
+      <c r="AC28">
+        <v>695</v>
+      </c>
       <c r="AD28" s="1">
         <v>0</v>
       </c>
@@ -2612,7 +2675,9 @@
       </c>
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
-      <c r="AC29" s="1"/>
+      <c r="AC29" s="1">
+        <v>0</v>
+      </c>
       <c r="AD29" s="1">
         <v>0</v>
       </c>
@@ -2647,7 +2712,9 @@
       </c>
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
-      <c r="AC30" s="1"/>
+      <c r="AC30" s="1">
+        <v>0</v>
+      </c>
       <c r="AD30" s="1">
         <v>0</v>
       </c>
@@ -2680,7 +2747,9 @@
       <c r="A31" t="s">
         <v>54</v>
       </c>
-      <c r="AC31" s="1"/>
+      <c r="AC31" s="1">
+        <v>0</v>
+      </c>
       <c r="AD31" s="1">
         <v>0</v>
       </c>
@@ -2715,7 +2784,9 @@
       </c>
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
-      <c r="AC32" s="1"/>
+      <c r="AC32" s="1">
+        <v>0</v>
+      </c>
       <c r="AD32" s="1">
         <v>0</v>
       </c>
@@ -2748,6 +2819,9 @@
       <c r="A33" t="s">
         <v>53</v>
       </c>
+      <c r="AC33">
+        <v>843</v>
+      </c>
       <c r="AD33">
         <v>712</v>
       </c>
@@ -2782,7 +2856,9 @@
       </c>
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
-      <c r="AC34" s="1"/>
+      <c r="AC34" s="1">
+        <v>0</v>
+      </c>
       <c r="AD34" s="1">
         <v>0</v>
       </c>
@@ -2817,7 +2893,9 @@
       </c>
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
-      <c r="AC35" s="1"/>
+      <c r="AC35" s="1">
+        <v>0</v>
+      </c>
       <c r="AD35" s="1">
         <v>0</v>
       </c>
@@ -2852,7 +2930,9 @@
       </c>
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
-      <c r="AC36" s="1"/>
+      <c r="AC36" s="1">
+        <v>0</v>
+      </c>
       <c r="AD36" s="1">
         <v>0</v>
       </c>
@@ -2887,7 +2967,9 @@
       </c>
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
-      <c r="AC37" s="1"/>
+      <c r="AC37" s="1">
+        <v>0</v>
+      </c>
       <c r="AD37" s="1">
         <v>0</v>
       </c>
@@ -2922,7 +3004,9 @@
       </c>
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
-      <c r="AC38" s="1"/>
+      <c r="AC38" s="1">
+        <v>0</v>
+      </c>
       <c r="AD38" s="1">
         <v>0</v>
       </c>
@@ -2958,7 +3042,9 @@
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
-      <c r="AC39" s="1"/>
+      <c r="AC39" s="1">
+        <v>0</v>
+      </c>
       <c r="AD39" s="1">
         <v>0</v>
       </c>
@@ -2994,7 +3080,9 @@
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
-      <c r="AC40" s="1"/>
+      <c r="AC40" s="1">
+        <v>0</v>
+      </c>
       <c r="AD40" s="1">
         <v>0</v>
       </c>
@@ -3027,6 +3115,9 @@
       <c r="A41" t="s">
         <v>64</v>
       </c>
+      <c r="AC41">
+        <v>909</v>
+      </c>
       <c r="AD41">
         <v>502</v>
       </c>
@@ -3062,7 +3153,9 @@
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
-      <c r="AC42" s="1"/>
+      <c r="AC42" s="1">
+        <v>0</v>
+      </c>
       <c r="AD42" s="1">
         <v>0</v>
       </c>
@@ -3098,7 +3191,9 @@
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
-      <c r="AC43" s="1"/>
+      <c r="AC43" s="1">
+        <v>0</v>
+      </c>
       <c r="AD43" s="1">
         <v>0</v>
       </c>
@@ -3135,7 +3230,9 @@
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
-      <c r="AC44" s="1"/>
+      <c r="AC44" s="1">
+        <v>0</v>
+      </c>
       <c r="AD44" s="1">
         <v>0</v>
       </c>
@@ -3167,6 +3264,9 @@
     <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>68</v>
+      </c>
+      <c r="AC45">
+        <v>868</v>
       </c>
       <c r="AD45">
         <v>685</v>
@@ -3204,7 +3304,9 @@
       <c r="Z46" s="1"/>
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
-      <c r="AC46" s="1"/>
+      <c r="AC46" s="1">
+        <v>0</v>
+      </c>
       <c r="AD46" s="1">
         <v>0</v>
       </c>
@@ -3241,7 +3343,9 @@
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
-      <c r="AC47" s="1"/>
+      <c r="AC47" s="1">
+        <v>0</v>
+      </c>
       <c r="AD47" s="1">
         <v>0</v>
       </c>
@@ -3278,7 +3382,9 @@
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
-      <c r="AC48" s="1"/>
+      <c r="AC48" s="1">
+        <v>0</v>
+      </c>
       <c r="AD48" s="1">
         <v>0</v>
       </c>
@@ -3315,7 +3421,9 @@
       <c r="Z49" s="1"/>
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
-      <c r="AC49" s="1"/>
+      <c r="AC49" s="1">
+        <v>0</v>
+      </c>
       <c r="AD49" s="1">
         <v>0</v>
       </c>
@@ -3352,7 +3460,9 @@
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
-      <c r="AC50" s="1"/>
+      <c r="AC50" s="1">
+        <v>0</v>
+      </c>
       <c r="AD50" s="1">
         <v>0</v>
       </c>
@@ -3390,7 +3500,9 @@
       <c r="Z51" s="1"/>
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
-      <c r="AC51" s="1"/>
+      <c r="AC51" s="1">
+        <v>0</v>
+      </c>
       <c r="AD51" s="1">
         <v>0</v>
       </c>
@@ -3428,7 +3540,9 @@
       <c r="Z52" s="1"/>
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
-      <c r="AC52" s="1"/>
+      <c r="AC52" s="1">
+        <v>0</v>
+      </c>
       <c r="AD52" s="1">
         <v>0</v>
       </c>
@@ -3466,7 +3580,9 @@
       <c r="Z53" s="1"/>
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
-      <c r="AC53" s="1"/>
+      <c r="AC53" s="1">
+        <v>0</v>
+      </c>
       <c r="AD53" s="1">
         <v>0</v>
       </c>
@@ -3504,7 +3620,9 @@
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
-      <c r="AC54" s="1"/>
+      <c r="AC54" s="1">
+        <v>0</v>
+      </c>
       <c r="AD54" s="1">
         <v>0</v>
       </c>
@@ -3542,7 +3660,9 @@
       <c r="Z55" s="1"/>
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
-      <c r="AC55" s="1"/>
+      <c r="AC55" s="1">
+        <v>0</v>
+      </c>
       <c r="AD55" s="1">
         <v>0</v>
       </c>
@@ -3580,7 +3700,9 @@
       <c r="Z56" s="1"/>
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
-      <c r="AC56" s="1"/>
+      <c r="AC56" s="1">
+        <v>0</v>
+      </c>
       <c r="AD56" s="1">
         <v>0</v>
       </c>
@@ -3619,7 +3741,9 @@
       <c r="Z57" s="1"/>
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
-      <c r="AC57" s="1"/>
+      <c r="AC57" s="1">
+        <v>0</v>
+      </c>
       <c r="AD57" s="1">
         <v>0</v>
       </c>
@@ -3658,7 +3782,9 @@
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
-      <c r="AC58" s="1"/>
+      <c r="AC58" s="1">
+        <v>0</v>
+      </c>
       <c r="AD58" s="1">
         <v>0</v>
       </c>
@@ -3697,7 +3823,9 @@
       <c r="Z59" s="1"/>
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
-      <c r="AC59" s="1"/>
+      <c r="AC59" s="1">
+        <v>0</v>
+      </c>
       <c r="AD59" s="1">
         <v>0</v>
       </c>
@@ -3736,7 +3864,9 @@
       <c r="Z60" s="1"/>
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
-      <c r="AC60" s="1"/>
+      <c r="AC60" s="1">
+        <v>0</v>
+      </c>
       <c r="AD60" s="1">
         <v>0</v>
       </c>
@@ -3775,7 +3905,9 @@
       <c r="Z61" s="1"/>
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
-      <c r="AC61" s="1"/>
+      <c r="AC61" s="1">
+        <v>0</v>
+      </c>
       <c r="AD61" s="1">
         <v>0</v>
       </c>
@@ -3815,7 +3947,9 @@
       <c r="Z62" s="1"/>
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
-      <c r="AC62" s="1"/>
+      <c r="AC62" s="1">
+        <v>0</v>
+      </c>
       <c r="AD62" s="1">
         <v>0</v>
       </c>
@@ -3855,7 +3989,9 @@
       <c r="Z63" s="1"/>
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
-      <c r="AC63" s="1"/>
+      <c r="AC63" s="1">
+        <v>0</v>
+      </c>
       <c r="AD63" s="1">
         <v>0</v>
       </c>
@@ -3896,7 +4032,9 @@
       <c r="Z64" s="1"/>
       <c r="AA64" s="1"/>
       <c r="AB64" s="1"/>
-      <c r="AC64" s="1"/>
+      <c r="AC64" s="1">
+        <v>0</v>
+      </c>
       <c r="AD64" s="1">
         <v>0</v>
       </c>
@@ -3937,7 +4075,9 @@
       <c r="Z65" s="1"/>
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
-      <c r="AC65" s="1"/>
+      <c r="AC65" s="1">
+        <v>0</v>
+      </c>
       <c r="AD65" s="1">
         <v>0</v>
       </c>
@@ -3978,7 +4118,9 @@
       <c r="Z66" s="1"/>
       <c r="AA66" s="1"/>
       <c r="AB66" s="1"/>
-      <c r="AC66" s="1"/>
+      <c r="AC66" s="1">
+        <v>0</v>
+      </c>
       <c r="AD66" s="1">
         <v>0</v>
       </c>
@@ -4019,7 +4161,9 @@
       <c r="Z67" s="1"/>
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
-      <c r="AC67" s="1"/>
+      <c r="AC67" s="1">
+        <v>0</v>
+      </c>
       <c r="AD67" s="1">
         <v>0</v>
       </c>
@@ -4120,7 +4264,9 @@
       <c r="Z69" s="1"/>
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
-      <c r="AC69" s="1"/>
+      <c r="AC69" s="1">
+        <v>0</v>
+      </c>
       <c r="AD69" s="1">
         <v>0</v>
       </c>
@@ -4162,7 +4308,9 @@
       <c r="Z70" s="1"/>
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
-      <c r="AC70" s="1"/>
+      <c r="AC70" s="1">
+        <v>0</v>
+      </c>
       <c r="AD70" s="1">
         <v>0</v>
       </c>
@@ -4204,7 +4352,9 @@
       <c r="Z71" s="1"/>
       <c r="AA71" s="1"/>
       <c r="AB71" s="1"/>
-      <c r="AC71" s="1"/>
+      <c r="AC71" s="1">
+        <v>0</v>
+      </c>
       <c r="AD71" s="1">
         <v>0</v>
       </c>
@@ -4246,7 +4396,9 @@
       <c r="Z72" s="1"/>
       <c r="AA72" s="1"/>
       <c r="AB72" s="1"/>
-      <c r="AC72" s="1"/>
+      <c r="AC72" s="1">
+        <v>0</v>
+      </c>
       <c r="AD72" s="1">
         <v>0</v>
       </c>
@@ -4288,7 +4440,9 @@
       <c r="Z73" s="1"/>
       <c r="AA73" s="1"/>
       <c r="AB73" s="1"/>
-      <c r="AC73" s="1"/>
+      <c r="AC73" s="1">
+        <v>0</v>
+      </c>
       <c r="AD73" s="1">
         <v>0</v>
       </c>
@@ -4331,7 +4485,9 @@
       <c r="Z74" s="1"/>
       <c r="AA74" s="1"/>
       <c r="AB74" s="1"/>
-      <c r="AC74" s="1"/>
+      <c r="AC74" s="1">
+        <v>0</v>
+      </c>
       <c r="AD74" s="1">
         <v>0</v>
       </c>
@@ -4374,7 +4530,9 @@
       <c r="Z75" s="1"/>
       <c r="AA75" s="1"/>
       <c r="AB75" s="1"/>
-      <c r="AC75" s="1"/>
+      <c r="AC75" s="1">
+        <v>0</v>
+      </c>
       <c r="AD75" s="1">
         <v>0</v>
       </c>
@@ -4417,7 +4575,9 @@
       <c r="Z76" s="1"/>
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
-      <c r="AC76" s="1"/>
+      <c r="AC76" s="1">
+        <v>0</v>
+      </c>
       <c r="AD76" s="1">
         <v>0</v>
       </c>
@@ -4460,7 +4620,9 @@
       <c r="Z77" s="1"/>
       <c r="AA77" s="1"/>
       <c r="AB77" s="1"/>
-      <c r="AC77" s="1"/>
+      <c r="AC77" s="1">
+        <v>0</v>
+      </c>
       <c r="AD77" s="1">
         <v>0</v>
       </c>
@@ -4503,7 +4665,9 @@
       <c r="Z78" s="1"/>
       <c r="AA78" s="1"/>
       <c r="AB78" s="1"/>
-      <c r="AC78" s="1"/>
+      <c r="AC78" s="1">
+        <v>0</v>
+      </c>
       <c r="AD78" s="1">
         <v>0</v>
       </c>
@@ -4547,7 +4711,9 @@
       <c r="Z79" s="1"/>
       <c r="AA79" s="1"/>
       <c r="AB79" s="1"/>
-      <c r="AC79" s="1"/>
+      <c r="AC79" s="1">
+        <v>0</v>
+      </c>
       <c r="AD79" s="1">
         <v>0</v>
       </c>
@@ -4591,7 +4757,9 @@
       <c r="Z80" s="1"/>
       <c r="AA80" s="1"/>
       <c r="AB80" s="1"/>
-      <c r="AC80" s="1"/>
+      <c r="AC80" s="1">
+        <v>0</v>
+      </c>
       <c r="AD80" s="1">
         <v>0</v>
       </c>
@@ -4636,7 +4804,9 @@
       <c r="Z81" s="1"/>
       <c r="AA81" s="1"/>
       <c r="AB81" s="1"/>
-      <c r="AC81" s="1"/>
+      <c r="AC81" s="1">
+        <v>0</v>
+      </c>
       <c r="AD81" s="1">
         <v>0</v>
       </c>
@@ -4681,7 +4851,9 @@
       <c r="Z82" s="1"/>
       <c r="AA82" s="1"/>
       <c r="AB82" s="1"/>
-      <c r="AC82" s="1"/>
+      <c r="AC82" s="1">
+        <v>0</v>
+      </c>
       <c r="AD82" s="1">
         <v>0</v>
       </c>
@@ -4726,7 +4898,9 @@
       <c r="Z83" s="1"/>
       <c r="AA83" s="1"/>
       <c r="AB83" s="1"/>
-      <c r="AC83" s="1"/>
+      <c r="AC83" s="1">
+        <v>0</v>
+      </c>
       <c r="AD83" s="1">
         <v>0</v>
       </c>
@@ -4771,7 +4945,9 @@
       <c r="Z84" s="1"/>
       <c r="AA84" s="1"/>
       <c r="AB84" s="1"/>
-      <c r="AC84" s="1"/>
+      <c r="AC84" s="1">
+        <v>0</v>
+      </c>
       <c r="AD84" s="1">
         <v>0</v>
       </c>
@@ -4816,7 +4992,9 @@
       <c r="Z85" s="1"/>
       <c r="AA85" s="1"/>
       <c r="AB85" s="1"/>
-      <c r="AC85" s="1"/>
+      <c r="AC85" s="1">
+        <v>0</v>
+      </c>
       <c r="AD85" s="1">
         <v>0</v>
       </c>
@@ -4862,7 +5040,9 @@
       <c r="Z86" s="1"/>
       <c r="AA86" s="1"/>
       <c r="AB86" s="1"/>
-      <c r="AC86" s="1"/>
+      <c r="AC86" s="1">
+        <v>0</v>
+      </c>
       <c r="AD86" s="1">
         <v>0</v>
       </c>
@@ -4908,7 +5088,9 @@
       <c r="Z87" s="1"/>
       <c r="AA87" s="1"/>
       <c r="AB87" s="1"/>
-      <c r="AC87" s="1"/>
+      <c r="AC87" s="1">
+        <v>0</v>
+      </c>
       <c r="AD87" s="1">
         <v>0</v>
       </c>
@@ -4954,7 +5136,9 @@
       <c r="Z88" s="1"/>
       <c r="AA88" s="1"/>
       <c r="AB88" s="1"/>
-      <c r="AC88" s="1"/>
+      <c r="AC88" s="1">
+        <v>0</v>
+      </c>
       <c r="AD88" s="1">
         <v>0</v>
       </c>
@@ -5000,7 +5184,9 @@
       <c r="Z89" s="1"/>
       <c r="AA89" s="1"/>
       <c r="AB89" s="1"/>
-      <c r="AC89" s="1"/>
+      <c r="AC89" s="1">
+        <v>0</v>
+      </c>
       <c r="AD89" s="1">
         <v>0</v>
       </c>
@@ -5047,7 +5233,9 @@
       <c r="Z90" s="1"/>
       <c r="AA90" s="1"/>
       <c r="AB90" s="1"/>
-      <c r="AC90" s="1"/>
+      <c r="AC90" s="1">
+        <v>0</v>
+      </c>
       <c r="AD90" s="1">
         <v>0</v>
       </c>
@@ -5094,7 +5282,9 @@
       <c r="Z91" s="1"/>
       <c r="AA91" s="1"/>
       <c r="AB91" s="1"/>
-      <c r="AC91" s="1"/>
+      <c r="AC91" s="1">
+        <v>0</v>
+      </c>
       <c r="AD91" s="1">
         <v>0</v>
       </c>
@@ -5141,7 +5331,9 @@
       <c r="Z92" s="1"/>
       <c r="AA92" s="1"/>
       <c r="AB92" s="1"/>
-      <c r="AC92" s="1"/>
+      <c r="AC92" s="1">
+        <v>0</v>
+      </c>
       <c r="AD92" s="1">
         <v>0</v>
       </c>
@@ -5188,7 +5380,9 @@
       <c r="Z93" s="1"/>
       <c r="AA93" s="1"/>
       <c r="AB93" s="1"/>
-      <c r="AC93" s="1"/>
+      <c r="AC93" s="1">
+        <v>0</v>
+      </c>
       <c r="AD93" s="1">
         <v>0</v>
       </c>
@@ -5235,7 +5429,9 @@
       <c r="Z94" s="1"/>
       <c r="AA94" s="1"/>
       <c r="AB94" s="1"/>
-      <c r="AC94" s="1"/>
+      <c r="AC94" s="1">
+        <v>0</v>
+      </c>
       <c r="AD94" s="1">
         <v>0</v>
       </c>
@@ -5283,7 +5479,9 @@
       <c r="Z95" s="1"/>
       <c r="AA95" s="1"/>
       <c r="AB95" s="1"/>
-      <c r="AC95" s="1"/>
+      <c r="AC95" s="1">
+        <v>0</v>
+      </c>
       <c r="AD95" s="1">
         <v>0</v>
       </c>
@@ -5331,7 +5529,9 @@
       <c r="Z96" s="1"/>
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
-      <c r="AC96" s="1"/>
+      <c r="AC96" s="1">
+        <v>0</v>
+      </c>
       <c r="AD96" s="1">
         <v>0</v>
       </c>
@@ -5379,7 +5579,9 @@
       <c r="Z97" s="1"/>
       <c r="AA97" s="1"/>
       <c r="AB97" s="1"/>
-      <c r="AC97" s="1"/>
+      <c r="AC97" s="1">
+        <v>0</v>
+      </c>
       <c r="AD97" s="1">
         <v>0</v>
       </c>
@@ -5427,7 +5629,9 @@
       <c r="Z98" s="1"/>
       <c r="AA98" s="1"/>
       <c r="AB98" s="1"/>
-      <c r="AC98" s="1"/>
+      <c r="AC98" s="1">
+        <v>0</v>
+      </c>
       <c r="AD98" s="1">
         <v>0</v>
       </c>
@@ -5475,7 +5679,9 @@
       <c r="Z99" s="1"/>
       <c r="AA99" s="1"/>
       <c r="AB99" s="1"/>
-      <c r="AC99" s="1"/>
+      <c r="AC99" s="1">
+        <v>0</v>
+      </c>
       <c r="AD99" s="1">
         <v>0</v>
       </c>
@@ -5524,7 +5730,9 @@
       <c r="Z100" s="1"/>
       <c r="AA100" s="1"/>
       <c r="AB100" s="1"/>
-      <c r="AC100" s="1"/>
+      <c r="AC100" s="1">
+        <v>0</v>
+      </c>
       <c r="AD100" s="1">
         <v>0</v>
       </c>
@@ -5573,7 +5781,9 @@
       <c r="Z101" s="1"/>
       <c r="AA101" s="1"/>
       <c r="AB101" s="1"/>
-      <c r="AC101" s="1"/>
+      <c r="AC101" s="1">
+        <v>0</v>
+      </c>
       <c r="AD101" s="1">
         <v>0</v>
       </c>
@@ -5622,7 +5832,9 @@
       <c r="Z102" s="1"/>
       <c r="AA102" s="1"/>
       <c r="AB102" s="1"/>
-      <c r="AC102" s="1"/>
+      <c r="AC102" s="1">
+        <v>0</v>
+      </c>
       <c r="AD102" s="1">
         <v>0</v>
       </c>
@@ -5671,7 +5883,9 @@
       <c r="Z103" s="1"/>
       <c r="AA103" s="1"/>
       <c r="AB103" s="1"/>
-      <c r="AC103" s="1"/>
+      <c r="AC103" s="1">
+        <v>0</v>
+      </c>
       <c r="AD103" s="1">
         <v>0</v>
       </c>
@@ -5721,7 +5935,9 @@
       <c r="Z104" s="1"/>
       <c r="AA104" s="1"/>
       <c r="AB104" s="1"/>
-      <c r="AC104" s="1"/>
+      <c r="AC104" s="1">
+        <v>0</v>
+      </c>
       <c r="AD104" s="1">
         <v>0</v>
       </c>
@@ -5771,7 +5987,9 @@
       <c r="Z105" s="1"/>
       <c r="AA105" s="1"/>
       <c r="AB105" s="1"/>
-      <c r="AC105" s="1"/>
+      <c r="AC105" s="1">
+        <v>0</v>
+      </c>
       <c r="AD105" s="1">
         <v>0</v>
       </c>
@@ -5822,7 +6040,9 @@
       <c r="Z106" s="1"/>
       <c r="AA106" s="1"/>
       <c r="AB106" s="1"/>
-      <c r="AC106" s="1"/>
+      <c r="AC106" s="1">
+        <v>0</v>
+      </c>
       <c r="AD106" s="1">
         <v>0</v>
       </c>
@@ -5873,7 +6093,9 @@
       <c r="Z107" s="1"/>
       <c r="AA107" s="1"/>
       <c r="AB107" s="1"/>
-      <c r="AC107" s="1"/>
+      <c r="AC107" s="1">
+        <v>0</v>
+      </c>
       <c r="AD107" s="1">
         <v>0</v>
       </c>
@@ -5924,7 +6146,9 @@
       <c r="Z108" s="1"/>
       <c r="AA108" s="1"/>
       <c r="AB108" s="1"/>
-      <c r="AC108" s="1"/>
+      <c r="AC108" s="1">
+        <v>0</v>
+      </c>
       <c r="AD108" s="1">
         <v>0</v>
       </c>
@@ -5976,7 +6200,9 @@
       <c r="Z109" s="1"/>
       <c r="AA109" s="1"/>
       <c r="AB109" s="1"/>
-      <c r="AC109" s="1"/>
+      <c r="AC109" s="1">
+        <v>0</v>
+      </c>
       <c r="AD109" s="1">
         <v>0</v>
       </c>
@@ -6028,7 +6254,9 @@
       <c r="Z110" s="1"/>
       <c r="AA110" s="1"/>
       <c r="AB110" s="1"/>
-      <c r="AC110" s="1"/>
+      <c r="AC110" s="1">
+        <v>0</v>
+      </c>
       <c r="AD110" s="1">
         <v>0</v>
       </c>
@@ -6080,7 +6308,9 @@
       <c r="Z111" s="1"/>
       <c r="AA111" s="1"/>
       <c r="AB111" s="1"/>
-      <c r="AC111" s="1"/>
+      <c r="AC111" s="1">
+        <v>0</v>
+      </c>
       <c r="AD111" s="1">
         <v>0</v>
       </c>
@@ -6133,7 +6363,9 @@
       <c r="Z112" s="1"/>
       <c r="AA112" s="1"/>
       <c r="AB112" s="1"/>
-      <c r="AC112" s="1"/>
+      <c r="AC112" s="1">
+        <v>0</v>
+      </c>
       <c r="AD112" s="1">
         <v>0</v>
       </c>
@@ -6186,7 +6418,9 @@
       <c r="Z113" s="1"/>
       <c r="AA113" s="1"/>
       <c r="AB113" s="1"/>
-      <c r="AC113" s="1"/>
+      <c r="AC113" s="1">
+        <v>0</v>
+      </c>
       <c r="AD113" s="1">
         <v>0</v>
       </c>
@@ -6239,7 +6473,9 @@
       <c r="Z114" s="1"/>
       <c r="AA114" s="1"/>
       <c r="AB114" s="1"/>
-      <c r="AC114" s="1"/>
+      <c r="AC114" s="1">
+        <v>0</v>
+      </c>
       <c r="AD114" s="1">
         <v>0</v>
       </c>
@@ -6293,7 +6529,9 @@
       <c r="Z115" s="1"/>
       <c r="AA115" s="1"/>
       <c r="AB115" s="1"/>
-      <c r="AC115" s="1"/>
+      <c r="AC115" s="1">
+        <v>0</v>
+      </c>
       <c r="AD115" s="1">
         <v>0</v>
       </c>
@@ -6347,7 +6585,9 @@
       <c r="Z116" s="1"/>
       <c r="AA116" s="1"/>
       <c r="AB116" s="1"/>
-      <c r="AC116" s="1"/>
+      <c r="AC116" s="1">
+        <v>0</v>
+      </c>
       <c r="AD116" s="1">
         <v>0</v>
       </c>
@@ -6402,7 +6642,9 @@
       <c r="Z117" s="1"/>
       <c r="AA117" s="1"/>
       <c r="AB117" s="1"/>
-      <c r="AC117" s="1"/>
+      <c r="AC117" s="1">
+        <v>0</v>
+      </c>
       <c r="AD117" s="1">
         <v>0</v>
       </c>
@@ -6457,7 +6699,9 @@
       <c r="Z118" s="1"/>
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
-      <c r="AC118" s="1"/>
+      <c r="AC118" s="1">
+        <v>0</v>
+      </c>
       <c r="AD118" s="1">
         <v>0</v>
       </c>
@@ -6512,7 +6756,9 @@
       <c r="Z119" s="1"/>
       <c r="AA119" s="1"/>
       <c r="AB119" s="1"/>
-      <c r="AC119" s="1"/>
+      <c r="AC119" s="1">
+        <v>0</v>
+      </c>
       <c r="AD119" s="1">
         <v>0</v>
       </c>
@@ -6568,7 +6814,9 @@
       <c r="Z120" s="1"/>
       <c r="AA120" s="1"/>
       <c r="AB120" s="1"/>
-      <c r="AC120" s="1"/>
+      <c r="AC120" s="1">
+        <v>0</v>
+      </c>
       <c r="AD120" s="1">
         <v>0</v>
       </c>
@@ -6624,7 +6872,9 @@
       <c r="Z121" s="1"/>
       <c r="AA121" s="1"/>
       <c r="AB121" s="1"/>
-      <c r="AC121" s="1"/>
+      <c r="AC121" s="1">
+        <v>0</v>
+      </c>
       <c r="AD121" s="1">
         <v>0</v>
       </c>
@@ -6680,7 +6930,9 @@
       <c r="Z122" s="1"/>
       <c r="AA122" s="1"/>
       <c r="AB122" s="1"/>
-      <c r="AC122" s="1"/>
+      <c r="AC122" s="1">
+        <v>0</v>
+      </c>
       <c r="AD122" s="1">
         <v>0</v>
       </c>
@@ -6737,7 +6989,9 @@
       <c r="Z123" s="1"/>
       <c r="AA123" s="1"/>
       <c r="AB123" s="1"/>
-      <c r="AC123" s="1"/>
+      <c r="AC123" s="1">
+        <v>0</v>
+      </c>
       <c r="AD123" s="1">
         <v>0</v>
       </c>
@@ -6794,7 +7048,9 @@
       <c r="Z124" s="1"/>
       <c r="AA124" s="1"/>
       <c r="AB124" s="1"/>
-      <c r="AC124" s="1"/>
+      <c r="AC124" s="1">
+        <v>0</v>
+      </c>
       <c r="AD124" s="1">
         <v>0</v>
       </c>
@@ -6851,7 +7107,9 @@
       <c r="Z125" s="1"/>
       <c r="AA125" s="1"/>
       <c r="AB125" s="1"/>
-      <c r="AC125" s="1"/>
+      <c r="AC125" s="1">
+        <v>0</v>
+      </c>
       <c r="AD125" s="1">
         <v>0</v>
       </c>
@@ -6909,7 +7167,9 @@
       <c r="Z126" s="1"/>
       <c r="AA126" s="1"/>
       <c r="AB126" s="1"/>
-      <c r="AC126" s="1"/>
+      <c r="AC126" s="1">
+        <v>0</v>
+      </c>
       <c r="AD126" s="1">
         <v>0</v>
       </c>
@@ -7942,9 +8202,1109 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC06B72-571E-40C4-AD69-3294909EA05A}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>SUM(C2:S2)</f>
+        <v>921</v>
+      </c>
+      <c r="C2">
+        <v>58</v>
+      </c>
+      <c r="D2">
+        <v>71</v>
+      </c>
+      <c r="E2">
+        <v>62</v>
+      </c>
+      <c r="F2">
+        <v>60</v>
+      </c>
+      <c r="G2">
+        <v>65</v>
+      </c>
+      <c r="H2">
+        <v>67</v>
+      </c>
+      <c r="I2">
+        <v>55</v>
+      </c>
+      <c r="J2">
+        <v>69</v>
+      </c>
+      <c r="K2">
+        <v>58</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>77</v>
+      </c>
+      <c r="O2">
+        <v>44</v>
+      </c>
+      <c r="P2">
+        <v>53</v>
+      </c>
+      <c r="Q2">
+        <v>73</v>
+      </c>
+      <c r="R2">
+        <v>53</v>
+      </c>
+      <c r="S2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B18" si="0">SUM(C3:S3)</f>
+        <v>939</v>
+      </c>
+      <c r="C3">
+        <v>58</v>
+      </c>
+      <c r="D3">
+        <v>27</v>
+      </c>
+      <c r="E3">
+        <v>62</v>
+      </c>
+      <c r="F3">
+        <v>35</v>
+      </c>
+      <c r="G3">
+        <v>65</v>
+      </c>
+      <c r="H3">
+        <v>66</v>
+      </c>
+      <c r="I3">
+        <v>78</v>
+      </c>
+      <c r="J3">
+        <v>69</v>
+      </c>
+      <c r="K3">
+        <v>72</v>
+      </c>
+      <c r="L3">
+        <v>71</v>
+      </c>
+      <c r="M3">
+        <v>45</v>
+      </c>
+      <c r="N3">
+        <v>77</v>
+      </c>
+      <c r="O3">
+        <v>32</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>73</v>
+      </c>
+      <c r="R3">
+        <v>53</v>
+      </c>
+      <c r="S3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>973</v>
+      </c>
+      <c r="C4">
+        <v>11</v>
+      </c>
+      <c r="D4">
+        <v>71</v>
+      </c>
+      <c r="E4">
+        <v>62</v>
+      </c>
+      <c r="F4">
+        <v>60</v>
+      </c>
+      <c r="G4">
+        <v>65</v>
+      </c>
+      <c r="H4">
+        <v>66</v>
+      </c>
+      <c r="I4">
+        <v>78</v>
+      </c>
+      <c r="J4">
+        <v>69</v>
+      </c>
+      <c r="K4">
+        <v>72</v>
+      </c>
+      <c r="L4">
+        <v>71</v>
+      </c>
+      <c r="M4">
+        <v>45</v>
+      </c>
+      <c r="N4">
+        <v>77</v>
+      </c>
+      <c r="O4">
+        <v>44</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>73</v>
+      </c>
+      <c r="R4">
+        <v>53</v>
+      </c>
+      <c r="S4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>913</v>
+      </c>
+      <c r="C5">
+        <v>58</v>
+      </c>
+      <c r="D5">
+        <v>70</v>
+      </c>
+      <c r="E5">
+        <v>45</v>
+      </c>
+      <c r="F5">
+        <v>60</v>
+      </c>
+      <c r="G5">
+        <v>65</v>
+      </c>
+      <c r="H5">
+        <v>29</v>
+      </c>
+      <c r="I5">
+        <v>37</v>
+      </c>
+      <c r="J5">
+        <v>64</v>
+      </c>
+      <c r="K5">
+        <v>72</v>
+      </c>
+      <c r="L5">
+        <v>52</v>
+      </c>
+      <c r="M5">
+        <v>45</v>
+      </c>
+      <c r="N5">
+        <v>77</v>
+      </c>
+      <c r="O5">
+        <v>44</v>
+      </c>
+      <c r="P5">
+        <v>53</v>
+      </c>
+      <c r="Q5">
+        <v>58</v>
+      </c>
+      <c r="R5">
+        <v>41</v>
+      </c>
+      <c r="S5">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>625</v>
+      </c>
+      <c r="C6">
+        <v>56</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>51</v>
+      </c>
+      <c r="G6">
+        <v>62</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>77</v>
+      </c>
+      <c r="J6">
+        <v>34</v>
+      </c>
+      <c r="K6">
+        <v>71</v>
+      </c>
+      <c r="L6">
+        <v>41</v>
+      </c>
+      <c r="M6">
+        <v>40</v>
+      </c>
+      <c r="N6">
+        <v>22</v>
+      </c>
+      <c r="O6">
+        <v>12</v>
+      </c>
+      <c r="P6">
+        <v>15</v>
+      </c>
+      <c r="Q6">
+        <v>72</v>
+      </c>
+      <c r="R6">
+        <v>41</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="C7">
+        <v>58</v>
+      </c>
+      <c r="D7">
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>61</v>
+      </c>
+      <c r="F7">
+        <v>56</v>
+      </c>
+      <c r="G7">
+        <v>21</v>
+      </c>
+      <c r="H7">
+        <v>46</v>
+      </c>
+      <c r="I7">
+        <v>77</v>
+      </c>
+      <c r="J7">
+        <v>64</v>
+      </c>
+      <c r="K7">
+        <v>72</v>
+      </c>
+      <c r="L7">
+        <v>70</v>
+      </c>
+      <c r="M7">
+        <v>45</v>
+      </c>
+      <c r="N7">
+        <v>75</v>
+      </c>
+      <c r="O7">
+        <v>44</v>
+      </c>
+      <c r="P7">
+        <v>14</v>
+      </c>
+      <c r="Q7">
+        <v>73</v>
+      </c>
+      <c r="R7">
+        <v>52</v>
+      </c>
+      <c r="S7">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>789</v>
+      </c>
+      <c r="C8">
+        <v>46</v>
+      </c>
+      <c r="D8">
+        <v>70</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>60</v>
+      </c>
+      <c r="G8">
+        <v>61</v>
+      </c>
+      <c r="H8">
+        <v>62</v>
+      </c>
+      <c r="I8">
+        <v>16</v>
+      </c>
+      <c r="J8">
+        <v>68</v>
+      </c>
+      <c r="K8">
+        <v>71</v>
+      </c>
+      <c r="L8">
+        <v>70</v>
+      </c>
+      <c r="M8">
+        <v>45</v>
+      </c>
+      <c r="N8">
+        <v>76</v>
+      </c>
+      <c r="O8">
+        <v>44</v>
+      </c>
+      <c r="P8">
+        <v>10</v>
+      </c>
+      <c r="Q8">
+        <v>14</v>
+      </c>
+      <c r="R8">
+        <v>53</v>
+      </c>
+      <c r="S8">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>709</v>
+      </c>
+      <c r="C9">
+        <v>35</v>
+      </c>
+      <c r="D9">
+        <v>71</v>
+      </c>
+      <c r="E9">
+        <v>58</v>
+      </c>
+      <c r="F9">
+        <v>60</v>
+      </c>
+      <c r="G9">
+        <v>64</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>36</v>
+      </c>
+      <c r="J9">
+        <v>69</v>
+      </c>
+      <c r="K9">
+        <v>72</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>45</v>
+      </c>
+      <c r="N9">
+        <v>76</v>
+      </c>
+      <c r="O9">
+        <v>4</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>12</v>
+      </c>
+      <c r="R9">
+        <v>52</v>
+      </c>
+      <c r="S9">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>839</v>
+      </c>
+      <c r="C10">
+        <v>58</v>
+      </c>
+      <c r="D10">
+        <v>71</v>
+      </c>
+      <c r="E10">
+        <v>61</v>
+      </c>
+      <c r="F10">
+        <v>59</v>
+      </c>
+      <c r="G10">
+        <v>64</v>
+      </c>
+      <c r="H10">
+        <v>66</v>
+      </c>
+      <c r="I10">
+        <v>78</v>
+      </c>
+      <c r="J10">
+        <v>69</v>
+      </c>
+      <c r="K10">
+        <v>71</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>31</v>
+      </c>
+      <c r="O10">
+        <v>8</v>
+      </c>
+      <c r="P10">
+        <v>52</v>
+      </c>
+      <c r="Q10">
+        <v>44</v>
+      </c>
+      <c r="R10">
+        <v>52</v>
+      </c>
+      <c r="S10">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>70</v>
+      </c>
+      <c r="E11">
+        <v>49</v>
+      </c>
+      <c r="F11">
+        <v>26</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>66</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>48</v>
+      </c>
+      <c r="K11">
+        <v>45</v>
+      </c>
+      <c r="L11">
+        <v>32</v>
+      </c>
+      <c r="M11">
+        <v>45</v>
+      </c>
+      <c r="N11">
+        <v>73</v>
+      </c>
+      <c r="O11">
+        <v>42</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>45</v>
+      </c>
+      <c r="R11">
+        <v>52</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>799</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <v>20</v>
+      </c>
+      <c r="E12">
+        <v>61</v>
+      </c>
+      <c r="F12">
+        <v>59</v>
+      </c>
+      <c r="G12">
+        <v>64</v>
+      </c>
+      <c r="H12">
+        <v>29</v>
+      </c>
+      <c r="I12">
+        <v>78</v>
+      </c>
+      <c r="J12">
+        <v>66</v>
+      </c>
+      <c r="K12">
+        <v>70</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>45</v>
+      </c>
+      <c r="N12">
+        <v>76</v>
+      </c>
+      <c r="O12">
+        <v>44</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>73</v>
+      </c>
+      <c r="R12">
+        <v>52</v>
+      </c>
+      <c r="S12">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>681</v>
+      </c>
+      <c r="C13">
+        <v>39</v>
+      </c>
+      <c r="D13">
+        <v>71</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>54</v>
+      </c>
+      <c r="G13">
+        <v>65</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
+        <v>70</v>
+      </c>
+      <c r="J13">
+        <v>32</v>
+      </c>
+      <c r="K13">
+        <v>71</v>
+      </c>
+      <c r="L13">
+        <v>4</v>
+      </c>
+      <c r="M13">
+        <v>39</v>
+      </c>
+      <c r="N13">
+        <v>77</v>
+      </c>
+      <c r="O13">
+        <v>44</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>73</v>
+      </c>
+      <c r="R13">
+        <v>29</v>
+      </c>
+      <c r="S13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>814</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>61</v>
+      </c>
+      <c r="F14">
+        <v>59</v>
+      </c>
+      <c r="G14">
+        <v>64</v>
+      </c>
+      <c r="H14">
+        <v>27</v>
+      </c>
+      <c r="I14">
+        <v>78</v>
+      </c>
+      <c r="J14">
+        <v>42</v>
+      </c>
+      <c r="K14">
+        <v>71</v>
+      </c>
+      <c r="L14">
+        <v>70</v>
+      </c>
+      <c r="M14">
+        <v>45</v>
+      </c>
+      <c r="N14">
+        <v>76</v>
+      </c>
+      <c r="O14">
+        <v>44</v>
+      </c>
+      <c r="P14">
+        <v>52</v>
+      </c>
+      <c r="Q14">
+        <v>18</v>
+      </c>
+      <c r="R14">
+        <v>52</v>
+      </c>
+      <c r="S14">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>695</v>
+      </c>
+      <c r="C15">
+        <v>16</v>
+      </c>
+      <c r="D15">
+        <v>70</v>
+      </c>
+      <c r="E15">
+        <v>59</v>
+      </c>
+      <c r="F15">
+        <v>20</v>
+      </c>
+      <c r="G15">
+        <v>25</v>
+      </c>
+      <c r="H15">
+        <v>29</v>
+      </c>
+      <c r="I15">
+        <v>60</v>
+      </c>
+      <c r="J15">
+        <v>69</v>
+      </c>
+      <c r="K15">
+        <v>25</v>
+      </c>
+      <c r="L15">
+        <v>14</v>
+      </c>
+      <c r="M15">
+        <v>39</v>
+      </c>
+      <c r="N15">
+        <v>75</v>
+      </c>
+      <c r="O15">
+        <v>43</v>
+      </c>
+      <c r="P15">
+        <v>53</v>
+      </c>
+      <c r="Q15">
+        <v>34</v>
+      </c>
+      <c r="R15">
+        <v>9</v>
+      </c>
+      <c r="S15">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>843</v>
+      </c>
+      <c r="C16">
+        <v>57</v>
+      </c>
+      <c r="D16">
+        <v>31</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+      <c r="F16">
+        <v>59</v>
+      </c>
+      <c r="G16">
+        <v>63</v>
+      </c>
+      <c r="H16">
+        <v>47</v>
+      </c>
+      <c r="I16">
+        <v>21</v>
+      </c>
+      <c r="J16">
+        <v>64</v>
+      </c>
+      <c r="K16">
+        <v>70</v>
+      </c>
+      <c r="L16">
+        <v>70</v>
+      </c>
+      <c r="M16">
+        <v>33</v>
+      </c>
+      <c r="N16">
+        <v>74</v>
+      </c>
+      <c r="O16">
+        <v>43</v>
+      </c>
+      <c r="P16">
+        <v>52</v>
+      </c>
+      <c r="Q16">
+        <v>72</v>
+      </c>
+      <c r="R16">
+        <v>46</v>
+      </c>
+      <c r="S16">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>909</v>
+      </c>
+      <c r="C17">
+        <v>58</v>
+      </c>
+      <c r="D17">
+        <v>69</v>
+      </c>
+      <c r="E17">
+        <v>61</v>
+      </c>
+      <c r="F17">
+        <v>36</v>
+      </c>
+      <c r="G17">
+        <v>64</v>
+      </c>
+      <c r="H17">
+        <v>51</v>
+      </c>
+      <c r="I17">
+        <v>48</v>
+      </c>
+      <c r="J17">
+        <v>69</v>
+      </c>
+      <c r="K17">
+        <v>16</v>
+      </c>
+      <c r="L17">
+        <v>58</v>
+      </c>
+      <c r="M17">
+        <v>37</v>
+      </c>
+      <c r="N17">
+        <v>75</v>
+      </c>
+      <c r="O17">
+        <v>43</v>
+      </c>
+      <c r="P17">
+        <v>53</v>
+      </c>
+      <c r="Q17">
+        <v>73</v>
+      </c>
+      <c r="R17">
+        <v>52</v>
+      </c>
+      <c r="S17">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>868</v>
+      </c>
+      <c r="C18">
+        <v>58</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+      <c r="E18">
+        <v>61</v>
+      </c>
+      <c r="F18">
+        <v>59</v>
+      </c>
+      <c r="G18">
+        <v>64</v>
+      </c>
+      <c r="H18">
+        <v>61</v>
+      </c>
+      <c r="I18">
+        <v>18</v>
+      </c>
+      <c r="J18">
+        <v>69</v>
+      </c>
+      <c r="K18">
+        <v>34</v>
+      </c>
+      <c r="L18">
+        <v>70</v>
+      </c>
+      <c r="M18">
+        <v>31</v>
+      </c>
+      <c r="N18">
+        <v>76</v>
+      </c>
+      <c r="O18">
+        <v>43</v>
+      </c>
+      <c r="P18">
+        <v>53</v>
+      </c>
+      <c r="Q18">
+        <v>72</v>
+      </c>
+      <c r="R18">
+        <v>37</v>
+      </c>
+      <c r="S18">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Data_Files/Laps_Completed.xlsx
+++ b/Data_Files/Laps_Completed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB049C59-6027-4A44-A9EB-E0B7BED583B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28CB748A-3AD2-4152-B414-FE62FAE3C1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="1500" windowWidth="16410" windowHeight="14145" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28695" yWindow="1500" windowWidth="16410" windowHeight="14145" firstSheet="4" activeTab="11" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Laps_Completed" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="153">
   <si>
     <t>Driver</t>
   </si>
@@ -1084,13 +1084,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>145</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1133,13 +1133,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>145</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1601,7 +1601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCEEE69D-1A9D-4213-BBC7-B7EBD153B749}">
-  <dimension ref="A1:AL126"/>
+  <dimension ref="A1:AL124"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
@@ -2745,13 +2745,13 @@
     </row>
     <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="1">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c r="AC31">
+        <v>843</v>
+      </c>
+      <c r="AD31">
+        <v>712</v>
       </c>
       <c r="AE31" s="1">
         <v>0</v>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
@@ -2817,13 +2817,15 @@
     </row>
     <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>53</v>
-      </c>
-      <c r="AC33">
-        <v>843</v>
-      </c>
-      <c r="AD33">
-        <v>712</v>
+        <v>58</v>
+      </c>
+      <c r="AA33" s="1"/>
+      <c r="AB33" s="1"/>
+      <c r="AC33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="1">
+        <v>0</v>
       </c>
       <c r="AE33" s="1">
         <v>0</v>
@@ -2852,7 +2854,7 @@
     </row>
     <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
@@ -2889,7 +2891,7 @@
     </row>
     <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
@@ -2926,7 +2928,7 @@
     </row>
     <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
@@ -2963,8 +2965,9 @@
     </row>
     <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>60</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1">
@@ -3000,8 +3003,9 @@
     </row>
     <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>61</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1">
@@ -3037,16 +3041,13 @@
     </row>
     <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z39" s="1"/>
-      <c r="AA39" s="1"/>
-      <c r="AB39" s="1"/>
-      <c r="AC39" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD39" s="1">
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="AC39">
+        <v>909</v>
+      </c>
+      <c r="AD39">
+        <v>502</v>
       </c>
       <c r="AE39" s="1">
         <v>0</v>
@@ -3075,7 +3076,7 @@
     </row>
     <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
@@ -3113,13 +3114,16 @@
     </row>
     <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC41">
-        <v>909</v>
-      </c>
-      <c r="AD41">
-        <v>502</v>
+        <v>66</v>
+      </c>
+      <c r="Z41" s="1"/>
+      <c r="AA41" s="1"/>
+      <c r="AB41" s="1"/>
+      <c r="AC41" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="1">
+        <v>0</v>
       </c>
       <c r="AE41" s="1">
         <v>0</v>
@@ -3148,8 +3152,9 @@
     </row>
     <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>65</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
@@ -3186,22 +3191,19 @@
     </row>
     <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z43" s="1"/>
-      <c r="AA43" s="1"/>
-      <c r="AB43" s="1"/>
-      <c r="AC43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF43" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="AC43">
+        <v>868</v>
+      </c>
+      <c r="AD43">
+        <v>685</v>
+      </c>
+      <c r="AE43">
+        <v>848</v>
+      </c>
+      <c r="AF43">
+        <v>154</v>
       </c>
       <c r="AG43" s="1">
         <v>0</v>
@@ -3224,7 +3226,7 @@
     </row>
     <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
@@ -3263,19 +3265,23 @@
     </row>
     <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC45">
-        <v>868</v>
-      </c>
-      <c r="AD45">
-        <v>685</v>
-      </c>
-      <c r="AE45">
-        <v>848</v>
-      </c>
-      <c r="AF45">
-        <v>154</v>
+        <v>70</v>
+      </c>
+      <c r="Y45" s="1"/>
+      <c r="Z45" s="1"/>
+      <c r="AA45" s="1"/>
+      <c r="AB45" s="1"/>
+      <c r="AC45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="1">
+        <v>0</v>
       </c>
       <c r="AG45" s="1">
         <v>0</v>
@@ -3298,7 +3304,7 @@
     </row>
     <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
@@ -3337,7 +3343,7 @@
     </row>
     <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
@@ -3376,7 +3382,7 @@
     </row>
     <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
@@ -3415,8 +3421,9 @@
     </row>
     <row r="49" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>72</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1"/>
@@ -3454,8 +3461,9 @@
     </row>
     <row r="50" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>73</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
@@ -3493,7 +3501,7 @@
     </row>
     <row r="51" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
@@ -3533,7 +3541,7 @@
     </row>
     <row r="52" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
@@ -3573,7 +3581,7 @@
     </row>
     <row r="53" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
@@ -3613,7 +3621,7 @@
     </row>
     <row r="54" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
@@ -3653,8 +3661,9 @@
     </row>
     <row r="55" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>78</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="W55" s="1"/>
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
@@ -3693,8 +3702,9 @@
     </row>
     <row r="56" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>79</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="W56" s="1"/>
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
@@ -3733,7 +3743,7 @@
     </row>
     <row r="57" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="W57" s="1"/>
       <c r="X57" s="1"/>
@@ -3774,7 +3784,7 @@
     </row>
     <row r="58" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W58" s="1"/>
       <c r="X58" s="1"/>
@@ -3815,7 +3825,7 @@
     </row>
     <row r="59" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="W59" s="1"/>
       <c r="X59" s="1"/>
@@ -3856,8 +3866,9 @@
     </row>
     <row r="60" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>83</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="V60" s="1"/>
       <c r="W60" s="1"/>
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
@@ -3897,8 +3908,9 @@
     </row>
     <row r="61" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>84</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="V61" s="1"/>
       <c r="W61" s="1"/>
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
@@ -3938,8 +3950,9 @@
     </row>
     <row r="62" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>86</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="U62" s="1"/>
       <c r="V62" s="1"/>
       <c r="W62" s="1"/>
       <c r="X62" s="1"/>
@@ -3980,8 +3993,9 @@
     </row>
     <row r="63" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>87</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="U63" s="1"/>
       <c r="V63" s="1"/>
       <c r="W63" s="1"/>
       <c r="X63" s="1"/>
@@ -4022,7 +4036,7 @@
     </row>
     <row r="64" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
@@ -4065,7 +4079,7 @@
     </row>
     <row r="65" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="U65" s="1"/>
       <c r="V65" s="1"/>
@@ -4108,21 +4122,37 @@
     </row>
     <row r="66" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>90</v>
-      </c>
-      <c r="U66" s="1"/>
-      <c r="V66" s="1"/>
-      <c r="W66" s="1"/>
-      <c r="X66" s="1"/>
-      <c r="Y66" s="1"/>
-      <c r="Z66" s="1"/>
-      <c r="AA66" s="1"/>
-      <c r="AB66" s="1"/>
+        <v>92</v>
+      </c>
+      <c r="U66" s="1">
+        <v>0</v>
+      </c>
+      <c r="V66" s="1">
+        <v>0</v>
+      </c>
+      <c r="W66" s="1">
+        <v>0</v>
+      </c>
+      <c r="X66" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB66" s="1">
+        <v>0</v>
+      </c>
       <c r="AC66" s="1">
         <v>0</v>
       </c>
-      <c r="AD66" s="1">
-        <v>0</v>
+      <c r="AD66">
+        <v>659</v>
       </c>
       <c r="AE66" s="1">
         <v>0</v>
@@ -4130,17 +4160,17 @@
       <c r="AF66" s="1">
         <v>0</v>
       </c>
-      <c r="AG66" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH66" s="1">
-        <v>0</v>
+      <c r="AG66">
+        <v>283</v>
+      </c>
+      <c r="AH66">
+        <v>807</v>
       </c>
       <c r="AI66" s="1">
         <v>0</v>
       </c>
-      <c r="AJ66" s="1">
-        <v>0</v>
+      <c r="AJ66">
+        <v>516</v>
       </c>
       <c r="AK66" s="1">
         <v>0</v>
@@ -4151,8 +4181,9 @@
     </row>
     <row r="67" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>91</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="T67" s="1"/>
       <c r="U67" s="1"/>
       <c r="V67" s="1"/>
       <c r="W67" s="1"/>
@@ -4194,37 +4225,22 @@
     </row>
     <row r="68" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>92</v>
-      </c>
-      <c r="U68" s="1">
-        <v>0</v>
-      </c>
-      <c r="V68" s="1">
-        <v>0</v>
-      </c>
-      <c r="W68" s="1">
-        <v>0</v>
-      </c>
-      <c r="X68" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y68" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z68" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA68" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB68" s="1">
-        <v>0</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="T68" s="1"/>
+      <c r="U68" s="1"/>
+      <c r="V68" s="1"/>
+      <c r="W68" s="1"/>
+      <c r="X68" s="1"/>
+      <c r="Y68" s="1"/>
+      <c r="Z68" s="1"/>
+      <c r="AA68" s="1"/>
+      <c r="AB68" s="1"/>
       <c r="AC68" s="1">
         <v>0</v>
       </c>
-      <c r="AD68">
-        <v>659</v>
+      <c r="AD68" s="1">
+        <v>0</v>
       </c>
       <c r="AE68" s="1">
         <v>0</v>
@@ -4232,17 +4248,17 @@
       <c r="AF68" s="1">
         <v>0</v>
       </c>
-      <c r="AG68">
-        <v>283</v>
-      </c>
-      <c r="AH68">
-        <v>807</v>
+      <c r="AG68" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="1">
+        <v>0</v>
       </c>
       <c r="AI68" s="1">
         <v>0</v>
       </c>
-      <c r="AJ68">
-        <v>516</v>
+      <c r="AJ68" s="1">
+        <v>0</v>
       </c>
       <c r="AK68" s="1">
         <v>0</v>
@@ -4253,7 +4269,7 @@
     </row>
     <row r="69" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="T69" s="1"/>
       <c r="U69" s="1"/>
@@ -4297,7 +4313,7 @@
     </row>
     <row r="70" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="T70" s="1"/>
       <c r="U70" s="1"/>
@@ -4341,7 +4357,7 @@
     </row>
     <row r="71" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="T71" s="1"/>
       <c r="U71" s="1"/>
@@ -4385,8 +4401,9 @@
     </row>
     <row r="72" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>96</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="S72" s="1"/>
       <c r="T72" s="1"/>
       <c r="U72" s="1"/>
       <c r="V72" s="1"/>
@@ -4429,8 +4446,9 @@
     </row>
     <row r="73" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>97</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="S73" s="1"/>
       <c r="T73" s="1"/>
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
@@ -4473,7 +4491,7 @@
     </row>
     <row r="74" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S74" s="1"/>
       <c r="T74" s="1"/>
@@ -4518,7 +4536,7 @@
     </row>
     <row r="75" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="S75" s="1"/>
       <c r="T75" s="1"/>
@@ -4563,7 +4581,7 @@
     </row>
     <row r="76" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S76" s="1"/>
       <c r="T76" s="1"/>
@@ -4608,8 +4626,9 @@
     </row>
     <row r="77" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>101</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="R77" s="1"/>
       <c r="S77" s="1"/>
       <c r="T77" s="1"/>
       <c r="U77" s="1"/>
@@ -4653,8 +4672,9 @@
     </row>
     <row r="78" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>102</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="R78" s="1"/>
       <c r="S78" s="1"/>
       <c r="T78" s="1"/>
       <c r="U78" s="1"/>
@@ -4698,8 +4718,9 @@
     </row>
     <row r="79" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>103</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
       <c r="T79" s="1"/>
@@ -4744,8 +4765,9 @@
     </row>
     <row r="80" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>104</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
       <c r="T80" s="1"/>
@@ -4790,7 +4812,7 @@
     </row>
     <row r="81" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
@@ -4837,7 +4859,7 @@
     </row>
     <row r="82" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
@@ -4884,7 +4906,7 @@
     </row>
     <row r="83" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
@@ -4931,8 +4953,9 @@
     </row>
     <row r="84" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>108</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="P84" s="1"/>
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
@@ -4978,8 +5001,9 @@
     </row>
     <row r="85" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>109</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="P85" s="1"/>
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
@@ -5025,7 +5049,7 @@
     </row>
     <row r="86" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="P86" s="1"/>
       <c r="Q86" s="1"/>
@@ -5073,7 +5097,7 @@
     </row>
     <row r="87" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="P87" s="1"/>
       <c r="Q87" s="1"/>
@@ -5121,8 +5145,9 @@
     </row>
     <row r="88" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>112</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O88" s="1"/>
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
@@ -5169,8 +5194,9 @@
     </row>
     <row r="89" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>113</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="O89" s="1"/>
       <c r="P89" s="1"/>
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
@@ -5217,7 +5243,7 @@
     </row>
     <row r="90" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
@@ -5266,7 +5292,7 @@
     </row>
     <row r="91" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O91" s="1"/>
       <c r="P91" s="1"/>
@@ -5315,7 +5341,7 @@
     </row>
     <row r="92" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="O92" s="1"/>
       <c r="P92" s="1"/>
@@ -5364,8 +5390,9 @@
     </row>
     <row r="93" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>117</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N93" s="1"/>
       <c r="O93" s="1"/>
       <c r="P93" s="1"/>
       <c r="Q93" s="1"/>
@@ -5413,8 +5440,9 @@
     </row>
     <row r="94" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>118</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N94" s="1"/>
       <c r="O94" s="1"/>
       <c r="P94" s="1"/>
       <c r="Q94" s="1"/>
@@ -5462,7 +5490,7 @@
     </row>
     <row r="95" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
@@ -5512,7 +5540,7 @@
     </row>
     <row r="96" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
@@ -5562,7 +5590,7 @@
     </row>
     <row r="97" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
@@ -5612,8 +5640,9 @@
     </row>
     <row r="98" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>122</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="M98" s="1"/>
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
       <c r="P98" s="1"/>
@@ -5662,8 +5691,9 @@
     </row>
     <row r="99" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>123</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="M99" s="1"/>
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
       <c r="P99" s="1"/>
@@ -5712,7 +5742,7 @@
     </row>
     <row r="100" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
@@ -5763,7 +5793,7 @@
     </row>
     <row r="101" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
@@ -5814,8 +5844,9 @@
     </row>
     <row r="102" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>126</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="L102" s="1"/>
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
       <c r="O102" s="1"/>
@@ -5865,8 +5896,9 @@
     </row>
     <row r="103" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>127</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="L103" s="1"/>
       <c r="M103" s="1"/>
       <c r="N103" s="1"/>
       <c r="O103" s="1"/>
@@ -5916,8 +5948,9 @@
     </row>
     <row r="104" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>128</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="K104" s="1"/>
       <c r="L104" s="1"/>
       <c r="M104" s="1"/>
       <c r="N104" s="1"/>
@@ -5968,8 +6001,9 @@
     </row>
     <row r="105" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>129</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="1"/>
       <c r="N105" s="1"/>
@@ -6020,7 +6054,7 @@
     </row>
     <row r="106" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -6073,8 +6107,9 @@
     </row>
     <row r="107" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>131</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="J107" s="1"/>
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
       <c r="M107" s="1"/>
@@ -6126,8 +6161,9 @@
     </row>
     <row r="108" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>132</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="J108" s="1"/>
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="1"/>
@@ -6179,7 +6215,7 @@
     </row>
     <row r="109" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J109" s="1"/>
       <c r="K109" s="1"/>
@@ -6233,8 +6269,9 @@
     </row>
     <row r="110" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>134</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="I110" s="1"/>
       <c r="J110" s="1"/>
       <c r="K110" s="1"/>
       <c r="L110" s="1"/>
@@ -6287,8 +6324,9 @@
     </row>
     <row r="111" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>135</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="I111" s="1"/>
       <c r="J111" s="1"/>
       <c r="K111" s="1"/>
       <c r="L111" s="1"/>
@@ -6341,7 +6379,7 @@
     </row>
     <row r="112" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
@@ -6396,8 +6434,9 @@
     </row>
     <row r="113" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>137</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="H113" s="1"/>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
       <c r="K113" s="1"/>
@@ -6451,8 +6490,9 @@
     </row>
     <row r="114" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>138</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="H114" s="1"/>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
       <c r="K114" s="1"/>
@@ -6506,8 +6546,9 @@
     </row>
     <row r="115" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>139</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="G115" s="1"/>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
@@ -6562,8 +6603,9 @@
     </row>
     <row r="116" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>140</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="G116" s="1"/>
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
@@ -6618,7 +6660,7 @@
     </row>
     <row r="117" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
@@ -6675,8 +6717,9 @@
     </row>
     <row r="118" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>142</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="F118" s="1"/>
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
@@ -6732,8 +6775,9 @@
     </row>
     <row r="119" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>143</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="F119" s="1"/>
       <c r="G119" s="1"/>
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
@@ -6789,7 +6833,7 @@
     </row>
     <row r="120" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
@@ -6847,8 +6891,9 @@
     </row>
     <row r="121" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>145</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="E121" s="1"/>
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
@@ -6905,8 +6950,9 @@
     </row>
     <row r="122" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>146</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="E122" s="1"/>
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
@@ -6963,7 +7009,7 @@
     </row>
     <row r="123" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
@@ -7022,8 +7068,9 @@
     </row>
     <row r="124" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>148</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="D124" s="1"/>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
@@ -7076,125 +7123,6 @@
         <v>0</v>
       </c>
       <c r="AL124" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>149</v>
-      </c>
-      <c r="E125" s="1"/>
-      <c r="F125" s="1"/>
-      <c r="G125" s="1"/>
-      <c r="H125" s="1"/>
-      <c r="I125" s="1"/>
-      <c r="J125" s="1"/>
-      <c r="K125" s="1"/>
-      <c r="L125" s="1"/>
-      <c r="M125" s="1"/>
-      <c r="N125" s="1"/>
-      <c r="O125" s="1"/>
-      <c r="P125" s="1"/>
-      <c r="Q125" s="1"/>
-      <c r="R125" s="1"/>
-      <c r="S125" s="1"/>
-      <c r="T125" s="1"/>
-      <c r="U125" s="1"/>
-      <c r="V125" s="1"/>
-      <c r="W125" s="1"/>
-      <c r="X125" s="1"/>
-      <c r="Y125" s="1"/>
-      <c r="Z125" s="1"/>
-      <c r="AA125" s="1"/>
-      <c r="AB125" s="1"/>
-      <c r="AC125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK125" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL125" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>150</v>
-      </c>
-      <c r="D126" s="1"/>
-      <c r="E126" s="1"/>
-      <c r="F126" s="1"/>
-      <c r="G126" s="1"/>
-      <c r="H126" s="1"/>
-      <c r="I126" s="1"/>
-      <c r="J126" s="1"/>
-      <c r="K126" s="1"/>
-      <c r="L126" s="1"/>
-      <c r="M126" s="1"/>
-      <c r="N126" s="1"/>
-      <c r="O126" s="1"/>
-      <c r="P126" s="1"/>
-      <c r="Q126" s="1"/>
-      <c r="R126" s="1"/>
-      <c r="S126" s="1"/>
-      <c r="T126" s="1"/>
-      <c r="U126" s="1"/>
-      <c r="V126" s="1"/>
-      <c r="W126" s="1"/>
-      <c r="X126" s="1"/>
-      <c r="Y126" s="1"/>
-      <c r="Z126" s="1"/>
-      <c r="AA126" s="1"/>
-      <c r="AB126" s="1"/>
-      <c r="AC126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK126" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL126" s="1">
         <v>0</v>
       </c>
     </row>
@@ -9311,9 +9239,928 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5463DBD5-1047-4E7D-B3B5-A719C2F7680D}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>SUM(C2:S2)</f>
+        <v>690</v>
+      </c>
+      <c r="C2">
+        <v>58</v>
+      </c>
+      <c r="D2">
+        <v>55</v>
+      </c>
+      <c r="E2">
+        <v>71</v>
+      </c>
+      <c r="F2">
+        <v>24</v>
+      </c>
+      <c r="G2">
+        <v>65</v>
+      </c>
+      <c r="H2">
+        <v>71</v>
+      </c>
+      <c r="I2">
+        <v>78</v>
+      </c>
+      <c r="J2">
+        <v>69</v>
+      </c>
+      <c r="K2">
+        <v>67</v>
+      </c>
+      <c r="L2">
+        <v>72</v>
+      </c>
+      <c r="M2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B21" si="0">SUM(C3:S3)</f>
+        <v>593</v>
+      </c>
+      <c r="C3">
+        <v>58</v>
+      </c>
+      <c r="D3">
+        <v>55</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>62</v>
+      </c>
+      <c r="G3">
+        <v>49</v>
+      </c>
+      <c r="H3">
+        <v>71</v>
+      </c>
+      <c r="I3">
+        <v>78</v>
+      </c>
+      <c r="J3">
+        <v>19</v>
+      </c>
+      <c r="K3">
+        <v>67</v>
+      </c>
+      <c r="L3">
+        <v>72</v>
+      </c>
+      <c r="M3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>604</v>
+      </c>
+      <c r="C4">
+        <v>58</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>55</v>
+      </c>
+      <c r="F4">
+        <v>17</v>
+      </c>
+      <c r="G4">
+        <v>65</v>
+      </c>
+      <c r="H4">
+        <v>71</v>
+      </c>
+      <c r="I4">
+        <v>73</v>
+      </c>
+      <c r="J4">
+        <v>69</v>
+      </c>
+      <c r="K4">
+        <v>66</v>
+      </c>
+      <c r="L4">
+        <v>71</v>
+      </c>
+      <c r="M4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>654</v>
+      </c>
+      <c r="C5">
+        <v>58</v>
+      </c>
+      <c r="D5">
+        <v>55</v>
+      </c>
+      <c r="E5">
+        <v>71</v>
+      </c>
+      <c r="F5">
+        <v>62</v>
+      </c>
+      <c r="G5">
+        <v>65</v>
+      </c>
+      <c r="H5">
+        <v>71</v>
+      </c>
+      <c r="I5">
+        <v>77</v>
+      </c>
+      <c r="J5">
+        <v>54</v>
+      </c>
+      <c r="K5">
+        <v>67</v>
+      </c>
+      <c r="L5">
+        <v>72</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>435</v>
+      </c>
+      <c r="C6">
+        <v>40</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>38</v>
+      </c>
+      <c r="F6">
+        <v>48</v>
+      </c>
+      <c r="G6">
+        <v>65</v>
+      </c>
+      <c r="H6">
+        <v>41</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>19</v>
+      </c>
+      <c r="K6">
+        <v>67</v>
+      </c>
+      <c r="L6">
+        <v>52</v>
+      </c>
+      <c r="M6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>506</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>55</v>
+      </c>
+      <c r="E7">
+        <v>54</v>
+      </c>
+      <c r="F7">
+        <v>62</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>57</v>
+      </c>
+      <c r="J7">
+        <v>69</v>
+      </c>
+      <c r="K7">
+        <v>67</v>
+      </c>
+      <c r="L7">
+        <v>72</v>
+      </c>
+      <c r="M7">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>511</v>
+      </c>
+      <c r="C8">
+        <v>58</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>70</v>
+      </c>
+      <c r="F8">
+        <v>61</v>
+      </c>
+      <c r="G8">
+        <v>65</v>
+      </c>
+      <c r="H8">
+        <v>69</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>54</v>
+      </c>
+      <c r="L8">
+        <v>71</v>
+      </c>
+      <c r="M8">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>484</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>70</v>
+      </c>
+      <c r="F9">
+        <v>30</v>
+      </c>
+      <c r="G9">
+        <v>65</v>
+      </c>
+      <c r="H9">
+        <v>70</v>
+      </c>
+      <c r="I9">
+        <v>78</v>
+      </c>
+      <c r="J9">
+        <v>34</v>
+      </c>
+      <c r="K9">
+        <v>66</v>
+      </c>
+      <c r="L9">
+        <v>5</v>
+      </c>
+      <c r="M9">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>471</v>
+      </c>
+      <c r="C10">
+        <v>58</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>70</v>
+      </c>
+      <c r="F10">
+        <v>61</v>
+      </c>
+      <c r="G10">
+        <v>65</v>
+      </c>
+      <c r="H10">
+        <v>71</v>
+      </c>
+      <c r="I10">
+        <v>13</v>
+      </c>
+      <c r="J10">
+        <v>38</v>
+      </c>
+      <c r="K10">
+        <v>23</v>
+      </c>
+      <c r="L10">
+        <v>71</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>636</v>
+      </c>
+      <c r="C11">
+        <v>52</v>
+      </c>
+      <c r="D11">
+        <v>53</v>
+      </c>
+      <c r="E11">
+        <v>64</v>
+      </c>
+      <c r="F11">
+        <v>60</v>
+      </c>
+      <c r="G11">
+        <v>62</v>
+      </c>
+      <c r="H11">
+        <v>60</v>
+      </c>
+      <c r="I11">
+        <v>77</v>
+      </c>
+      <c r="J11">
+        <v>17</v>
+      </c>
+      <c r="K11">
+        <v>65</v>
+      </c>
+      <c r="L11">
+        <v>68</v>
+      </c>
+      <c r="M11">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>512</v>
+      </c>
+      <c r="C12">
+        <v>38</v>
+      </c>
+      <c r="D12">
+        <v>54</v>
+      </c>
+      <c r="E12">
+        <v>70</v>
+      </c>
+      <c r="F12">
+        <v>62</v>
+      </c>
+      <c r="G12">
+        <v>65</v>
+      </c>
+      <c r="H12">
+        <v>14</v>
+      </c>
+      <c r="I12">
+        <v>30</v>
+      </c>
+      <c r="J12">
+        <v>63</v>
+      </c>
+      <c r="K12">
+        <v>44</v>
+      </c>
+      <c r="L12">
+        <v>72</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>491</v>
+      </c>
+      <c r="C13">
+        <v>55</v>
+      </c>
+      <c r="D13">
+        <v>31</v>
+      </c>
+      <c r="E13">
+        <v>70</v>
+      </c>
+      <c r="F13">
+        <v>31</v>
+      </c>
+      <c r="G13">
+        <v>63</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13">
+        <v>43</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>66</v>
+      </c>
+      <c r="L13">
+        <v>71</v>
+      </c>
+      <c r="M13">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>333</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14">
+        <v>48</v>
+      </c>
+      <c r="I14">
+        <v>18</v>
+      </c>
+      <c r="J14">
+        <v>68</v>
+      </c>
+      <c r="K14">
+        <v>66</v>
+      </c>
+      <c r="L14">
+        <v>70</v>
+      </c>
+      <c r="M14">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>531</v>
+      </c>
+      <c r="C15">
+        <v>57</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15">
+        <v>52</v>
+      </c>
+      <c r="F15">
+        <v>42</v>
+      </c>
+      <c r="G15">
+        <v>48</v>
+      </c>
+      <c r="H15">
+        <v>70</v>
+      </c>
+      <c r="I15">
+        <v>78</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>67</v>
+      </c>
+      <c r="L15">
+        <v>54</v>
+      </c>
+      <c r="M15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>309</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17">
+        <v>15</v>
+      </c>
+      <c r="F17">
+        <v>60</v>
+      </c>
+      <c r="G17">
+        <v>8</v>
+      </c>
+      <c r="H17">
+        <v>17</v>
+      </c>
+      <c r="I17">
+        <v>76</v>
+      </c>
+      <c r="J17">
+        <v>24</v>
+      </c>
+      <c r="K17">
+        <v>29</v>
+      </c>
+      <c r="L17">
+        <v>17</v>
+      </c>
+      <c r="M17">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>469</v>
+      </c>
+      <c r="C18">
+        <v>58</v>
+      </c>
+      <c r="D18">
+        <v>55</v>
+      </c>
+      <c r="E18">
+        <v>63</v>
+      </c>
+      <c r="F18">
+        <v>61</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>49</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>48</v>
+      </c>
+      <c r="L18">
+        <v>71</v>
+      </c>
+      <c r="M18">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>487</v>
+      </c>
+      <c r="C19">
+        <v>56</v>
+      </c>
+      <c r="D19">
+        <v>52</v>
+      </c>
+      <c r="E19">
+        <v>25</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+      <c r="G19">
+        <v>63</v>
+      </c>
+      <c r="H19">
+        <v>38</v>
+      </c>
+      <c r="I19">
+        <v>54</v>
+      </c>
+      <c r="J19">
+        <v>7</v>
+      </c>
+      <c r="K19">
+        <v>65</v>
+      </c>
+      <c r="L19">
+        <v>65</v>
+      </c>
+      <c r="M19">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>616</v>
+      </c>
+      <c r="C20">
+        <v>57</v>
+      </c>
+      <c r="D20">
+        <v>55</v>
+      </c>
+      <c r="E20">
+        <v>37</v>
+      </c>
+      <c r="F20">
+        <v>6</v>
+      </c>
+      <c r="G20">
+        <v>63</v>
+      </c>
+      <c r="H20">
+        <v>70</v>
+      </c>
+      <c r="I20">
+        <v>77</v>
+      </c>
+      <c r="J20">
+        <v>65</v>
+      </c>
+      <c r="K20">
+        <v>58</v>
+      </c>
+      <c r="L20">
+        <v>70</v>
+      </c>
+      <c r="M20">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>68</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Data_Files/Laps_Completed.xlsx
+++ b/Data_Files/Laps_Completed.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owens\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28CB748A-3AD2-4152-B414-FE62FAE3C1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BC2DC1-E0CE-4AA6-A45D-27760ADB3F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="1500" windowWidth="16410" windowHeight="14145" firstSheet="4" activeTab="11" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="4" activeTab="11" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Laps_Completed" sheetId="1" r:id="rId1"/>
@@ -1602,13 +1602,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCEEE69D-1A9D-4213-BBC7-B7EBD153B749}">
   <dimension ref="A1:AL124"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>85</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>55</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -2525,7 +2525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>44</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>45</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>48</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>53</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>57</v>
       </c>
@@ -2815,7 +2815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>58</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>59</v>
       </c>
@@ -2889,7 +2889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>61</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>62</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>63</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>64</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>65</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>66</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>67</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>68</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>69</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>70</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>71</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>73</v>
       </c>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>75</v>
       </c>
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>76</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>78</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>79</v>
       </c>
@@ -3659,7 +3659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>80</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>81</v>
       </c>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>82</v>
       </c>
@@ -3782,7 +3782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>83</v>
       </c>
@@ -3823,7 +3823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>84</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>86</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>87</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>88</v>
       </c>
@@ -3991,7 +3991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>89</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>90</v>
       </c>
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>91</v>
       </c>
@@ -4120,7 +4120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>92</v>
       </c>
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>93</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>94</v>
       </c>
@@ -4267,7 +4267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>95</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>96</v>
       </c>
@@ -4355,7 +4355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>97</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>98</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>99</v>
       </c>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>100</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>101</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>102</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>103</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>104</v>
       </c>
@@ -4716,7 +4716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>105</v>
       </c>
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>106</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>107</v>
       </c>
@@ -4857,7 +4857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>108</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>109</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>110</v>
       </c>
@@ -4999,7 +4999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>111</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>112</v>
       </c>
@@ -5095,7 +5095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>113</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>114</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>115</v>
       </c>
@@ -5241,7 +5241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>116</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>117</v>
       </c>
@@ -5339,7 +5339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>118</v>
       </c>
@@ -5388,7 +5388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>119</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>120</v>
       </c>
@@ -5488,7 +5488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>121</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>122</v>
       </c>
@@ -5588,7 +5588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>123</v>
       </c>
@@ -5638,7 +5638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>124</v>
       </c>
@@ -5689,7 +5689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>125</v>
       </c>
@@ -5740,7 +5740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>126</v>
       </c>
@@ -5791,7 +5791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>127</v>
       </c>
@@ -5842,7 +5842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>128</v>
       </c>
@@ -5894,7 +5894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>129</v>
       </c>
@@ -5946,7 +5946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>130</v>
       </c>
@@ -5999,7 +5999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>131</v>
       </c>
@@ -6052,7 +6052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>132</v>
       </c>
@@ -6105,7 +6105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>133</v>
       </c>
@@ -6159,7 +6159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>134</v>
       </c>
@@ -6213,7 +6213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>135</v>
       </c>
@@ -6267,7 +6267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>136</v>
       </c>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>137</v>
       </c>
@@ -6377,7 +6377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>138</v>
       </c>
@@ -6432,7 +6432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>139</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>140</v>
       </c>
@@ -6544,7 +6544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>141</v>
       </c>
@@ -6601,7 +6601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>142</v>
       </c>
@@ -6658,7 +6658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>143</v>
       </c>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>144</v>
       </c>
@@ -6773,7 +6773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>145</v>
       </c>
@@ -6831,7 +6831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>146</v>
       </c>
@@ -6889,7 +6889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>147</v>
       </c>
@@ -6948,7 +6948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>148</v>
       </c>
@@ -7007,7 +7007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>149</v>
       </c>
@@ -7066,7 +7066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>150</v>
       </c>
@@ -7135,26 +7135,26 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A672F957-1D62-4580-B7C6-2DFEBD8C86A9}">
   <dimension ref="A1:R17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7210,7 +7210,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -7267,7 +7267,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7324,7 +7324,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -7381,7 +7381,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -7438,7 +7438,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -7495,7 +7495,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -7552,7 +7552,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -7609,7 +7609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -7666,7 +7666,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -7723,7 +7723,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>55</v>
       </c>
@@ -7837,7 +7837,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -7894,7 +7894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>53</v>
       </c>
@@ -7951,7 +7951,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>64</v>
       </c>
@@ -8008,7 +8008,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -8065,7 +8065,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -8131,29 +8131,29 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC06B72-571E-40C4-AD69-3294909EA05A}">
   <dimension ref="A1:S18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8212,7 +8212,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -8272,7 +8272,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -8332,7 +8332,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -8392,7 +8392,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -8452,7 +8452,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -8512,7 +8512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -8572,7 +8572,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -8692,7 +8692,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -8752,7 +8752,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -8812,7 +8812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -8872,7 +8872,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -8932,7 +8932,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -8992,7 +8992,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -9052,7 +9052,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>53</v>
       </c>
@@ -9112,7 +9112,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>64</v>
       </c>
@@ -9172,7 +9172,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -9240,28 +9240,28 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5463DBD5-1047-4E7D-B3B5-A719C2F7680D}">
   <dimension ref="A1:S21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9320,13 +9320,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
         <f>SUM(C2:S2)</f>
-        <v>690</v>
+        <v>713</v>
       </c>
       <c r="C2">
         <v>58</v>
@@ -9361,14 +9361,17 @@
       <c r="M2">
         <v>60</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
         <f t="shared" ref="B3:B21" si="0">SUM(C3:S3)</f>
-        <v>593</v>
+        <v>638</v>
       </c>
       <c r="C3">
         <v>58</v>
@@ -9403,14 +9406,17 @@
       <c r="M3">
         <v>60</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
         <f t="shared" si="0"/>
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="C4">
         <v>58</v>
@@ -9445,14 +9451,17 @@
       <c r="M4">
         <v>59</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
-        <v>654</v>
+        <v>681</v>
       </c>
       <c r="C5">
         <v>58</v>
@@ -9487,14 +9496,17 @@
       <c r="M5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
-        <v>435</v>
+        <v>459</v>
       </c>
       <c r="C6">
         <v>40</v>
@@ -9529,14 +9541,17 @@
       <c r="M6">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
-        <v>506</v>
+        <v>551</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -9571,8 +9586,11 @@
       <c r="M7">
         <v>36</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -9613,14 +9631,17 @@
       <c r="M8">
         <v>59</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
-        <v>484</v>
+        <v>529</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -9655,14 +9676,17 @@
       <c r="M9">
         <v>59</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N9">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
-        <v>471</v>
+        <v>516</v>
       </c>
       <c r="C10">
         <v>58</v>
@@ -9697,14 +9721,17 @@
       <c r="M10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N10">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
-        <v>636</v>
+        <v>681</v>
       </c>
       <c r="C11">
         <v>52</v>
@@ -9739,14 +9766,17 @@
       <c r="M11">
         <v>58</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N11">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
-        <v>512</v>
+        <v>546</v>
       </c>
       <c r="C12">
         <v>38</v>
@@ -9781,14 +9811,17 @@
       <c r="M12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
-        <v>491</v>
+        <v>536</v>
       </c>
       <c r="C13">
         <v>55</v>
@@ -9823,8 +9856,11 @@
       <c r="M13">
         <v>58</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -9865,14 +9901,17 @@
       <c r="M14">
         <v>58</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
-        <v>531</v>
+        <v>547</v>
       </c>
       <c r="C15">
         <v>57</v>
@@ -9907,8 +9946,11 @@
       <c r="M15">
         <v>59</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="N15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -9949,14 +9991,17 @@
       <c r="M16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>19</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
-        <v>309</v>
+        <v>353</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -9991,8 +10036,11 @@
       <c r="M17">
         <v>58</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N17">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>55</v>
       </c>
@@ -10033,14 +10081,17 @@
       <c r="M18">
         <v>59</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>44</v>
       </c>
       <c r="B19">
         <f t="shared" si="0"/>
-        <v>487</v>
+        <v>531</v>
       </c>
       <c r="C19">
         <v>56</v>
@@ -10075,14 +10126,17 @@
       <c r="M19">
         <v>57</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N19">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>47</v>
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
-        <v>616</v>
+        <v>660</v>
       </c>
       <c r="C20">
         <v>57</v>
@@ -10117,14 +10171,17 @@
       <c r="M20">
         <v>58</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N20">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>64</v>
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -10158,6 +10215,9 @@
       </c>
       <c r="M21">
         <v>0</v>
+      </c>
+      <c r="N21">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -10168,15 +10228,15 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7053FD00-70E4-44ED-874D-48591AC61FE1}">
   <dimension ref="A1:S24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10235,7 +10295,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -10244,7 +10304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -10253,7 +10313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -10262,7 +10322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -10271,7 +10331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -10280,7 +10340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -10289,7 +10349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -10298,7 +10358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -10307,7 +10367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -10316,7 +10376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -10325,7 +10385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -10334,7 +10394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -10343,7 +10403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -10352,7 +10412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -10361,7 +10421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -10370,7 +10430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -10379,7 +10439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -10388,7 +10448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -10397,7 +10457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -10406,7 +10466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -10415,7 +10475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -10424,7 +10484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -10433,7 +10493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -10450,13 +10510,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D4303C-7F1D-4CBD-BF56-16C815E789BE}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10464,122 +10524,122 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -10592,12 +10652,12 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E80DB57-1D34-4995-8AA7-BD186A2BDBE8}">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10605,127 +10665,127 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>66</v>
       </c>
@@ -10738,137 +10798,137 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95F0FCB7-825F-41B0-8DBE-275FB691B4D1}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>73</v>
       </c>
@@ -10881,147 +10941,147 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C60C079E-583C-4AF5-A6A9-C3E86F60AFD7}">
   <dimension ref="A1:A28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -11034,137 +11094,137 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9C6E86-EC8A-4EA5-A30B-4A7F0858E0A5}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>70</v>
       </c>
@@ -11177,122 +11237,122 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5342EC0-9A20-4134-BF81-DC6CEEC14B92}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>85</v>
       </c>
@@ -11305,16 +11365,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0EC39A2-025A-41B3-9C60-22F202BB8868}">
   <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11370,7 +11430,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -11435,137 +11495,137 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F76B976-1DE3-4828-AFA3-C2C8CE6A8C8D}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>92</v>
       </c>
@@ -11578,147 +11638,147 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FD15434-4874-452F-8199-FC863C296E8B}">
   <dimension ref="A1:A28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -11731,152 +11791,152 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B951F07-E9BC-4825-9AA7-DCA2D6A9E9B8}">
   <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>95</v>
       </c>
@@ -11889,137 +11949,137 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED86059-0F40-42A6-AE6A-E4A8243B3C21}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -12032,127 +12092,127 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B828EF67-0DDF-4C73-BB7C-135261ED3818}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>109</v>
       </c>
@@ -12165,127 +12225,127 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7D05EA9-09C8-45DF-9887-5028388B0199}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>113</v>
       </c>
@@ -12298,117 +12358,117 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AB2F14C-4266-4398-862F-517EC6F2BF68}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>113</v>
       </c>
@@ -12421,132 +12481,132 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9081B27-A4FF-4FDB-A545-8BEAAEB98497}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>123</v>
       </c>
@@ -12559,127 +12619,127 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D47B59A-B1BE-4472-A7E7-70223D1707FA}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>127</v>
       </c>
@@ -12692,112 +12752,112 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F202A74-DE9C-4BEE-9BC5-F661CBB67E18}">
   <dimension ref="A1:A21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>129</v>
       </c>
@@ -12810,17 +12870,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA742C1-0B95-4CA1-8FA2-14D0BE967B15}">
   <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12876,7 +12936,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -12941,112 +13001,112 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5FA89E6-064E-4CAF-91E1-B8698E14C23C}">
   <dimension ref="A1:A21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>132</v>
       </c>
@@ -13059,127 +13119,127 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7743BE8-494B-4549-A27B-0B0C0DC916B8}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>135</v>
       </c>
@@ -13192,117 +13252,117 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56826E7E-7CC5-4FC4-AA7B-870479195203}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>138</v>
       </c>
@@ -13315,122 +13375,122 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C16F4FE-A52D-4398-8BE4-A0ECC46C9962}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -13443,122 +13503,122 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A16EA40-13C9-4D0C-A228-ED069B0DFCDE}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>140</v>
       </c>
@@ -13571,132 +13631,132 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A1C5AB-79A4-4A2A-A59C-9F1C1089C3B0}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>146</v>
       </c>
@@ -13710,117 +13770,117 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC85092-DD56-4DFB-A3DE-A66B323B833F}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>146</v>
       </c>
@@ -13833,122 +13893,122 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{194B9004-BFC1-4A04-AEDF-CD50347CD713}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>124</v>
       </c>
@@ -13962,16 +14022,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D2BC23-0382-4C73-BD55-9C5BF90A5872}">
   <dimension ref="A1:R5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14027,7 +14087,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -14084,7 +14144,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14141,7 +14201,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -14198,7 +14258,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -14263,15 +14323,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD508AD-7632-48CF-B894-9F6914C08CD8}">
   <dimension ref="A1:R9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14327,7 +14387,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -14384,7 +14444,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14441,7 +14501,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -14498,7 +14558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -14555,7 +14615,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -14612,7 +14672,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>55</v>
       </c>
@@ -14669,7 +14729,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -14726,7 +14786,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -14791,13 +14851,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1668A00-6C37-4B7D-B869-26E922968418}">
   <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14856,7 +14916,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -14916,7 +14976,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14976,7 +15036,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -15036,7 +15096,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -15096,7 +15156,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -15156,7 +15216,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>55</v>
       </c>
@@ -15216,7 +15276,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -15276,7 +15336,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -15336,7 +15396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>151</v>
       </c>
@@ -15404,12 +15464,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D405A22-72AA-4B8B-8276-187361E5AFF5}">
   <dimension ref="A1:R12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15465,7 +15525,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -15522,7 +15582,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -15579,7 +15639,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -15636,7 +15696,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -15693,7 +15753,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -15750,7 +15810,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -15807,7 +15867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -15864,7 +15924,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -15921,7 +15981,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -15978,7 +16038,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -16035,7 +16095,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>92</v>
       </c>
@@ -16100,12 +16160,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D914D4-403F-4B81-B472-8E3F05ADF641}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -16164,7 +16224,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -16224,7 +16284,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -16284,7 +16344,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -16344,7 +16404,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -16404,7 +16464,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -16464,7 +16524,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -16524,7 +16584,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -16584,7 +16644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -16644,7 +16704,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -16704,7 +16764,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -16764,7 +16824,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -16824,7 +16884,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -16884,7 +16944,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -16952,16 +17012,16 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6443FC8D-E56E-407E-83EA-E01E6A3300AE}">
   <dimension ref="A1:R14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -17017,7 +17077,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -17074,7 +17134,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -17131,7 +17191,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -17188,7 +17248,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -17245,7 +17305,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -17302,7 +17362,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -17359,7 +17419,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -17416,7 +17476,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -17473,7 +17533,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -17530,7 +17590,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -17587,7 +17647,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -17644,7 +17704,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -17701,7 +17761,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>68</v>
       </c>

--- a/Data_Files/Laps_Completed.xlsx
+++ b/Data_Files/Laps_Completed.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owens\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BC2DC1-E0CE-4AA6-A45D-27760ADB3F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1296261-DF24-4663-BE8A-A35DC4E115E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="4" activeTab="11" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28695" yWindow="1500" windowWidth="16410" windowHeight="14145" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Laps_Completed" sheetId="1" r:id="rId1"/>
@@ -1602,13 +1602,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCEEE69D-1A9D-4213-BBC7-B7EBD153B749}">
   <dimension ref="A1:AL124"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1721,10 +1721,13 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="AB2">
+        <v>1005</v>
+      </c>
       <c r="AC2">
         <v>921</v>
       </c>
@@ -1756,10 +1759,13 @@
         <v>228</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
+      <c r="AB3">
+        <v>928</v>
+      </c>
       <c r="AC3">
         <v>939</v>
       </c>
@@ -1791,11 +1797,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="AC4" s="1"/>
+      <c r="AB4">
+        <v>756</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>0</v>
+      </c>
       <c r="AD4" s="1">
         <v>0</v>
       </c>
@@ -1824,10 +1835,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
+      <c r="AB5">
+        <v>926</v>
+      </c>
       <c r="AC5">
         <v>973</v>
       </c>
@@ -1859,11 +1873,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="AC6" s="1"/>
+      <c r="AB6">
+        <v>680</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>0</v>
+      </c>
       <c r="AD6" s="1">
         <v>0</v>
       </c>
@@ -1892,10 +1911,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
+      <c r="AB7">
+        <v>806</v>
+      </c>
       <c r="AC7">
         <v>913</v>
       </c>
@@ -1927,11 +1949,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="AB8" s="1"/>
+      <c r="AB8" s="1">
+        <v>0</v>
+      </c>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1">
         <v>0</v>
@@ -1961,10 +1985,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
+      <c r="AB9">
+        <v>764</v>
+      </c>
       <c r="AC9">
         <v>625</v>
       </c>
@@ -1996,10 +2023,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
+      <c r="AB10">
+        <v>790</v>
+      </c>
       <c r="AC10">
         <v>900</v>
       </c>
@@ -2031,10 +2061,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
+      <c r="AB11">
+        <v>784</v>
+      </c>
       <c r="AC11" s="1">
         <v>0</v>
       </c>
@@ -2066,10 +2099,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
+      <c r="AB12">
+        <v>861</v>
+      </c>
       <c r="AC12">
         <v>789</v>
       </c>
@@ -2101,10 +2137,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
+      <c r="AB13">
+        <v>755</v>
+      </c>
       <c r="AC13">
         <v>709</v>
       </c>
@@ -2136,11 +2175,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="AB14" s="1"/>
+      <c r="AB14" s="1">
+        <v>0</v>
+      </c>
       <c r="AC14" s="1">
         <v>0</v>
       </c>
@@ -2172,10 +2213,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
+      <c r="AB15">
+        <v>810</v>
+      </c>
       <c r="AC15">
         <v>389</v>
       </c>
@@ -2207,10 +2251,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
+      <c r="AB16">
+        <v>579</v>
+      </c>
       <c r="AC16">
         <v>600</v>
       </c>
@@ -2242,10 +2289,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
+      <c r="AB17">
+        <v>658</v>
+      </c>
       <c r="AC17">
         <v>799</v>
       </c>
@@ -2277,11 +2327,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="AB18" s="1"/>
+      <c r="AB18" s="1">
+        <v>0</v>
+      </c>
       <c r="AC18" s="1">
         <v>0</v>
       </c>
@@ -2313,11 +2365,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>85</v>
       </c>
-      <c r="AB19" s="1"/>
+      <c r="AB19" s="1">
+        <v>0</v>
+      </c>
       <c r="AC19" s="1">
         <v>0</v>
       </c>
@@ -2349,10 +2403,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
+      <c r="AB20">
+        <v>132</v>
+      </c>
       <c r="AC20" s="1">
         <v>0</v>
       </c>
@@ -2384,10 +2441,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
+      <c r="AB21">
+        <v>568</v>
+      </c>
       <c r="AC21" s="1">
         <v>0</v>
       </c>
@@ -2419,10 +2479,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>55</v>
       </c>
+      <c r="AB22">
+        <v>719</v>
+      </c>
       <c r="AC22">
         <v>681</v>
       </c>
@@ -2454,10 +2517,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
       <c r="AC23">
         <v>814</v>
       </c>
@@ -2489,11 +2555,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
-      <c r="AB24" s="1"/>
+      <c r="AB24" s="1">
+        <v>0</v>
+      </c>
       <c r="AC24" s="1">
         <v>0</v>
       </c>
@@ -2525,10 +2593,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>44</v>
       </c>
+      <c r="AB25">
+        <v>707</v>
+      </c>
       <c r="AC25" s="1">
         <v>0</v>
       </c>
@@ -2560,12 +2631,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>45</v>
       </c>
       <c r="AA26" s="1"/>
-      <c r="AB26" s="1"/>
+      <c r="AB26" s="1">
+        <v>0</v>
+      </c>
       <c r="AC26" s="1">
         <v>0</v>
       </c>
@@ -2597,12 +2670,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>46</v>
       </c>
       <c r="AA27" s="1"/>
-      <c r="AB27" s="1"/>
+      <c r="AB27" s="1">
+        <v>0</v>
+      </c>
       <c r="AC27" s="1">
         <v>0</v>
       </c>
@@ -2634,10 +2709,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>47</v>
       </c>
+      <c r="AB28">
+        <v>889</v>
+      </c>
       <c r="AC28">
         <v>695</v>
       </c>
@@ -2669,12 +2747,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>48</v>
       </c>
       <c r="AA29" s="1"/>
-      <c r="AB29" s="1"/>
+      <c r="AB29" s="1">
+        <v>0</v>
+      </c>
       <c r="AC29" s="1">
         <v>0</v>
       </c>
@@ -2706,12 +2786,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>49</v>
       </c>
       <c r="AA30" s="1"/>
-      <c r="AB30" s="1"/>
+      <c r="AB30" s="1">
+        <v>0</v>
+      </c>
       <c r="AC30" s="1">
         <v>0</v>
       </c>
@@ -2743,10 +2825,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>53</v>
       </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
       <c r="AC31">
         <v>843</v>
       </c>
@@ -2778,12 +2863,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>57</v>
       </c>
       <c r="AA32" s="1"/>
-      <c r="AB32" s="1"/>
+      <c r="AB32" s="1">
+        <v>0</v>
+      </c>
       <c r="AC32" s="1">
         <v>0</v>
       </c>
@@ -2815,12 +2902,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>58</v>
       </c>
       <c r="AA33" s="1"/>
-      <c r="AB33" s="1"/>
+      <c r="AB33" s="1">
+        <v>0</v>
+      </c>
       <c r="AC33" s="1">
         <v>0</v>
       </c>
@@ -2852,12 +2941,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>59</v>
       </c>
       <c r="AA34" s="1"/>
-      <c r="AB34" s="1"/>
+      <c r="AB34" s="1">
+        <v>0</v>
+      </c>
       <c r="AC34" s="1">
         <v>0</v>
       </c>
@@ -2889,12 +2980,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>60</v>
       </c>
       <c r="AA35" s="1"/>
-      <c r="AB35" s="1"/>
+      <c r="AB35" s="1">
+        <v>0</v>
+      </c>
       <c r="AC35" s="1">
         <v>0</v>
       </c>
@@ -2926,12 +3019,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>61</v>
       </c>
       <c r="AA36" s="1"/>
-      <c r="AB36" s="1"/>
+      <c r="AB36" s="1">
+        <v>0</v>
+      </c>
       <c r="AC36" s="1">
         <v>0</v>
       </c>
@@ -2963,13 +3058,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>62</v>
       </c>
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
-      <c r="AB37" s="1"/>
+      <c r="AB37" s="1">
+        <v>0</v>
+      </c>
       <c r="AC37" s="1">
         <v>0</v>
       </c>
@@ -3001,13 +3098,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>63</v>
       </c>
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
-      <c r="AB38" s="1"/>
+      <c r="AB38" s="1">
+        <v>0</v>
+      </c>
       <c r="AC38" s="1">
         <v>0</v>
       </c>
@@ -3039,10 +3138,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>64</v>
       </c>
+      <c r="AB39">
+        <v>75</v>
+      </c>
       <c r="AC39">
         <v>909</v>
       </c>
@@ -3074,13 +3176,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>65</v>
       </c>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
-      <c r="AB40" s="1"/>
+      <c r="AB40" s="1">
+        <v>0</v>
+      </c>
       <c r="AC40" s="1">
         <v>0</v>
       </c>
@@ -3112,13 +3216,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>66</v>
       </c>
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
-      <c r="AB41" s="1"/>
+      <c r="AB41" s="1">
+        <v>0</v>
+      </c>
       <c r="AC41" s="1">
         <v>0</v>
       </c>
@@ -3150,14 +3256,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>67</v>
       </c>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
-      <c r="AB42" s="1"/>
+      <c r="AB42" s="1">
+        <v>0</v>
+      </c>
       <c r="AC42" s="1">
         <v>0</v>
       </c>
@@ -3189,10 +3297,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>68</v>
       </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
       <c r="AC43">
         <v>868</v>
       </c>
@@ -3224,14 +3335,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>69</v>
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
-      <c r="AB44" s="1"/>
+      <c r="AB44" s="1">
+        <v>0</v>
+      </c>
       <c r="AC44" s="1">
         <v>0</v>
       </c>
@@ -3263,14 +3376,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>70</v>
       </c>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
       <c r="AA45" s="1"/>
-      <c r="AB45" s="1"/>
+      <c r="AB45" s="1">
+        <v>0</v>
+      </c>
       <c r="AC45" s="1">
         <v>0</v>
       </c>
@@ -3302,14 +3417,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>71</v>
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
       <c r="AA46" s="1"/>
-      <c r="AB46" s="1"/>
+      <c r="AB46" s="1">
+        <v>0</v>
+      </c>
       <c r="AC46" s="1">
         <v>0</v>
       </c>
@@ -3341,14 +3458,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>72</v>
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
-      <c r="AB47" s="1"/>
+      <c r="AB47" s="1">
+        <v>0</v>
+      </c>
       <c r="AC47" s="1">
         <v>0</v>
       </c>
@@ -3380,14 +3499,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>73</v>
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
-      <c r="AB48" s="1"/>
+      <c r="AB48" s="1">
+        <v>0</v>
+      </c>
       <c r="AC48" s="1">
         <v>0</v>
       </c>
@@ -3419,7 +3540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -3427,7 +3548,9 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1"/>
-      <c r="AB49" s="1"/>
+      <c r="AB49" s="1">
+        <v>0</v>
+      </c>
       <c r="AC49" s="1">
         <v>0</v>
       </c>
@@ -3459,7 +3582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>75</v>
       </c>
@@ -3467,7 +3590,9 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
-      <c r="AB50" s="1"/>
+      <c r="AB50" s="1">
+        <v>0</v>
+      </c>
       <c r="AC50" s="1">
         <v>0</v>
       </c>
@@ -3499,7 +3624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>76</v>
       </c>
@@ -3507,7 +3632,9 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
       <c r="AA51" s="1"/>
-      <c r="AB51" s="1"/>
+      <c r="AB51" s="1">
+        <v>0</v>
+      </c>
       <c r="AC51" s="1">
         <v>0</v>
       </c>
@@ -3539,7 +3666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -3547,7 +3674,9 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
       <c r="AA52" s="1"/>
-      <c r="AB52" s="1"/>
+      <c r="AB52" s="1">
+        <v>0</v>
+      </c>
       <c r="AC52" s="1">
         <v>0</v>
       </c>
@@ -3579,7 +3708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>78</v>
       </c>
@@ -3587,7 +3716,9 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1"/>
-      <c r="AB53" s="1"/>
+      <c r="AB53" s="1">
+        <v>0</v>
+      </c>
       <c r="AC53" s="1">
         <v>0</v>
       </c>
@@ -3619,7 +3750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>79</v>
       </c>
@@ -3627,7 +3758,9 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
-      <c r="AB54" s="1"/>
+      <c r="AB54" s="1">
+        <v>0</v>
+      </c>
       <c r="AC54" s="1">
         <v>0</v>
       </c>
@@ -3659,7 +3792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>80</v>
       </c>
@@ -3668,7 +3801,9 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
       <c r="AA55" s="1"/>
-      <c r="AB55" s="1"/>
+      <c r="AB55" s="1">
+        <v>0</v>
+      </c>
       <c r="AC55" s="1">
         <v>0</v>
       </c>
@@ -3700,7 +3835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>81</v>
       </c>
@@ -3709,7 +3844,9 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
       <c r="AA56" s="1"/>
-      <c r="AB56" s="1"/>
+      <c r="AB56" s="1">
+        <v>0</v>
+      </c>
       <c r="AC56" s="1">
         <v>0</v>
       </c>
@@ -3741,7 +3878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>82</v>
       </c>
@@ -3750,7 +3887,9 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
       <c r="AA57" s="1"/>
-      <c r="AB57" s="1"/>
+      <c r="AB57" s="1">
+        <v>0</v>
+      </c>
       <c r="AC57" s="1">
         <v>0</v>
       </c>
@@ -3782,7 +3921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>83</v>
       </c>
@@ -3791,7 +3930,9 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
       <c r="AA58" s="1"/>
-      <c r="AB58" s="1"/>
+      <c r="AB58" s="1">
+        <v>0</v>
+      </c>
       <c r="AC58" s="1">
         <v>0</v>
       </c>
@@ -3823,7 +3964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>84</v>
       </c>
@@ -3832,7 +3973,9 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
       <c r="AA59" s="1"/>
-      <c r="AB59" s="1"/>
+      <c r="AB59" s="1">
+        <v>0</v>
+      </c>
       <c r="AC59" s="1">
         <v>0</v>
       </c>
@@ -3864,7 +4007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>86</v>
       </c>
@@ -3874,7 +4017,9 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
       <c r="AA60" s="1"/>
-      <c r="AB60" s="1"/>
+      <c r="AB60" s="1">
+        <v>0</v>
+      </c>
       <c r="AC60" s="1">
         <v>0</v>
       </c>
@@ -3906,7 +4051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>87</v>
       </c>
@@ -3916,7 +4061,9 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
       <c r="AA61" s="1"/>
-      <c r="AB61" s="1"/>
+      <c r="AB61" s="1">
+        <v>0</v>
+      </c>
       <c r="AC61" s="1">
         <v>0</v>
       </c>
@@ -3948,7 +4095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>88</v>
       </c>
@@ -3959,7 +4106,9 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
       <c r="AA62" s="1"/>
-      <c r="AB62" s="1"/>
+      <c r="AB62" s="1">
+        <v>0</v>
+      </c>
       <c r="AC62" s="1">
         <v>0</v>
       </c>
@@ -3991,7 +4140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>89</v>
       </c>
@@ -4002,7 +4151,9 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
       <c r="AA63" s="1"/>
-      <c r="AB63" s="1"/>
+      <c r="AB63" s="1">
+        <v>0</v>
+      </c>
       <c r="AC63" s="1">
         <v>0</v>
       </c>
@@ -4034,7 +4185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>90</v>
       </c>
@@ -4045,7 +4196,9 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
       <c r="AA64" s="1"/>
-      <c r="AB64" s="1"/>
+      <c r="AB64" s="1">
+        <v>0</v>
+      </c>
       <c r="AC64" s="1">
         <v>0</v>
       </c>
@@ -4077,7 +4230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>91</v>
       </c>
@@ -4088,7 +4241,9 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
       <c r="AA65" s="1"/>
-      <c r="AB65" s="1"/>
+      <c r="AB65" s="1">
+        <v>0</v>
+      </c>
       <c r="AC65" s="1">
         <v>0</v>
       </c>
@@ -4120,7 +4275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>92</v>
       </c>
@@ -4179,7 +4334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>93</v>
       </c>
@@ -4191,7 +4346,9 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
       <c r="AA67" s="1"/>
-      <c r="AB67" s="1"/>
+      <c r="AB67" s="1">
+        <v>0</v>
+      </c>
       <c r="AC67" s="1">
         <v>0</v>
       </c>
@@ -4223,7 +4380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>94</v>
       </c>
@@ -4235,7 +4392,9 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
       <c r="AA68" s="1"/>
-      <c r="AB68" s="1"/>
+      <c r="AB68" s="1">
+        <v>0</v>
+      </c>
       <c r="AC68" s="1">
         <v>0</v>
       </c>
@@ -4267,7 +4426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>95</v>
       </c>
@@ -4279,7 +4438,9 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
       <c r="AA69" s="1"/>
-      <c r="AB69" s="1"/>
+      <c r="AB69" s="1">
+        <v>0</v>
+      </c>
       <c r="AC69" s="1">
         <v>0</v>
       </c>
@@ -4311,7 +4472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>96</v>
       </c>
@@ -4323,7 +4484,9 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
       <c r="AA70" s="1"/>
-      <c r="AB70" s="1"/>
+      <c r="AB70" s="1">
+        <v>0</v>
+      </c>
       <c r="AC70" s="1">
         <v>0</v>
       </c>
@@ -4355,7 +4518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>97</v>
       </c>
@@ -4367,7 +4530,9 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
       <c r="AA71" s="1"/>
-      <c r="AB71" s="1"/>
+      <c r="AB71" s="1">
+        <v>0</v>
+      </c>
       <c r="AC71" s="1">
         <v>0</v>
       </c>
@@ -4399,7 +4564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>98</v>
       </c>
@@ -4412,7 +4577,9 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
       <c r="AA72" s="1"/>
-      <c r="AB72" s="1"/>
+      <c r="AB72" s="1">
+        <v>0</v>
+      </c>
       <c r="AC72" s="1">
         <v>0</v>
       </c>
@@ -4444,7 +4611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>99</v>
       </c>
@@ -4457,7 +4624,9 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
       <c r="AA73" s="1"/>
-      <c r="AB73" s="1"/>
+      <c r="AB73" s="1">
+        <v>0</v>
+      </c>
       <c r="AC73" s="1">
         <v>0</v>
       </c>
@@ -4489,7 +4658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>100</v>
       </c>
@@ -4502,7 +4671,9 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
       <c r="AA74" s="1"/>
-      <c r="AB74" s="1"/>
+      <c r="AB74" s="1">
+        <v>0</v>
+      </c>
       <c r="AC74" s="1">
         <v>0</v>
       </c>
@@ -4534,7 +4705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>101</v>
       </c>
@@ -4547,7 +4718,9 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
       <c r="AA75" s="1"/>
-      <c r="AB75" s="1"/>
+      <c r="AB75" s="1">
+        <v>0</v>
+      </c>
       <c r="AC75" s="1">
         <v>0</v>
       </c>
@@ -4579,7 +4752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>102</v>
       </c>
@@ -4592,7 +4765,9 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
       <c r="AA76" s="1"/>
-      <c r="AB76" s="1"/>
+      <c r="AB76" s="1">
+        <v>0</v>
+      </c>
       <c r="AC76" s="1">
         <v>0</v>
       </c>
@@ -4624,7 +4799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>103</v>
       </c>
@@ -4638,7 +4813,9 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
       <c r="AA77" s="1"/>
-      <c r="AB77" s="1"/>
+      <c r="AB77" s="1">
+        <v>0</v>
+      </c>
       <c r="AC77" s="1">
         <v>0</v>
       </c>
@@ -4670,7 +4847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>104</v>
       </c>
@@ -4684,7 +4861,9 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
       <c r="AA78" s="1"/>
-      <c r="AB78" s="1"/>
+      <c r="AB78" s="1">
+        <v>0</v>
+      </c>
       <c r="AC78" s="1">
         <v>0</v>
       </c>
@@ -4716,7 +4895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>105</v>
       </c>
@@ -4731,7 +4910,9 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
       <c r="AA79" s="1"/>
-      <c r="AB79" s="1"/>
+      <c r="AB79" s="1">
+        <v>0</v>
+      </c>
       <c r="AC79" s="1">
         <v>0</v>
       </c>
@@ -4763,7 +4944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>106</v>
       </c>
@@ -4778,7 +4959,9 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
       <c r="AA80" s="1"/>
-      <c r="AB80" s="1"/>
+      <c r="AB80" s="1">
+        <v>0</v>
+      </c>
       <c r="AC80" s="1">
         <v>0</v>
       </c>
@@ -4810,7 +4993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>107</v>
       </c>
@@ -4825,7 +5008,9 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
       <c r="AA81" s="1"/>
-      <c r="AB81" s="1"/>
+      <c r="AB81" s="1">
+        <v>0</v>
+      </c>
       <c r="AC81" s="1">
         <v>0</v>
       </c>
@@ -4857,7 +5042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>108</v>
       </c>
@@ -4872,7 +5057,9 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
       <c r="AA82" s="1"/>
-      <c r="AB82" s="1"/>
+      <c r="AB82" s="1">
+        <v>0</v>
+      </c>
       <c r="AC82" s="1">
         <v>0</v>
       </c>
@@ -4904,7 +5091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>109</v>
       </c>
@@ -4919,7 +5106,9 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
       <c r="AA83" s="1"/>
-      <c r="AB83" s="1"/>
+      <c r="AB83" s="1">
+        <v>0</v>
+      </c>
       <c r="AC83" s="1">
         <v>0</v>
       </c>
@@ -4951,7 +5140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>110</v>
       </c>
@@ -4967,7 +5156,9 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
       <c r="AA84" s="1"/>
-      <c r="AB84" s="1"/>
+      <c r="AB84" s="1">
+        <v>0</v>
+      </c>
       <c r="AC84" s="1">
         <v>0</v>
       </c>
@@ -4999,7 +5190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>111</v>
       </c>
@@ -5015,7 +5206,9 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
       <c r="AA85" s="1"/>
-      <c r="AB85" s="1"/>
+      <c r="AB85" s="1">
+        <v>0</v>
+      </c>
       <c r="AC85" s="1">
         <v>0</v>
       </c>
@@ -5047,7 +5240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>112</v>
       </c>
@@ -5063,7 +5256,9 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
       <c r="AA86" s="1"/>
-      <c r="AB86" s="1"/>
+      <c r="AB86" s="1">
+        <v>0</v>
+      </c>
       <c r="AC86" s="1">
         <v>0</v>
       </c>
@@ -5095,7 +5290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>113</v>
       </c>
@@ -5111,7 +5306,9 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
       <c r="AA87" s="1"/>
-      <c r="AB87" s="1"/>
+      <c r="AB87" s="1">
+        <v>0</v>
+      </c>
       <c r="AC87" s="1">
         <v>0</v>
       </c>
@@ -5143,7 +5340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>114</v>
       </c>
@@ -5160,7 +5357,9 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
       <c r="AA88" s="1"/>
-      <c r="AB88" s="1"/>
+      <c r="AB88" s="1">
+        <v>0</v>
+      </c>
       <c r="AC88" s="1">
         <v>0</v>
       </c>
@@ -5192,7 +5391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>115</v>
       </c>
@@ -5209,7 +5408,9 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
       <c r="AA89" s="1"/>
-      <c r="AB89" s="1"/>
+      <c r="AB89" s="1">
+        <v>0</v>
+      </c>
       <c r="AC89" s="1">
         <v>0</v>
       </c>
@@ -5241,7 +5442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>116</v>
       </c>
@@ -5258,7 +5459,9 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
       <c r="AA90" s="1"/>
-      <c r="AB90" s="1"/>
+      <c r="AB90" s="1">
+        <v>0</v>
+      </c>
       <c r="AC90" s="1">
         <v>0</v>
       </c>
@@ -5290,7 +5493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>117</v>
       </c>
@@ -5307,7 +5510,9 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
       <c r="AA91" s="1"/>
-      <c r="AB91" s="1"/>
+      <c r="AB91" s="1">
+        <v>0</v>
+      </c>
       <c r="AC91" s="1">
         <v>0</v>
       </c>
@@ -5339,7 +5544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>118</v>
       </c>
@@ -5356,7 +5561,9 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
       <c r="AA92" s="1"/>
-      <c r="AB92" s="1"/>
+      <c r="AB92" s="1">
+        <v>0</v>
+      </c>
       <c r="AC92" s="1">
         <v>0</v>
       </c>
@@ -5388,7 +5595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>119</v>
       </c>
@@ -5406,7 +5613,9 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
       <c r="AA93" s="1"/>
-      <c r="AB93" s="1"/>
+      <c r="AB93" s="1">
+        <v>0</v>
+      </c>
       <c r="AC93" s="1">
         <v>0</v>
       </c>
@@ -5438,7 +5647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>120</v>
       </c>
@@ -5456,7 +5665,9 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
       <c r="AA94" s="1"/>
-      <c r="AB94" s="1"/>
+      <c r="AB94" s="1">
+        <v>0</v>
+      </c>
       <c r="AC94" s="1">
         <v>0</v>
       </c>
@@ -5488,7 +5699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>121</v>
       </c>
@@ -5506,7 +5717,9 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
       <c r="AA95" s="1"/>
-      <c r="AB95" s="1"/>
+      <c r="AB95" s="1">
+        <v>0</v>
+      </c>
       <c r="AC95" s="1">
         <v>0</v>
       </c>
@@ -5538,7 +5751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>122</v>
       </c>
@@ -5556,7 +5769,9 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
       <c r="AA96" s="1"/>
-      <c r="AB96" s="1"/>
+      <c r="AB96" s="1">
+        <v>0</v>
+      </c>
       <c r="AC96" s="1">
         <v>0</v>
       </c>
@@ -5588,7 +5803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>123</v>
       </c>
@@ -5606,7 +5821,9 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
       <c r="AA97" s="1"/>
-      <c r="AB97" s="1"/>
+      <c r="AB97" s="1">
+        <v>0</v>
+      </c>
       <c r="AC97" s="1">
         <v>0</v>
       </c>
@@ -5638,7 +5855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>124</v>
       </c>
@@ -5657,7 +5874,9 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
       <c r="AA98" s="1"/>
-      <c r="AB98" s="1"/>
+      <c r="AB98" s="1">
+        <v>0</v>
+      </c>
       <c r="AC98" s="1">
         <v>0</v>
       </c>
@@ -5689,7 +5908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>125</v>
       </c>
@@ -5708,7 +5927,9 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
       <c r="AA99" s="1"/>
-      <c r="AB99" s="1"/>
+      <c r="AB99" s="1">
+        <v>0</v>
+      </c>
       <c r="AC99" s="1">
         <v>0</v>
       </c>
@@ -5740,7 +5961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>126</v>
       </c>
@@ -5759,7 +5980,9 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
       <c r="AA100" s="1"/>
-      <c r="AB100" s="1"/>
+      <c r="AB100" s="1">
+        <v>0</v>
+      </c>
       <c r="AC100" s="1">
         <v>0</v>
       </c>
@@ -5791,7 +6014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>127</v>
       </c>
@@ -5810,7 +6033,9 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
       <c r="AA101" s="1"/>
-      <c r="AB101" s="1"/>
+      <c r="AB101" s="1">
+        <v>0</v>
+      </c>
       <c r="AC101" s="1">
         <v>0</v>
       </c>
@@ -5842,7 +6067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>128</v>
       </c>
@@ -5862,7 +6087,9 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
       <c r="AA102" s="1"/>
-      <c r="AB102" s="1"/>
+      <c r="AB102" s="1">
+        <v>0</v>
+      </c>
       <c r="AC102" s="1">
         <v>0</v>
       </c>
@@ -5894,7 +6121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>129</v>
       </c>
@@ -5914,7 +6141,9 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
       <c r="AA103" s="1"/>
-      <c r="AB103" s="1"/>
+      <c r="AB103" s="1">
+        <v>0</v>
+      </c>
       <c r="AC103" s="1">
         <v>0</v>
       </c>
@@ -5946,7 +6175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>130</v>
       </c>
@@ -5967,7 +6196,9 @@
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
       <c r="AA104" s="1"/>
-      <c r="AB104" s="1"/>
+      <c r="AB104" s="1">
+        <v>0</v>
+      </c>
       <c r="AC104" s="1">
         <v>0</v>
       </c>
@@ -5999,7 +6230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>131</v>
       </c>
@@ -6020,7 +6251,9 @@
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
       <c r="AA105" s="1"/>
-      <c r="AB105" s="1"/>
+      <c r="AB105" s="1">
+        <v>0</v>
+      </c>
       <c r="AC105" s="1">
         <v>0</v>
       </c>
@@ -6052,7 +6285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>132</v>
       </c>
@@ -6073,7 +6306,9 @@
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
       <c r="AA106" s="1"/>
-      <c r="AB106" s="1"/>
+      <c r="AB106" s="1">
+        <v>0</v>
+      </c>
       <c r="AC106" s="1">
         <v>0</v>
       </c>
@@ -6105,7 +6340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>133</v>
       </c>
@@ -6127,7 +6362,9 @@
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
       <c r="AA107" s="1"/>
-      <c r="AB107" s="1"/>
+      <c r="AB107" s="1">
+        <v>0</v>
+      </c>
       <c r="AC107" s="1">
         <v>0</v>
       </c>
@@ -6159,7 +6396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>134</v>
       </c>
@@ -6181,7 +6418,9 @@
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
       <c r="AA108" s="1"/>
-      <c r="AB108" s="1"/>
+      <c r="AB108" s="1">
+        <v>0</v>
+      </c>
       <c r="AC108" s="1">
         <v>0</v>
       </c>
@@ -6213,7 +6452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>135</v>
       </c>
@@ -6235,7 +6474,9 @@
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
       <c r="AA109" s="1"/>
-      <c r="AB109" s="1"/>
+      <c r="AB109" s="1">
+        <v>0</v>
+      </c>
       <c r="AC109" s="1">
         <v>0</v>
       </c>
@@ -6267,7 +6508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>136</v>
       </c>
@@ -6290,7 +6531,9 @@
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
       <c r="AA110" s="1"/>
-      <c r="AB110" s="1"/>
+      <c r="AB110" s="1">
+        <v>0</v>
+      </c>
       <c r="AC110" s="1">
         <v>0</v>
       </c>
@@ -6322,7 +6565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>137</v>
       </c>
@@ -6345,7 +6588,9 @@
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
       <c r="AA111" s="1"/>
-      <c r="AB111" s="1"/>
+      <c r="AB111" s="1">
+        <v>0</v>
+      </c>
       <c r="AC111" s="1">
         <v>0</v>
       </c>
@@ -6377,7 +6622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>138</v>
       </c>
@@ -6400,7 +6645,9 @@
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
       <c r="AA112" s="1"/>
-      <c r="AB112" s="1"/>
+      <c r="AB112" s="1">
+        <v>0</v>
+      </c>
       <c r="AC112" s="1">
         <v>0</v>
       </c>
@@ -6432,7 +6679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>139</v>
       </c>
@@ -6456,7 +6703,9 @@
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
       <c r="AA113" s="1"/>
-      <c r="AB113" s="1"/>
+      <c r="AB113" s="1">
+        <v>0</v>
+      </c>
       <c r="AC113" s="1">
         <v>0</v>
       </c>
@@ -6488,7 +6737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>140</v>
       </c>
@@ -6512,7 +6761,9 @@
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
       <c r="AA114" s="1"/>
-      <c r="AB114" s="1"/>
+      <c r="AB114" s="1">
+        <v>0</v>
+      </c>
       <c r="AC114" s="1">
         <v>0</v>
       </c>
@@ -6544,7 +6795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>141</v>
       </c>
@@ -6569,7 +6820,9 @@
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
       <c r="AA115" s="1"/>
-      <c r="AB115" s="1"/>
+      <c r="AB115" s="1">
+        <v>0</v>
+      </c>
       <c r="AC115" s="1">
         <v>0</v>
       </c>
@@ -6601,7 +6854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>142</v>
       </c>
@@ -6626,7 +6879,9 @@
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
       <c r="AA116" s="1"/>
-      <c r="AB116" s="1"/>
+      <c r="AB116" s="1">
+        <v>0</v>
+      </c>
       <c r="AC116" s="1">
         <v>0</v>
       </c>
@@ -6658,7 +6913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>143</v>
       </c>
@@ -6683,7 +6938,9 @@
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
       <c r="AA117" s="1"/>
-      <c r="AB117" s="1"/>
+      <c r="AB117" s="1">
+        <v>0</v>
+      </c>
       <c r="AC117" s="1">
         <v>0</v>
       </c>
@@ -6715,7 +6972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>144</v>
       </c>
@@ -6741,7 +6998,9 @@
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
       <c r="AA118" s="1"/>
-      <c r="AB118" s="1"/>
+      <c r="AB118" s="1">
+        <v>0</v>
+      </c>
       <c r="AC118" s="1">
         <v>0</v>
       </c>
@@ -6773,7 +7032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>145</v>
       </c>
@@ -6799,7 +7058,9 @@
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
       <c r="AA119" s="1"/>
-      <c r="AB119" s="1"/>
+      <c r="AB119" s="1">
+        <v>0</v>
+      </c>
       <c r="AC119" s="1">
         <v>0</v>
       </c>
@@ -6831,7 +7092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>146</v>
       </c>
@@ -6857,7 +7118,9 @@
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
       <c r="AA120" s="1"/>
-      <c r="AB120" s="1"/>
+      <c r="AB120" s="1">
+        <v>0</v>
+      </c>
       <c r="AC120" s="1">
         <v>0</v>
       </c>
@@ -6889,7 +7152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>147</v>
       </c>
@@ -6916,7 +7179,9 @@
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
       <c r="AA121" s="1"/>
-      <c r="AB121" s="1"/>
+      <c r="AB121" s="1">
+        <v>0</v>
+      </c>
       <c r="AC121" s="1">
         <v>0</v>
       </c>
@@ -6948,7 +7213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>148</v>
       </c>
@@ -6975,7 +7240,9 @@
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
       <c r="AA122" s="1"/>
-      <c r="AB122" s="1"/>
+      <c r="AB122" s="1">
+        <v>0</v>
+      </c>
       <c r="AC122" s="1">
         <v>0</v>
       </c>
@@ -7007,7 +7274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>149</v>
       </c>
@@ -7034,7 +7301,9 @@
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
       <c r="AA123" s="1"/>
-      <c r="AB123" s="1"/>
+      <c r="AB123" s="1">
+        <v>0</v>
+      </c>
       <c r="AC123" s="1">
         <v>0</v>
       </c>
@@ -7066,7 +7335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>150</v>
       </c>
@@ -7094,7 +7363,9 @@
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
       <c r="AA124" s="1"/>
-      <c r="AB124" s="1"/>
+      <c r="AB124" s="1">
+        <v>0</v>
+      </c>
       <c r="AC124" s="1">
         <v>0</v>
       </c>
@@ -7135,26 +7406,26 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A672F957-1D62-4580-B7C6-2DFEBD8C86A9}">
   <dimension ref="A1:R17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7210,7 +7481,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -7267,7 +7538,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -7324,7 +7595,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -7381,7 +7652,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -7438,7 +7709,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -7495,7 +7766,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -7552,7 +7823,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -7609,7 +7880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -7666,7 +7937,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -7723,7 +7994,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -7780,7 +8051,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>55</v>
       </c>
@@ -7837,7 +8108,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -7894,7 +8165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>53</v>
       </c>
@@ -7951,7 +8222,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>64</v>
       </c>
@@ -8008,7 +8279,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -8065,7 +8336,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -8131,29 +8402,29 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC06B72-571E-40C4-AD69-3294909EA05A}">
   <dimension ref="A1:S18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8212,7 +8483,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -8272,7 +8543,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -8332,7 +8603,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -8392,7 +8663,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -8452,7 +8723,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -8512,7 +8783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -8572,7 +8843,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -8632,7 +8903,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -8692,7 +8963,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -8752,7 +9023,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -8812,7 +9083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -8872,7 +9143,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -8932,7 +9203,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -8992,7 +9263,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -9052,7 +9323,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>53</v>
       </c>
@@ -9112,7 +9383,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>64</v>
       </c>
@@ -9172,7 +9443,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -9240,28 +9511,28 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5463DBD5-1047-4E7D-B3B5-A719C2F7680D}">
   <dimension ref="A1:S21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9320,13 +9591,13 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
         <f>SUM(C2:S2)</f>
-        <v>713</v>
+        <v>1005</v>
       </c>
       <c r="C2">
         <v>58</v>
@@ -9364,14 +9635,29 @@
       <c r="N2">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O2">
+        <v>77</v>
+      </c>
+      <c r="P2">
+        <v>36</v>
+      </c>
+      <c r="Q2">
+        <v>53</v>
+      </c>
+      <c r="R2">
+        <v>73</v>
+      </c>
+      <c r="S2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
         <f t="shared" ref="B3:B21" si="0">SUM(C3:S3)</f>
-        <v>638</v>
+        <v>928</v>
       </c>
       <c r="C3">
         <v>58</v>
@@ -9409,14 +9695,29 @@
       <c r="N3">
         <v>45</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O3">
+        <v>77</v>
+      </c>
+      <c r="P3">
+        <v>36</v>
+      </c>
+      <c r="Q3">
+        <v>53</v>
+      </c>
+      <c r="R3">
+        <v>71</v>
+      </c>
+      <c r="S3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
         <f t="shared" si="0"/>
-        <v>620</v>
+        <v>756</v>
       </c>
       <c r="C4">
         <v>58</v>
@@ -9454,14 +9755,29 @@
       <c r="N4">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O4">
+        <v>76</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>53</v>
+      </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
+      <c r="S4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
-        <v>681</v>
+        <v>926</v>
       </c>
       <c r="C5">
         <v>58</v>
@@ -9499,14 +9815,29 @@
       <c r="N5">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O5">
+        <v>77</v>
+      </c>
+      <c r="P5">
+        <v>36</v>
+      </c>
+      <c r="Q5">
+        <v>6</v>
+      </c>
+      <c r="R5">
+        <v>73</v>
+      </c>
+      <c r="S5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
-        <v>459</v>
+        <v>680</v>
       </c>
       <c r="C6">
         <v>40</v>
@@ -9544,14 +9875,29 @@
       <c r="N6">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O6">
+        <v>76</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>53</v>
+      </c>
+      <c r="R6">
+        <v>38</v>
+      </c>
+      <c r="S6">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
-        <v>551</v>
+        <v>806</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -9589,14 +9935,29 @@
       <c r="N7">
         <v>45</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O7">
+        <v>77</v>
+      </c>
+      <c r="P7">
+        <v>36</v>
+      </c>
+      <c r="Q7">
+        <v>53</v>
+      </c>
+      <c r="R7">
+        <v>36</v>
+      </c>
+      <c r="S7">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
-        <v>511</v>
+        <v>764</v>
       </c>
       <c r="C8">
         <v>58</v>
@@ -9634,14 +9995,29 @@
       <c r="N8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O8">
+        <v>76</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>52</v>
+      </c>
+      <c r="R8">
+        <v>73</v>
+      </c>
+      <c r="S8">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
-        <v>529</v>
+        <v>790</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -9679,14 +10055,29 @@
       <c r="N9">
         <v>45</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O9">
+        <v>75</v>
+      </c>
+      <c r="P9">
+        <v>36</v>
+      </c>
+      <c r="Q9">
+        <v>53</v>
+      </c>
+      <c r="R9">
+        <v>45</v>
+      </c>
+      <c r="S9">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
-        <v>516</v>
+        <v>784</v>
       </c>
       <c r="C10">
         <v>58</v>
@@ -9724,14 +10115,29 @@
       <c r="N10">
         <v>45</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O10">
+        <v>58</v>
+      </c>
+      <c r="P10">
+        <v>35</v>
+      </c>
+      <c r="Q10">
+        <v>52</v>
+      </c>
+      <c r="R10">
+        <v>72</v>
+      </c>
+      <c r="S10">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
-        <v>681</v>
+        <v>861</v>
       </c>
       <c r="C11">
         <v>52</v>
@@ -9769,14 +10175,29 @@
       <c r="N11">
         <v>45</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O11">
+        <v>34</v>
+      </c>
+      <c r="P11">
+        <v>17</v>
+      </c>
+      <c r="Q11">
+        <v>4</v>
+      </c>
+      <c r="R11">
+        <v>72</v>
+      </c>
+      <c r="S11">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
-        <v>546</v>
+        <v>755</v>
       </c>
       <c r="C12">
         <v>38</v>
@@ -9814,14 +10235,29 @@
       <c r="N12">
         <v>34</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O12">
+        <v>53</v>
+      </c>
+      <c r="P12">
+        <v>31</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>73</v>
+      </c>
+      <c r="S12">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
-        <v>536</v>
+        <v>810</v>
       </c>
       <c r="C13">
         <v>55</v>
@@ -9859,14 +10295,29 @@
       <c r="N13">
         <v>45</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O13">
+        <v>67</v>
+      </c>
+      <c r="P13">
+        <v>36</v>
+      </c>
+      <c r="Q13">
+        <v>52</v>
+      </c>
+      <c r="R13">
+        <v>72</v>
+      </c>
+      <c r="S13">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
-        <v>333</v>
+        <v>579</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -9904,14 +10355,29 @@
       <c r="N14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O14">
+        <v>75</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>53</v>
+      </c>
+      <c r="R14">
+        <v>72</v>
+      </c>
+      <c r="S14">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
-        <v>547</v>
+        <v>658</v>
       </c>
       <c r="C15">
         <v>57</v>
@@ -9949,14 +10415,29 @@
       <c r="N15">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>14</v>
+      </c>
+      <c r="R15">
+        <v>73</v>
+      </c>
+      <c r="S15">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -9994,14 +10475,29 @@
       <c r="N16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>44</v>
+      </c>
+      <c r="R16">
+        <v>38</v>
+      </c>
+      <c r="S16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
-        <v>353</v>
+        <v>568</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -10039,14 +10535,29 @@
       <c r="N17">
         <v>44</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O17">
+        <v>11</v>
+      </c>
+      <c r="P17">
+        <v>35</v>
+      </c>
+      <c r="Q17">
+        <v>46</v>
+      </c>
+      <c r="R17">
+        <v>72</v>
+      </c>
+      <c r="S17">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>55</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
-        <v>469</v>
+        <v>719</v>
       </c>
       <c r="C18">
         <v>58</v>
@@ -10084,14 +10595,29 @@
       <c r="N18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O18">
+        <v>63</v>
+      </c>
+      <c r="P18">
+        <v>35</v>
+      </c>
+      <c r="Q18">
+        <v>28</v>
+      </c>
+      <c r="R18">
+        <v>72</v>
+      </c>
+      <c r="S18">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>44</v>
       </c>
       <c r="B19">
         <f t="shared" si="0"/>
-        <v>531</v>
+        <v>707</v>
       </c>
       <c r="C19">
         <v>56</v>
@@ -10129,14 +10655,29 @@
       <c r="N19">
         <v>44</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O19">
+        <v>37</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>51</v>
+      </c>
+      <c r="R19">
+        <v>36</v>
+      </c>
+      <c r="S19">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
-        <v>660</v>
+        <v>889</v>
       </c>
       <c r="C20">
         <v>57</v>
@@ -10174,8 +10715,23 @@
       <c r="N20">
         <v>44</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O20">
+        <v>74</v>
+      </c>
+      <c r="P20">
+        <v>35</v>
+      </c>
+      <c r="Q20">
+        <v>25</v>
+      </c>
+      <c r="R20">
+        <v>44</v>
+      </c>
+      <c r="S20">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>64</v>
       </c>
@@ -10218,6 +10774,21 @@
       </c>
       <c r="N21">
         <v>7</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10228,15 +10799,15 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7053FD00-70E4-44ED-874D-48591AC61FE1}">
   <dimension ref="A1:S24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10295,7 +10866,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -10304,7 +10875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -10313,7 +10884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -10322,7 +10893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -10331,7 +10902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -10340,7 +10911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -10349,7 +10920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -10358,7 +10929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -10367,7 +10938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -10376,7 +10947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -10385,7 +10956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -10394,7 +10965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -10403,7 +10974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -10412,7 +10983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -10421,7 +10992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -10430,7 +11001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -10439,7 +11010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -10448,7 +11019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -10457,7 +11028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -10466,7 +11037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -10475,7 +11046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -10484,7 +11055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -10493,7 +11064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -10510,13 +11081,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D4303C-7F1D-4CBD-BF56-16C815E789BE}">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10524,122 +11095,122 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -10652,12 +11223,12 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E80DB57-1D34-4995-8AA7-BD186A2BDBE8}">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10665,127 +11236,127 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>66</v>
       </c>
@@ -10798,137 +11369,137 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95F0FCB7-825F-41B0-8DBE-275FB691B4D1}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>73</v>
       </c>
@@ -10941,147 +11512,147 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C60C079E-583C-4AF5-A6A9-C3E86F60AFD7}">
   <dimension ref="A1:A28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>79</v>
       </c>
@@ -11094,137 +11665,137 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9C6E86-EC8A-4EA5-A30B-4A7F0858E0A5}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>70</v>
       </c>
@@ -11237,122 +11808,122 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5342EC0-9A20-4134-BF81-DC6CEEC14B92}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>85</v>
       </c>
@@ -11365,16 +11936,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0EC39A2-025A-41B3-9C60-22F202BB8868}">
   <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11430,7 +12001,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -11495,137 +12066,137 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F76B976-1DE3-4828-AFA3-C2C8CE6A8C8D}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>92</v>
       </c>
@@ -11638,147 +12209,147 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FD15434-4874-452F-8199-FC863C296E8B}">
   <dimension ref="A1:A28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -11791,152 +12362,152 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B951F07-E9BC-4825-9AA7-DCA2D6A9E9B8}">
   <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>95</v>
       </c>
@@ -11949,137 +12520,137 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED86059-0F40-42A6-AE6A-E4A8243B3C21}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>15</v>
       </c>
@@ -12092,127 +12663,127 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B828EF67-0DDF-4C73-BB7C-135261ED3818}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>109</v>
       </c>
@@ -12225,127 +12796,127 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7D05EA9-09C8-45DF-9887-5028388B0199}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>113</v>
       </c>
@@ -12358,117 +12929,117 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AB2F14C-4266-4398-862F-517EC6F2BF68}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>113</v>
       </c>
@@ -12481,132 +13052,132 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9081B27-A4FF-4FDB-A545-8BEAAEB98497}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>123</v>
       </c>
@@ -12619,127 +13190,127 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D47B59A-B1BE-4472-A7E7-70223D1707FA}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>127</v>
       </c>
@@ -12752,112 +13323,112 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F202A74-DE9C-4BEE-9BC5-F661CBB67E18}">
   <dimension ref="A1:A21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>129</v>
       </c>
@@ -12870,17 +13441,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA742C1-0B95-4CA1-8FA2-14D0BE967B15}">
   <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12936,7 +13507,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -13001,112 +13572,112 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5FA89E6-064E-4CAF-91E1-B8698E14C23C}">
   <dimension ref="A1:A21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>132</v>
       </c>
@@ -13119,127 +13690,127 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7743BE8-494B-4549-A27B-0B0C0DC916B8}">
   <dimension ref="A1:A24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>135</v>
       </c>
@@ -13252,117 +13823,117 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56826E7E-7CC5-4FC4-AA7B-870479195203}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>138</v>
       </c>
@@ -13375,122 +13946,122 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C16F4FE-A52D-4398-8BE4-A0ECC46C9962}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -13503,122 +14074,122 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A16EA40-13C9-4D0C-A228-ED069B0DFCDE}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>140</v>
       </c>
@@ -13631,132 +14202,132 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A1C5AB-79A4-4A2A-A59C-9F1C1089C3B0}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>146</v>
       </c>
@@ -13770,117 +14341,117 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC85092-DD56-4DFB-A3DE-A66B323B833F}">
   <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>146</v>
       </c>
@@ -13893,122 +14464,122 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{194B9004-BFC1-4A04-AEDF-CD50347CD713}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>124</v>
       </c>
@@ -14022,16 +14593,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D2BC23-0382-4C73-BD55-9C5BF90A5872}">
   <dimension ref="A1:R5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14087,7 +14658,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -14144,7 +14715,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14201,7 +14772,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -14258,7 +14829,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -14323,15 +14894,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD508AD-7632-48CF-B894-9F6914C08CD8}">
   <dimension ref="A1:R9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14387,7 +14958,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -14444,7 +15015,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14501,7 +15072,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -14558,7 +15129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -14615,7 +15186,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -14672,7 +15243,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>55</v>
       </c>
@@ -14729,7 +15300,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -14786,7 +15357,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -14851,13 +15422,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1668A00-6C37-4B7D-B869-26E922968418}">
   <dimension ref="A1:S10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14916,7 +15487,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -14976,7 +15547,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -15036,7 +15607,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -15096,7 +15667,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -15156,7 +15727,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -15216,7 +15787,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>55</v>
       </c>
@@ -15276,7 +15847,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -15336,7 +15907,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -15396,7 +15967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>151</v>
       </c>
@@ -15464,12 +16035,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D405A22-72AA-4B8B-8276-187361E5AFF5}">
   <dimension ref="A1:R12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15525,7 +16096,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -15582,7 +16153,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -15639,7 +16210,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -15696,7 +16267,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -15753,7 +16324,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -15810,7 +16381,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -15867,7 +16438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -15924,7 +16495,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -15981,7 +16552,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -16038,7 +16609,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>47</v>
       </c>
@@ -16095,7 +16666,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>92</v>
       </c>
@@ -16160,12 +16731,12 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D914D4-403F-4B81-B472-8E3F05ADF641}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -16224,7 +16795,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -16284,7 +16855,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -16344,7 +16915,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -16404,7 +16975,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -16464,7 +17035,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -16524,7 +17095,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -16584,7 +17155,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -16644,7 +17215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -16704,7 +17275,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -16764,7 +17335,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -16824,7 +17395,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -16884,7 +17455,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -16944,7 +17515,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -17012,16 +17583,16 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6443FC8D-E56E-407E-83EA-E01E6A3300AE}">
   <dimension ref="A1:R14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -17077,7 +17648,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -17134,7 +17705,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -17191,7 +17762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -17248,7 +17819,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -17305,7 +17876,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -17362,7 +17933,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -17419,7 +17990,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -17476,7 +18047,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -17533,7 +18104,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -17590,7 +18161,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -17647,7 +18218,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -17704,7 +18275,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>47</v>
       </c>
@@ -17761,7 +18332,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>

--- a/Data_Files/Laps_Completed.xlsx
+++ b/Data_Files/Laps_Completed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1296261-DF24-4663-BE8A-A35DC4E115E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FBA74C-54C4-45BD-BDE0-88A7D3B2C3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="1500" windowWidth="16410" windowHeight="14145" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28695" yWindow="1500" windowWidth="16410" windowHeight="14145" firstSheet="6" activeTab="13" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Laps_Completed" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="153">
   <si>
     <t>Driver</t>
   </si>
@@ -1725,6 +1725,9 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="AA2">
+        <v>1090</v>
+      </c>
       <c r="AB2">
         <v>1005</v>
       </c>
@@ -1763,6 +1766,9 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
+      <c r="AA3">
+        <v>822</v>
+      </c>
       <c r="AB3">
         <v>928</v>
       </c>
@@ -1801,6 +1807,9 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
+      <c r="AA4">
+        <v>792</v>
+      </c>
       <c r="AB4">
         <v>756</v>
       </c>
@@ -1839,6 +1848,9 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
+      <c r="AA5">
+        <v>941</v>
+      </c>
       <c r="AB5">
         <v>926</v>
       </c>
@@ -1877,6 +1889,9 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
+      <c r="AA6">
+        <v>990</v>
+      </c>
       <c r="AB6">
         <v>680</v>
       </c>
@@ -1915,6 +1930,9 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
+      <c r="AA7">
+        <v>973</v>
+      </c>
       <c r="AB7">
         <v>806</v>
       </c>
@@ -1953,6 +1971,9 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
+      <c r="AA8">
+        <v>726</v>
+      </c>
       <c r="AB8" s="1">
         <v>0</v>
       </c>
@@ -1989,6 +2010,9 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
+      <c r="AA9">
+        <v>965</v>
+      </c>
       <c r="AB9">
         <v>764</v>
       </c>
@@ -2027,6 +2051,9 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
+      <c r="AA10">
+        <v>794</v>
+      </c>
       <c r="AB10">
         <v>790</v>
       </c>
@@ -2065,6 +2092,9 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
+      <c r="AA11">
+        <v>697</v>
+      </c>
       <c r="AB11">
         <v>784</v>
       </c>
@@ -2103,6 +2133,9 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
+      <c r="AA12">
+        <v>862</v>
+      </c>
       <c r="AB12">
         <v>861</v>
       </c>
@@ -2141,6 +2174,9 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
+      <c r="AA13">
+        <v>834</v>
+      </c>
       <c r="AB13">
         <v>755</v>
       </c>
@@ -2179,6 +2215,9 @@
       <c r="A14" t="s">
         <v>13</v>
       </c>
+      <c r="AA14">
+        <v>760</v>
+      </c>
       <c r="AB14" s="1">
         <v>0</v>
       </c>
@@ -2217,6 +2256,9 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
+      <c r="AA15">
+        <v>722</v>
+      </c>
       <c r="AB15">
         <v>810</v>
       </c>
@@ -2255,6 +2297,9 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
+      <c r="AA16">
+        <v>694</v>
+      </c>
       <c r="AB16">
         <v>579</v>
       </c>
@@ -2293,6 +2338,9 @@
       <c r="A17" t="s">
         <v>16</v>
       </c>
+      <c r="AA17">
+        <v>815</v>
+      </c>
       <c r="AB17">
         <v>658</v>
       </c>
@@ -2331,6 +2379,9 @@
       <c r="A18" t="s">
         <v>17</v>
       </c>
+      <c r="AA18">
+        <v>781</v>
+      </c>
       <c r="AB18" s="1">
         <v>0</v>
       </c>
@@ -2369,6 +2420,9 @@
       <c r="A19" t="s">
         <v>85</v>
       </c>
+      <c r="AA19">
+        <v>75</v>
+      </c>
       <c r="AB19" s="1">
         <v>0</v>
       </c>
@@ -2407,6 +2461,9 @@
       <c r="A20" t="s">
         <v>18</v>
       </c>
+      <c r="AA20">
+        <v>513</v>
+      </c>
       <c r="AB20">
         <v>132</v>
       </c>
@@ -2445,6 +2502,9 @@
       <c r="A21" t="s">
         <v>19</v>
       </c>
+      <c r="AA21">
+        <v>358</v>
+      </c>
       <c r="AB21">
         <v>568</v>
       </c>
@@ -2483,6 +2543,9 @@
       <c r="A22" t="s">
         <v>55</v>
       </c>
+      <c r="AA22">
+        <v>552</v>
+      </c>
       <c r="AB22">
         <v>719</v>
       </c>
@@ -2521,6 +2584,9 @@
       <c r="A23" t="s">
         <v>21</v>
       </c>
+      <c r="AA23">
+        <v>924</v>
+      </c>
       <c r="AB23">
         <v>0</v>
       </c>
@@ -2559,6 +2625,9 @@
       <c r="A24" t="s">
         <v>22</v>
       </c>
+      <c r="AA24">
+        <v>639</v>
+      </c>
       <c r="AB24" s="1">
         <v>0</v>
       </c>
@@ -2597,6 +2666,9 @@
       <c r="A25" t="s">
         <v>44</v>
       </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
       <c r="AB25">
         <v>707</v>
       </c>
@@ -2635,7 +2707,9 @@
       <c r="A26" t="s">
         <v>45</v>
       </c>
-      <c r="AA26" s="1"/>
+      <c r="AA26" s="1">
+        <v>0</v>
+      </c>
       <c r="AB26" s="1">
         <v>0</v>
       </c>
@@ -2674,7 +2748,9 @@
       <c r="A27" t="s">
         <v>46</v>
       </c>
-      <c r="AA27" s="1"/>
+      <c r="AA27" s="1">
+        <v>0</v>
+      </c>
       <c r="AB27" s="1">
         <v>0</v>
       </c>
@@ -2713,6 +2789,9 @@
       <c r="A28" t="s">
         <v>47</v>
       </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
       <c r="AB28">
         <v>889</v>
       </c>
@@ -2751,7 +2830,9 @@
       <c r="A29" t="s">
         <v>48</v>
       </c>
-      <c r="AA29" s="1"/>
+      <c r="AA29" s="1">
+        <v>0</v>
+      </c>
       <c r="AB29" s="1">
         <v>0</v>
       </c>
@@ -2790,7 +2871,9 @@
       <c r="A30" t="s">
         <v>49</v>
       </c>
-      <c r="AA30" s="1"/>
+      <c r="AA30" s="1">
+        <v>0</v>
+      </c>
       <c r="AB30" s="1">
         <v>0</v>
       </c>
@@ -2829,6 +2912,9 @@
       <c r="A31" t="s">
         <v>53</v>
       </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
       <c r="AB31">
         <v>0</v>
       </c>
@@ -2867,7 +2953,9 @@
       <c r="A32" t="s">
         <v>57</v>
       </c>
-      <c r="AA32" s="1"/>
+      <c r="AA32" s="1">
+        <v>0</v>
+      </c>
       <c r="AB32" s="1">
         <v>0</v>
       </c>
@@ -2906,7 +2994,9 @@
       <c r="A33" t="s">
         <v>58</v>
       </c>
-      <c r="AA33" s="1"/>
+      <c r="AA33" s="1">
+        <v>0</v>
+      </c>
       <c r="AB33" s="1">
         <v>0</v>
       </c>
@@ -2945,7 +3035,9 @@
       <c r="A34" t="s">
         <v>59</v>
       </c>
-      <c r="AA34" s="1"/>
+      <c r="AA34" s="1">
+        <v>0</v>
+      </c>
       <c r="AB34" s="1">
         <v>0</v>
       </c>
@@ -2984,7 +3076,9 @@
       <c r="A35" t="s">
         <v>60</v>
       </c>
-      <c r="AA35" s="1"/>
+      <c r="AA35" s="1">
+        <v>0</v>
+      </c>
       <c r="AB35" s="1">
         <v>0</v>
       </c>
@@ -3023,7 +3117,9 @@
       <c r="A36" t="s">
         <v>61</v>
       </c>
-      <c r="AA36" s="1"/>
+      <c r="AA36" s="1">
+        <v>0</v>
+      </c>
       <c r="AB36" s="1">
         <v>0</v>
       </c>
@@ -3063,7 +3159,9 @@
         <v>62</v>
       </c>
       <c r="Z37" s="1"/>
-      <c r="AA37" s="1"/>
+      <c r="AA37" s="1">
+        <v>0</v>
+      </c>
       <c r="AB37" s="1">
         <v>0</v>
       </c>
@@ -3103,7 +3201,9 @@
         <v>63</v>
       </c>
       <c r="Z38" s="1"/>
-      <c r="AA38" s="1"/>
+      <c r="AA38" s="1">
+        <v>0</v>
+      </c>
       <c r="AB38" s="1">
         <v>0</v>
       </c>
@@ -3142,6 +3242,9 @@
       <c r="A39" t="s">
         <v>64</v>
       </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
       <c r="AB39">
         <v>75</v>
       </c>
@@ -3181,7 +3284,9 @@
         <v>65</v>
       </c>
       <c r="Z40" s="1"/>
-      <c r="AA40" s="1"/>
+      <c r="AA40" s="1">
+        <v>0</v>
+      </c>
       <c r="AB40" s="1">
         <v>0</v>
       </c>
@@ -3221,7 +3326,9 @@
         <v>66</v>
       </c>
       <c r="Z41" s="1"/>
-      <c r="AA41" s="1"/>
+      <c r="AA41" s="1">
+        <v>0</v>
+      </c>
       <c r="AB41" s="1">
         <v>0</v>
       </c>
@@ -3262,7 +3369,9 @@
       </c>
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
-      <c r="AA42" s="1"/>
+      <c r="AA42" s="1">
+        <v>0</v>
+      </c>
       <c r="AB42" s="1">
         <v>0</v>
       </c>
@@ -3301,6 +3410,9 @@
       <c r="A43" t="s">
         <v>68</v>
       </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
       <c r="AB43">
         <v>0</v>
       </c>
@@ -3341,7 +3453,9 @@
       </c>
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
-      <c r="AA44" s="1"/>
+      <c r="AA44" s="1">
+        <v>0</v>
+      </c>
       <c r="AB44" s="1">
         <v>0</v>
       </c>
@@ -3382,7 +3496,9 @@
       </c>
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
-      <c r="AA45" s="1"/>
+      <c r="AA45" s="1">
+        <v>0</v>
+      </c>
       <c r="AB45" s="1">
         <v>0</v>
       </c>
@@ -3423,7 +3539,9 @@
       </c>
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
-      <c r="AA46" s="1"/>
+      <c r="AA46" s="1">
+        <v>0</v>
+      </c>
       <c r="AB46" s="1">
         <v>0</v>
       </c>
@@ -3464,7 +3582,9 @@
       </c>
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
-      <c r="AA47" s="1"/>
+      <c r="AA47" s="1">
+        <v>0</v>
+      </c>
       <c r="AB47" s="1">
         <v>0</v>
       </c>
@@ -3505,7 +3625,9 @@
       </c>
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
-      <c r="AA48" s="1"/>
+      <c r="AA48" s="1">
+        <v>0</v>
+      </c>
       <c r="AB48" s="1">
         <v>0</v>
       </c>
@@ -3547,7 +3669,9 @@
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
-      <c r="AA49" s="1"/>
+      <c r="AA49" s="1">
+        <v>0</v>
+      </c>
       <c r="AB49" s="1">
         <v>0</v>
       </c>
@@ -3589,7 +3713,9 @@
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
-      <c r="AA50" s="1"/>
+      <c r="AA50" s="1">
+        <v>0</v>
+      </c>
       <c r="AB50" s="1">
         <v>0</v>
       </c>
@@ -3631,7 +3757,9 @@
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
-      <c r="AA51" s="1"/>
+      <c r="AA51" s="1">
+        <v>0</v>
+      </c>
       <c r="AB51" s="1">
         <v>0</v>
       </c>
@@ -3673,7 +3801,9 @@
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
-      <c r="AA52" s="1"/>
+      <c r="AA52" s="1">
+        <v>0</v>
+      </c>
       <c r="AB52" s="1">
         <v>0</v>
       </c>
@@ -3715,7 +3845,9 @@
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
-      <c r="AA53" s="1"/>
+      <c r="AA53" s="1">
+        <v>0</v>
+      </c>
       <c r="AB53" s="1">
         <v>0</v>
       </c>
@@ -3757,7 +3889,9 @@
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
-      <c r="AA54" s="1"/>
+      <c r="AA54" s="1">
+        <v>0</v>
+      </c>
       <c r="AB54" s="1">
         <v>0</v>
       </c>
@@ -3800,7 +3934,9 @@
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
-      <c r="AA55" s="1"/>
+      <c r="AA55" s="1">
+        <v>0</v>
+      </c>
       <c r="AB55" s="1">
         <v>0</v>
       </c>
@@ -3843,7 +3979,9 @@
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
-      <c r="AA56" s="1"/>
+      <c r="AA56" s="1">
+        <v>0</v>
+      </c>
       <c r="AB56" s="1">
         <v>0</v>
       </c>
@@ -3886,7 +4024,9 @@
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
-      <c r="AA57" s="1"/>
+      <c r="AA57" s="1">
+        <v>0</v>
+      </c>
       <c r="AB57" s="1">
         <v>0</v>
       </c>
@@ -3929,7 +4069,9 @@
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
-      <c r="AA58" s="1"/>
+      <c r="AA58" s="1">
+        <v>0</v>
+      </c>
       <c r="AB58" s="1">
         <v>0</v>
       </c>
@@ -3972,7 +4114,9 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
-      <c r="AA59" s="1"/>
+      <c r="AA59" s="1">
+        <v>0</v>
+      </c>
       <c r="AB59" s="1">
         <v>0</v>
       </c>
@@ -4016,7 +4160,9 @@
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
-      <c r="AA60" s="1"/>
+      <c r="AA60" s="1">
+        <v>0</v>
+      </c>
       <c r="AB60" s="1">
         <v>0</v>
       </c>
@@ -4060,7 +4206,9 @@
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
-      <c r="AA61" s="1"/>
+      <c r="AA61" s="1">
+        <v>0</v>
+      </c>
       <c r="AB61" s="1">
         <v>0</v>
       </c>
@@ -4105,7 +4253,9 @@
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
-      <c r="AA62" s="1"/>
+      <c r="AA62" s="1">
+        <v>0</v>
+      </c>
       <c r="AB62" s="1">
         <v>0</v>
       </c>
@@ -4150,7 +4300,9 @@
       <c r="X63" s="1"/>
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
-      <c r="AA63" s="1"/>
+      <c r="AA63" s="1">
+        <v>0</v>
+      </c>
       <c r="AB63" s="1">
         <v>0</v>
       </c>
@@ -4195,7 +4347,9 @@
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
-      <c r="AA64" s="1"/>
+      <c r="AA64" s="1">
+        <v>0</v>
+      </c>
       <c r="AB64" s="1">
         <v>0</v>
       </c>
@@ -4240,7 +4394,9 @@
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
-      <c r="AA65" s="1"/>
+      <c r="AA65" s="1">
+        <v>0</v>
+      </c>
       <c r="AB65" s="1">
         <v>0</v>
       </c>
@@ -4345,7 +4501,9 @@
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
-      <c r="AA67" s="1"/>
+      <c r="AA67" s="1">
+        <v>0</v>
+      </c>
       <c r="AB67" s="1">
         <v>0</v>
       </c>
@@ -4391,7 +4549,9 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
-      <c r="AA68" s="1"/>
+      <c r="AA68" s="1">
+        <v>0</v>
+      </c>
       <c r="AB68" s="1">
         <v>0</v>
       </c>
@@ -4437,7 +4597,9 @@
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
-      <c r="AA69" s="1"/>
+      <c r="AA69" s="1">
+        <v>0</v>
+      </c>
       <c r="AB69" s="1">
         <v>0</v>
       </c>
@@ -4483,7 +4645,9 @@
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
-      <c r="AA70" s="1"/>
+      <c r="AA70" s="1">
+        <v>0</v>
+      </c>
       <c r="AB70" s="1">
         <v>0</v>
       </c>
@@ -4529,7 +4693,9 @@
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
-      <c r="AA71" s="1"/>
+      <c r="AA71" s="1">
+        <v>0</v>
+      </c>
       <c r="AB71" s="1">
         <v>0</v>
       </c>
@@ -4576,7 +4742,9 @@
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
-      <c r="AA72" s="1"/>
+      <c r="AA72" s="1">
+        <v>0</v>
+      </c>
       <c r="AB72" s="1">
         <v>0</v>
       </c>
@@ -4623,7 +4791,9 @@
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
-      <c r="AA73" s="1"/>
+      <c r="AA73" s="1">
+        <v>0</v>
+      </c>
       <c r="AB73" s="1">
         <v>0</v>
       </c>
@@ -4670,7 +4840,9 @@
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
-      <c r="AA74" s="1"/>
+      <c r="AA74" s="1">
+        <v>0</v>
+      </c>
       <c r="AB74" s="1">
         <v>0</v>
       </c>
@@ -4717,7 +4889,9 @@
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
-      <c r="AA75" s="1"/>
+      <c r="AA75" s="1">
+        <v>0</v>
+      </c>
       <c r="AB75" s="1">
         <v>0</v>
       </c>
@@ -4764,7 +4938,9 @@
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
-      <c r="AA76" s="1"/>
+      <c r="AA76" s="1">
+        <v>0</v>
+      </c>
       <c r="AB76" s="1">
         <v>0</v>
       </c>
@@ -4812,7 +4988,9 @@
       <c r="X77" s="1"/>
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
-      <c r="AA77" s="1"/>
+      <c r="AA77" s="1">
+        <v>0</v>
+      </c>
       <c r="AB77" s="1">
         <v>0</v>
       </c>
@@ -4860,7 +5038,9 @@
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
-      <c r="AA78" s="1"/>
+      <c r="AA78" s="1">
+        <v>0</v>
+      </c>
       <c r="AB78" s="1">
         <v>0</v>
       </c>
@@ -4909,7 +5089,9 @@
       <c r="X79" s="1"/>
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
-      <c r="AA79" s="1"/>
+      <c r="AA79" s="1">
+        <v>0</v>
+      </c>
       <c r="AB79" s="1">
         <v>0</v>
       </c>
@@ -4958,7 +5140,9 @@
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
-      <c r="AA80" s="1"/>
+      <c r="AA80" s="1">
+        <v>0</v>
+      </c>
       <c r="AB80" s="1">
         <v>0</v>
       </c>
@@ -5007,7 +5191,9 @@
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
-      <c r="AA81" s="1"/>
+      <c r="AA81" s="1">
+        <v>0</v>
+      </c>
       <c r="AB81" s="1">
         <v>0</v>
       </c>
@@ -5056,7 +5242,9 @@
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
-      <c r="AA82" s="1"/>
+      <c r="AA82" s="1">
+        <v>0</v>
+      </c>
       <c r="AB82" s="1">
         <v>0</v>
       </c>
@@ -5105,7 +5293,9 @@
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
-      <c r="AA83" s="1"/>
+      <c r="AA83" s="1">
+        <v>0</v>
+      </c>
       <c r="AB83" s="1">
         <v>0</v>
       </c>
@@ -5155,7 +5345,9 @@
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
-      <c r="AA84" s="1"/>
+      <c r="AA84" s="1">
+        <v>0</v>
+      </c>
       <c r="AB84" s="1">
         <v>0</v>
       </c>
@@ -5205,7 +5397,9 @@
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
-      <c r="AA85" s="1"/>
+      <c r="AA85" s="1">
+        <v>0</v>
+      </c>
       <c r="AB85" s="1">
         <v>0</v>
       </c>
@@ -5255,7 +5449,9 @@
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
-      <c r="AA86" s="1"/>
+      <c r="AA86" s="1">
+        <v>0</v>
+      </c>
       <c r="AB86" s="1">
         <v>0</v>
       </c>
@@ -5305,7 +5501,9 @@
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
-      <c r="AA87" s="1"/>
+      <c r="AA87" s="1">
+        <v>0</v>
+      </c>
       <c r="AB87" s="1">
         <v>0</v>
       </c>
@@ -5356,7 +5554,9 @@
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
-      <c r="AA88" s="1"/>
+      <c r="AA88" s="1">
+        <v>0</v>
+      </c>
       <c r="AB88" s="1">
         <v>0</v>
       </c>
@@ -5407,7 +5607,9 @@
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
-      <c r="AA89" s="1"/>
+      <c r="AA89" s="1">
+        <v>0</v>
+      </c>
       <c r="AB89" s="1">
         <v>0</v>
       </c>
@@ -5458,7 +5660,9 @@
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
-      <c r="AA90" s="1"/>
+      <c r="AA90" s="1">
+        <v>0</v>
+      </c>
       <c r="AB90" s="1">
         <v>0</v>
       </c>
@@ -5509,7 +5713,9 @@
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
-      <c r="AA91" s="1"/>
+      <c r="AA91" s="1">
+        <v>0</v>
+      </c>
       <c r="AB91" s="1">
         <v>0</v>
       </c>
@@ -5560,7 +5766,9 @@
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
-      <c r="AA92" s="1"/>
+      <c r="AA92" s="1">
+        <v>0</v>
+      </c>
       <c r="AB92" s="1">
         <v>0</v>
       </c>
@@ -5612,7 +5820,9 @@
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
-      <c r="AA93" s="1"/>
+      <c r="AA93" s="1">
+        <v>0</v>
+      </c>
       <c r="AB93" s="1">
         <v>0</v>
       </c>
@@ -5664,7 +5874,9 @@
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
-      <c r="AA94" s="1"/>
+      <c r="AA94" s="1">
+        <v>0</v>
+      </c>
       <c r="AB94" s="1">
         <v>0</v>
       </c>
@@ -5716,7 +5928,9 @@
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
-      <c r="AA95" s="1"/>
+      <c r="AA95" s="1">
+        <v>0</v>
+      </c>
       <c r="AB95" s="1">
         <v>0</v>
       </c>
@@ -5768,7 +5982,9 @@
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
-      <c r="AA96" s="1"/>
+      <c r="AA96" s="1">
+        <v>0</v>
+      </c>
       <c r="AB96" s="1">
         <v>0</v>
       </c>
@@ -5820,7 +6036,9 @@
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
-      <c r="AA97" s="1"/>
+      <c r="AA97" s="1">
+        <v>0</v>
+      </c>
       <c r="AB97" s="1">
         <v>0</v>
       </c>
@@ -5873,7 +6091,9 @@
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
-      <c r="AA98" s="1"/>
+      <c r="AA98" s="1">
+        <v>0</v>
+      </c>
       <c r="AB98" s="1">
         <v>0</v>
       </c>
@@ -5926,7 +6146,9 @@
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
-      <c r="AA99" s="1"/>
+      <c r="AA99" s="1">
+        <v>0</v>
+      </c>
       <c r="AB99" s="1">
         <v>0</v>
       </c>
@@ -5979,7 +6201,9 @@
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
-      <c r="AA100" s="1"/>
+      <c r="AA100" s="1">
+        <v>0</v>
+      </c>
       <c r="AB100" s="1">
         <v>0</v>
       </c>
@@ -6032,7 +6256,9 @@
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
-      <c r="AA101" s="1"/>
+      <c r="AA101" s="1">
+        <v>0</v>
+      </c>
       <c r="AB101" s="1">
         <v>0</v>
       </c>
@@ -6086,7 +6312,9 @@
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
-      <c r="AA102" s="1"/>
+      <c r="AA102" s="1">
+        <v>0</v>
+      </c>
       <c r="AB102" s="1">
         <v>0</v>
       </c>
@@ -6140,7 +6368,9 @@
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
-      <c r="AA103" s="1"/>
+      <c r="AA103" s="1">
+        <v>0</v>
+      </c>
       <c r="AB103" s="1">
         <v>0</v>
       </c>
@@ -6195,7 +6425,9 @@
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
-      <c r="AA104" s="1"/>
+      <c r="AA104" s="1">
+        <v>0</v>
+      </c>
       <c r="AB104" s="1">
         <v>0</v>
       </c>
@@ -6250,7 +6482,9 @@
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
-      <c r="AA105" s="1"/>
+      <c r="AA105" s="1">
+        <v>0</v>
+      </c>
       <c r="AB105" s="1">
         <v>0</v>
       </c>
@@ -6305,7 +6539,9 @@
       <c r="X106" s="1"/>
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
-      <c r="AA106" s="1"/>
+      <c r="AA106" s="1">
+        <v>0</v>
+      </c>
       <c r="AB106" s="1">
         <v>0</v>
       </c>
@@ -6361,7 +6597,9 @@
       <c r="X107" s="1"/>
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
-      <c r="AA107" s="1"/>
+      <c r="AA107" s="1">
+        <v>0</v>
+      </c>
       <c r="AB107" s="1">
         <v>0</v>
       </c>
@@ -6417,7 +6655,9 @@
       <c r="X108" s="1"/>
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
-      <c r="AA108" s="1"/>
+      <c r="AA108" s="1">
+        <v>0</v>
+      </c>
       <c r="AB108" s="1">
         <v>0</v>
       </c>
@@ -6473,7 +6713,9 @@
       <c r="X109" s="1"/>
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
-      <c r="AA109" s="1"/>
+      <c r="AA109" s="1">
+        <v>0</v>
+      </c>
       <c r="AB109" s="1">
         <v>0</v>
       </c>
@@ -6530,7 +6772,9 @@
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
-      <c r="AA110" s="1"/>
+      <c r="AA110" s="1">
+        <v>0</v>
+      </c>
       <c r="AB110" s="1">
         <v>0</v>
       </c>
@@ -6587,7 +6831,9 @@
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
-      <c r="AA111" s="1"/>
+      <c r="AA111" s="1">
+        <v>0</v>
+      </c>
       <c r="AB111" s="1">
         <v>0</v>
       </c>
@@ -6644,7 +6890,9 @@
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
-      <c r="AA112" s="1"/>
+      <c r="AA112" s="1">
+        <v>0</v>
+      </c>
       <c r="AB112" s="1">
         <v>0</v>
       </c>
@@ -6702,7 +6950,9 @@
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
-      <c r="AA113" s="1"/>
+      <c r="AA113" s="1">
+        <v>0</v>
+      </c>
       <c r="AB113" s="1">
         <v>0</v>
       </c>
@@ -6760,7 +7010,9 @@
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
-      <c r="AA114" s="1"/>
+      <c r="AA114" s="1">
+        <v>0</v>
+      </c>
       <c r="AB114" s="1">
         <v>0</v>
       </c>
@@ -6819,7 +7071,9 @@
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
-      <c r="AA115" s="1"/>
+      <c r="AA115" s="1">
+        <v>0</v>
+      </c>
       <c r="AB115" s="1">
         <v>0</v>
       </c>
@@ -6878,7 +7132,9 @@
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
-      <c r="AA116" s="1"/>
+      <c r="AA116" s="1">
+        <v>0</v>
+      </c>
       <c r="AB116" s="1">
         <v>0</v>
       </c>
@@ -6937,7 +7193,9 @@
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
-      <c r="AA117" s="1"/>
+      <c r="AA117" s="1">
+        <v>0</v>
+      </c>
       <c r="AB117" s="1">
         <v>0</v>
       </c>
@@ -6997,7 +7255,9 @@
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
-      <c r="AA118" s="1"/>
+      <c r="AA118" s="1">
+        <v>0</v>
+      </c>
       <c r="AB118" s="1">
         <v>0</v>
       </c>
@@ -7057,7 +7317,9 @@
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
-      <c r="AA119" s="1"/>
+      <c r="AA119" s="1">
+        <v>0</v>
+      </c>
       <c r="AB119" s="1">
         <v>0</v>
       </c>
@@ -7117,7 +7379,9 @@
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
-      <c r="AA120" s="1"/>
+      <c r="AA120" s="1">
+        <v>0</v>
+      </c>
       <c r="AB120" s="1">
         <v>0</v>
       </c>
@@ -7178,7 +7442,9 @@
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
-      <c r="AA121" s="1"/>
+      <c r="AA121" s="1">
+        <v>0</v>
+      </c>
       <c r="AB121" s="1">
         <v>0</v>
       </c>
@@ -7239,7 +7505,9 @@
       <c r="X122" s="1"/>
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
-      <c r="AA122" s="1"/>
+      <c r="AA122" s="1">
+        <v>0</v>
+      </c>
       <c r="AB122" s="1">
         <v>0</v>
       </c>
@@ -7300,7 +7568,9 @@
       <c r="X123" s="1"/>
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
-      <c r="AA123" s="1"/>
+      <c r="AA123" s="1">
+        <v>0</v>
+      </c>
       <c r="AB123" s="1">
         <v>0</v>
       </c>
@@ -7362,7 +7632,9 @@
       <c r="X124" s="1"/>
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
-      <c r="AA124" s="1"/>
+      <c r="AA124" s="1">
+        <v>0</v>
+      </c>
       <c r="AB124" s="1">
         <v>0</v>
       </c>
@@ -10802,9 +11074,22 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -10872,7 +11157,58 @@
       </c>
       <c r="B2">
         <f>SUM(C2:C2:S2)</f>
-        <v>0</v>
+        <v>1090</v>
+      </c>
+      <c r="C2">
+        <v>58</v>
+      </c>
+      <c r="D2">
+        <v>56</v>
+      </c>
+      <c r="E2">
+        <v>71</v>
+      </c>
+      <c r="F2">
+        <v>62</v>
+      </c>
+      <c r="G2">
+        <v>65</v>
+      </c>
+      <c r="H2">
+        <v>71</v>
+      </c>
+      <c r="I2">
+        <v>78</v>
+      </c>
+      <c r="J2">
+        <v>70</v>
+      </c>
+      <c r="K2">
+        <v>60</v>
+      </c>
+      <c r="L2">
+        <v>60</v>
+      </c>
+      <c r="M2">
+        <v>72</v>
+      </c>
+      <c r="N2">
+        <v>67</v>
+      </c>
+      <c r="O2">
+        <v>77</v>
+      </c>
+      <c r="P2">
+        <v>44</v>
+      </c>
+      <c r="Q2">
+        <v>53</v>
+      </c>
+      <c r="R2">
+        <v>73</v>
+      </c>
+      <c r="S2">
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -10881,7 +11217,58 @@
       </c>
       <c r="B3">
         <f>SUM(C3:C3:S3)</f>
-        <v>0</v>
+        <v>822</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>39</v>
+      </c>
+      <c r="E3">
+        <v>16</v>
+      </c>
+      <c r="F3">
+        <v>62</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>71</v>
+      </c>
+      <c r="I3">
+        <v>77</v>
+      </c>
+      <c r="J3">
+        <v>70</v>
+      </c>
+      <c r="K3">
+        <v>60</v>
+      </c>
+      <c r="L3">
+        <v>60</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>67</v>
+      </c>
+      <c r="O3">
+        <v>77</v>
+      </c>
+      <c r="P3">
+        <v>44</v>
+      </c>
+      <c r="Q3">
+        <v>53</v>
+      </c>
+      <c r="R3">
+        <v>73</v>
+      </c>
+      <c r="S3">
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -10890,7 +11277,58 @@
       </c>
       <c r="B4">
         <f>SUM(C4:C4:S4)</f>
-        <v>0</v>
+        <v>792</v>
+      </c>
+      <c r="C4">
+        <v>58</v>
+      </c>
+      <c r="D4">
+        <v>24</v>
+      </c>
+      <c r="E4">
+        <v>67</v>
+      </c>
+      <c r="F4">
+        <v>44</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <v>41</v>
+      </c>
+      <c r="J4">
+        <v>70</v>
+      </c>
+      <c r="K4">
+        <v>60</v>
+      </c>
+      <c r="L4">
+        <v>44</v>
+      </c>
+      <c r="M4">
+        <v>72</v>
+      </c>
+      <c r="N4">
+        <v>59</v>
+      </c>
+      <c r="O4">
+        <v>77</v>
+      </c>
+      <c r="P4">
+        <v>35</v>
+      </c>
+      <c r="Q4">
+        <v>29</v>
+      </c>
+      <c r="R4">
+        <v>50</v>
+      </c>
+      <c r="S4">
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -10899,7 +11337,58 @@
       </c>
       <c r="B5">
         <f>SUM(C5:C5:S5)</f>
-        <v>0</v>
+        <v>941</v>
+      </c>
+      <c r="C5">
+        <v>33</v>
+      </c>
+      <c r="D5">
+        <v>15</v>
+      </c>
+      <c r="E5">
+        <v>71</v>
+      </c>
+      <c r="F5">
+        <v>61</v>
+      </c>
+      <c r="G5">
+        <v>65</v>
+      </c>
+      <c r="H5">
+        <v>71</v>
+      </c>
+      <c r="I5">
+        <v>78</v>
+      </c>
+      <c r="J5">
+        <v>70</v>
+      </c>
+      <c r="K5">
+        <v>27</v>
+      </c>
+      <c r="L5">
+        <v>58</v>
+      </c>
+      <c r="M5">
+        <v>72</v>
+      </c>
+      <c r="N5">
+        <v>66</v>
+      </c>
+      <c r="O5">
+        <v>77</v>
+      </c>
+      <c r="P5">
+        <v>44</v>
+      </c>
+      <c r="Q5">
+        <v>53</v>
+      </c>
+      <c r="R5">
+        <v>73</v>
+      </c>
+      <c r="S5">
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -10908,7 +11397,58 @@
       </c>
       <c r="B6">
         <f>SUM(C6:C6:S6)</f>
-        <v>0</v>
+        <v>990</v>
+      </c>
+      <c r="C6">
+        <v>58</v>
+      </c>
+      <c r="D6">
+        <v>56</v>
+      </c>
+      <c r="E6">
+        <v>71</v>
+      </c>
+      <c r="F6">
+        <v>62</v>
+      </c>
+      <c r="G6">
+        <v>65</v>
+      </c>
+      <c r="H6">
+        <v>71</v>
+      </c>
+      <c r="I6">
+        <v>46</v>
+      </c>
+      <c r="J6">
+        <v>56</v>
+      </c>
+      <c r="K6">
+        <v>27</v>
+      </c>
+      <c r="L6">
+        <v>60</v>
+      </c>
+      <c r="M6">
+        <v>72</v>
+      </c>
+      <c r="N6">
+        <v>67</v>
+      </c>
+      <c r="O6">
+        <v>76</v>
+      </c>
+      <c r="P6">
+        <v>44</v>
+      </c>
+      <c r="Q6">
+        <v>33</v>
+      </c>
+      <c r="R6">
+        <v>73</v>
+      </c>
+      <c r="S6">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -10917,7 +11457,58 @@
       </c>
       <c r="B7">
         <f>SUM(C7:C7:S7)</f>
-        <v>0</v>
+        <v>973</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>56</v>
+      </c>
+      <c r="E7">
+        <v>71</v>
+      </c>
+      <c r="F7">
+        <v>62</v>
+      </c>
+      <c r="G7">
+        <v>63</v>
+      </c>
+      <c r="H7">
+        <v>71</v>
+      </c>
+      <c r="I7">
+        <v>78</v>
+      </c>
+      <c r="J7">
+        <v>70</v>
+      </c>
+      <c r="K7">
+        <v>60</v>
+      </c>
+      <c r="L7">
+        <v>59</v>
+      </c>
+      <c r="M7">
+        <v>72</v>
+      </c>
+      <c r="N7">
+        <v>67</v>
+      </c>
+      <c r="O7">
+        <v>77</v>
+      </c>
+      <c r="P7">
+        <v>44</v>
+      </c>
+      <c r="Q7">
+        <v>4</v>
+      </c>
+      <c r="R7">
+        <v>71</v>
+      </c>
+      <c r="S7">
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -10926,7 +11517,58 @@
       </c>
       <c r="B8">
         <f>SUM(C8:C8:S8)</f>
-        <v>0</v>
+        <v>726</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>55</v>
+      </c>
+      <c r="E8">
+        <v>41</v>
+      </c>
+      <c r="F8">
+        <v>61</v>
+      </c>
+      <c r="G8">
+        <v>65</v>
+      </c>
+      <c r="H8">
+        <v>7</v>
+      </c>
+      <c r="I8">
+        <v>63</v>
+      </c>
+      <c r="J8">
+        <v>69</v>
+      </c>
+      <c r="K8">
+        <v>59</v>
+      </c>
+      <c r="L8">
+        <v>59</v>
+      </c>
+      <c r="M8">
+        <v>48</v>
+      </c>
+      <c r="N8">
+        <v>66</v>
+      </c>
+      <c r="O8">
+        <v>77</v>
+      </c>
+      <c r="P8">
+        <v>37</v>
+      </c>
+      <c r="Q8">
+        <v>16</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -10935,7 +11577,58 @@
       </c>
       <c r="B9">
         <f>SUM(C9:C9:S9)</f>
-        <v>0</v>
+        <v>965</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>55</v>
+      </c>
+      <c r="E9">
+        <v>61</v>
+      </c>
+      <c r="F9">
+        <v>61</v>
+      </c>
+      <c r="G9">
+        <v>65</v>
+      </c>
+      <c r="H9">
+        <v>27</v>
+      </c>
+      <c r="I9">
+        <v>76</v>
+      </c>
+      <c r="J9">
+        <v>69</v>
+      </c>
+      <c r="K9">
+        <v>59</v>
+      </c>
+      <c r="L9">
+        <v>59</v>
+      </c>
+      <c r="M9">
+        <v>71</v>
+      </c>
+      <c r="N9">
+        <v>66</v>
+      </c>
+      <c r="O9">
+        <v>76</v>
+      </c>
+      <c r="P9">
+        <v>43</v>
+      </c>
+      <c r="Q9">
+        <v>53</v>
+      </c>
+      <c r="R9">
+        <v>72</v>
+      </c>
+      <c r="S9">
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -10944,7 +11637,58 @@
       </c>
       <c r="B10">
         <f>SUM(C10:C10:S10)</f>
-        <v>0</v>
+        <v>794</v>
+      </c>
+      <c r="C10">
+        <v>27</v>
+      </c>
+      <c r="D10">
+        <v>55</v>
+      </c>
+      <c r="E10">
+        <v>68</v>
+      </c>
+      <c r="F10">
+        <v>61</v>
+      </c>
+      <c r="G10">
+        <v>64</v>
+      </c>
+      <c r="H10">
+        <v>70</v>
+      </c>
+      <c r="I10">
+        <v>44</v>
+      </c>
+      <c r="J10">
+        <v>8</v>
+      </c>
+      <c r="K10">
+        <v>59</v>
+      </c>
+      <c r="L10">
+        <v>59</v>
+      </c>
+      <c r="M10">
+        <v>35</v>
+      </c>
+      <c r="N10">
+        <v>27</v>
+      </c>
+      <c r="O10">
+        <v>20</v>
+      </c>
+      <c r="P10">
+        <v>44</v>
+      </c>
+      <c r="Q10">
+        <v>53</v>
+      </c>
+      <c r="R10">
+        <v>73</v>
+      </c>
+      <c r="S10">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -10953,7 +11697,58 @@
       </c>
       <c r="B11">
         <f>SUM(C11:C11:S11)</f>
-        <v>0</v>
+        <v>697</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>9</v>
+      </c>
+      <c r="E11">
+        <v>25</v>
+      </c>
+      <c r="F11">
+        <v>44</v>
+      </c>
+      <c r="G11">
+        <v>43</v>
+      </c>
+      <c r="H11">
+        <v>22</v>
+      </c>
+      <c r="I11">
+        <v>51</v>
+      </c>
+      <c r="J11">
+        <v>69</v>
+      </c>
+      <c r="K11">
+        <v>59</v>
+      </c>
+      <c r="L11">
+        <v>59</v>
+      </c>
+      <c r="M11">
+        <v>29</v>
+      </c>
+      <c r="N11">
+        <v>39</v>
+      </c>
+      <c r="O11">
+        <v>76</v>
+      </c>
+      <c r="P11">
+        <v>39</v>
+      </c>
+      <c r="Q11">
+        <v>53</v>
+      </c>
+      <c r="R11">
+        <v>72</v>
+      </c>
+      <c r="S11">
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -10962,7 +11757,58 @@
       </c>
       <c r="B12">
         <f>SUM(C12:C12:S12)</f>
-        <v>0</v>
+        <v>862</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>56</v>
+      </c>
+      <c r="E12">
+        <v>71</v>
+      </c>
+      <c r="F12">
+        <v>62</v>
+      </c>
+      <c r="G12">
+        <v>60</v>
+      </c>
+      <c r="H12">
+        <v>71</v>
+      </c>
+      <c r="I12">
+        <v>51</v>
+      </c>
+      <c r="J12">
+        <v>65</v>
+      </c>
+      <c r="K12">
+        <v>60</v>
+      </c>
+      <c r="L12">
+        <v>54</v>
+      </c>
+      <c r="M12">
+        <v>71</v>
+      </c>
+      <c r="N12">
+        <v>24</v>
+      </c>
+      <c r="O12">
+        <v>30</v>
+      </c>
+      <c r="P12">
+        <v>10</v>
+      </c>
+      <c r="Q12">
+        <v>53</v>
+      </c>
+      <c r="R12">
+        <v>72</v>
+      </c>
+      <c r="S12">
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -10971,7 +11817,58 @@
       </c>
       <c r="B13">
         <f>SUM(C13:C13:S13)</f>
-        <v>0</v>
+        <v>834</v>
+      </c>
+      <c r="C13">
+        <v>8</v>
+      </c>
+      <c r="D13">
+        <v>9</v>
+      </c>
+      <c r="E13">
+        <v>60</v>
+      </c>
+      <c r="F13">
+        <v>61</v>
+      </c>
+      <c r="G13">
+        <v>63</v>
+      </c>
+      <c r="H13">
+        <v>44</v>
+      </c>
+      <c r="I13">
+        <v>77</v>
+      </c>
+      <c r="J13">
+        <v>70</v>
+      </c>
+      <c r="K13">
+        <v>59</v>
+      </c>
+      <c r="L13">
+        <v>29</v>
+      </c>
+      <c r="M13">
+        <v>49</v>
+      </c>
+      <c r="N13">
+        <v>36</v>
+      </c>
+      <c r="O13">
+        <v>76</v>
+      </c>
+      <c r="P13">
+        <v>35</v>
+      </c>
+      <c r="Q13">
+        <v>53</v>
+      </c>
+      <c r="R13">
+        <v>73</v>
+      </c>
+      <c r="S13">
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -10980,7 +11877,58 @@
       </c>
       <c r="B14">
         <f>SUM(C14:C14:S14)</f>
-        <v>0</v>
+        <v>760</v>
+      </c>
+      <c r="C14">
+        <v>12</v>
+      </c>
+      <c r="D14">
+        <v>54</v>
+      </c>
+      <c r="E14">
+        <v>69</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
+      <c r="H14">
+        <v>26</v>
+      </c>
+      <c r="I14">
+        <v>22</v>
+      </c>
+      <c r="J14">
+        <v>69</v>
+      </c>
+      <c r="K14">
+        <v>58</v>
+      </c>
+      <c r="L14">
+        <v>50</v>
+      </c>
+      <c r="M14">
+        <v>23</v>
+      </c>
+      <c r="N14">
+        <v>66</v>
+      </c>
+      <c r="O14">
+        <v>76</v>
+      </c>
+      <c r="P14">
+        <v>43</v>
+      </c>
+      <c r="Q14">
+        <v>52</v>
+      </c>
+      <c r="R14">
+        <v>72</v>
+      </c>
+      <c r="S14">
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -10989,7 +11937,58 @@
       </c>
       <c r="B15">
         <f>SUM(C15:C15:S15)</f>
-        <v>0</v>
+        <v>722</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>53</v>
+      </c>
+      <c r="E15">
+        <v>6</v>
+      </c>
+      <c r="F15">
+        <v>19</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>71</v>
+      </c>
+      <c r="I15">
+        <v>77</v>
+      </c>
+      <c r="J15">
+        <v>70</v>
+      </c>
+      <c r="K15">
+        <v>26</v>
+      </c>
+      <c r="L15">
+        <v>59</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>59</v>
+      </c>
+      <c r="O15">
+        <v>77</v>
+      </c>
+      <c r="P15">
+        <v>38</v>
+      </c>
+      <c r="Q15">
+        <v>53</v>
+      </c>
+      <c r="R15">
+        <v>72</v>
+      </c>
+      <c r="S15">
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -10998,78 +11997,537 @@
       </c>
       <c r="B16">
         <f>SUM(C16:C16:S16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>694</v>
+      </c>
+      <c r="C16">
+        <v>53</v>
+      </c>
+      <c r="D16">
+        <v>54</v>
+      </c>
+      <c r="E16">
+        <v>70</v>
+      </c>
+      <c r="F16">
+        <v>30</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>76</v>
+      </c>
+      <c r="J16">
+        <v>29</v>
+      </c>
+      <c r="K16">
+        <v>59</v>
+      </c>
+      <c r="L16">
+        <v>58</v>
+      </c>
+      <c r="M16">
+        <v>70</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>75</v>
+      </c>
+      <c r="P16">
+        <v>37</v>
+      </c>
+      <c r="Q16">
+        <v>15</v>
+      </c>
+      <c r="R16">
+        <v>27</v>
+      </c>
+      <c r="S16">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
         <f>SUM(C17:C17:S17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>815</v>
+      </c>
+      <c r="C17">
+        <v>57</v>
+      </c>
+      <c r="D17">
+        <v>30</v>
+      </c>
+      <c r="E17">
+        <v>70</v>
+      </c>
+      <c r="F17">
+        <v>45</v>
+      </c>
+      <c r="G17">
+        <v>41</v>
+      </c>
+      <c r="H17">
+        <v>38</v>
+      </c>
+      <c r="I17">
+        <v>76</v>
+      </c>
+      <c r="J17">
+        <v>41</v>
+      </c>
+      <c r="K17">
+        <v>41</v>
+      </c>
+      <c r="L17">
+        <v>23</v>
+      </c>
+      <c r="M17">
+        <v>52</v>
+      </c>
+      <c r="N17">
+        <v>57</v>
+      </c>
+      <c r="O17">
+        <v>23</v>
+      </c>
+      <c r="P17">
+        <v>44</v>
+      </c>
+      <c r="Q17">
+        <v>53</v>
+      </c>
+      <c r="R17">
+        <v>72</v>
+      </c>
+      <c r="S17">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18">
         <f>SUM(C18:C18:S18)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>781</v>
+      </c>
+      <c r="C18">
+        <v>56</v>
+      </c>
+      <c r="D18">
+        <v>34</v>
+      </c>
+      <c r="E18">
+        <v>68</v>
+      </c>
+      <c r="F18">
+        <v>60</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>69</v>
+      </c>
+      <c r="I18">
+        <v>76</v>
+      </c>
+      <c r="J18">
+        <v>69</v>
+      </c>
+      <c r="K18">
+        <v>58</v>
+      </c>
+      <c r="L18">
+        <v>9</v>
+      </c>
+      <c r="M18">
+        <v>71</v>
+      </c>
+      <c r="N18">
+        <v>23</v>
+      </c>
+      <c r="O18">
+        <v>75</v>
+      </c>
+      <c r="P18">
+        <v>4</v>
+      </c>
+      <c r="Q18">
+        <v>20</v>
+      </c>
+      <c r="R18">
+        <v>38</v>
+      </c>
+      <c r="S18">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>52</v>
       </c>
       <c r="B19">
         <f>SUM(C19:C19:S19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>58</v>
+      </c>
+      <c r="P19">
+        <v>17</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
       <c r="B20">
         <f>SUM(C20:C20:S20)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+      <c r="C20">
+        <v>55</v>
+      </c>
+      <c r="D20">
+        <v>29</v>
+      </c>
+      <c r="E20">
+        <v>67</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>42</v>
+      </c>
+      <c r="I20">
+        <v>29</v>
+      </c>
+      <c r="J20">
+        <v>68</v>
+      </c>
+      <c r="K20">
+        <v>48</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>68</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>47</v>
+      </c>
+      <c r="R20">
+        <v>46</v>
+      </c>
+      <c r="S20">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
       <c r="B21">
         <f>SUM(C21:C21:S21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>358</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>20</v>
+      </c>
+      <c r="E21">
+        <v>19</v>
+      </c>
+      <c r="F21">
+        <v>50</v>
+      </c>
+      <c r="G21">
+        <v>40</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
+      </c>
+      <c r="I21">
+        <v>76</v>
+      </c>
+      <c r="J21">
+        <v>16</v>
+      </c>
+      <c r="K21">
+        <v>59</v>
+      </c>
+      <c r="L21">
+        <v>28</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>48</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>20</v>
       </c>
       <c r="B22">
         <f>SUM(C22:C22:S22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>552</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>54</v>
+      </c>
+      <c r="E22">
+        <v>25</v>
+      </c>
+      <c r="F22">
+        <v>25</v>
+      </c>
+      <c r="G22">
+        <v>65</v>
+      </c>
+      <c r="H22">
+        <v>69</v>
+      </c>
+      <c r="I22">
+        <v>77</v>
+      </c>
+      <c r="J22">
+        <v>69</v>
+      </c>
+      <c r="K22">
+        <v>59</v>
+      </c>
+      <c r="L22">
+        <v>20</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>18</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>71</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
       <c r="B23">
         <f>SUM(C23:C23:S23)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>924</v>
+      </c>
+      <c r="C23">
+        <v>56</v>
+      </c>
+      <c r="D23">
+        <v>53</v>
+      </c>
+      <c r="E23">
+        <v>70</v>
+      </c>
+      <c r="F23">
+        <v>26</v>
+      </c>
+      <c r="G23">
+        <v>64</v>
+      </c>
+      <c r="H23">
+        <v>71</v>
+      </c>
+      <c r="I23">
+        <v>69</v>
+      </c>
+      <c r="J23">
+        <v>41</v>
+      </c>
+      <c r="K23">
+        <v>51</v>
+      </c>
+      <c r="L23">
+        <v>15</v>
+      </c>
+      <c r="M23">
+        <v>48</v>
+      </c>
+      <c r="N23">
+        <v>66</v>
+      </c>
+      <c r="O23">
+        <v>75</v>
+      </c>
+      <c r="P23">
+        <v>44</v>
+      </c>
+      <c r="Q23">
+        <v>52</v>
+      </c>
+      <c r="R23">
+        <v>71</v>
+      </c>
+      <c r="S23">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
       <c r="B24">
         <f>SUM(C24:C24:S24)</f>
+        <v>639</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>55</v>
+      </c>
+      <c r="E24">
+        <v>40</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>64</v>
+      </c>
+      <c r="H24">
+        <v>71</v>
+      </c>
+      <c r="I24">
+        <v>15</v>
+      </c>
+      <c r="J24">
+        <v>45</v>
+      </c>
+      <c r="K24">
+        <v>59</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>65</v>
+      </c>
+      <c r="N24">
+        <v>23</v>
+      </c>
+      <c r="O24">
+        <v>75</v>
+      </c>
+      <c r="P24">
+        <v>43</v>
+      </c>
+      <c r="Q24">
+        <v>13</v>
+      </c>
+      <c r="R24">
+        <v>71</v>
+      </c>
+      <c r="S24">
         <v>0</v>
       </c>
     </row>
@@ -11080,139 +12538,1450 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D4303C-7F1D-4CBD-BF56-16C815E789BE}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <f>SUM(C2:R2)</f>
+        <v>987</v>
+      </c>
+      <c r="C2">
+        <v>58</v>
+      </c>
+      <c r="D2">
+        <v>55</v>
+      </c>
+      <c r="E2">
+        <v>26</v>
+      </c>
+      <c r="F2">
+        <v>62</v>
+      </c>
+      <c r="G2">
+        <v>65</v>
+      </c>
+      <c r="H2">
+        <v>69</v>
+      </c>
+      <c r="I2">
+        <v>78</v>
+      </c>
+      <c r="J2">
+        <v>70</v>
+      </c>
+      <c r="K2">
+        <v>60</v>
+      </c>
+      <c r="L2">
+        <v>70</v>
+      </c>
+      <c r="M2">
+        <v>60</v>
+      </c>
+      <c r="N2">
+        <v>66</v>
+      </c>
+      <c r="O2">
+        <v>69</v>
+      </c>
+      <c r="P2">
+        <v>53</v>
+      </c>
+      <c r="Q2">
+        <v>73</v>
+      </c>
+      <c r="R2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <f t="shared" ref="B3:B25" si="0">SUM(C3:R3)</f>
+        <v>851</v>
+      </c>
+      <c r="C3">
+        <v>58</v>
+      </c>
+      <c r="D3">
+        <v>56</v>
+      </c>
+      <c r="E3">
+        <v>54</v>
+      </c>
+      <c r="F3">
+        <v>62</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>69</v>
+      </c>
+      <c r="I3">
+        <v>78</v>
+      </c>
+      <c r="J3">
+        <v>70</v>
+      </c>
+      <c r="K3">
+        <v>25</v>
+      </c>
+      <c r="L3">
+        <v>70</v>
+      </c>
+      <c r="M3">
+        <v>60</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>70</v>
+      </c>
+      <c r="P3">
+        <v>53</v>
+      </c>
+      <c r="Q3">
+        <v>73</v>
+      </c>
+      <c r="R3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>903</v>
+      </c>
+      <c r="C4">
+        <v>58</v>
+      </c>
+      <c r="D4">
+        <v>53</v>
+      </c>
+      <c r="E4">
+        <v>24</v>
+      </c>
+      <c r="F4">
+        <v>62</v>
+      </c>
+      <c r="G4">
+        <v>65</v>
+      </c>
+      <c r="H4">
+        <v>32</v>
+      </c>
+      <c r="I4">
+        <v>78</v>
+      </c>
+      <c r="J4">
+        <v>70</v>
+      </c>
+      <c r="K4">
+        <v>60</v>
+      </c>
+      <c r="L4">
+        <v>70</v>
+      </c>
+      <c r="M4">
+        <v>60</v>
+      </c>
+      <c r="N4">
+        <v>67</v>
+      </c>
+      <c r="O4">
+        <v>70</v>
+      </c>
+      <c r="P4">
+        <v>53</v>
+      </c>
+      <c r="Q4">
+        <v>72</v>
+      </c>
+      <c r="R4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>767</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>56</v>
+      </c>
+      <c r="E5">
+        <v>46</v>
+      </c>
+      <c r="F5">
+        <v>62</v>
+      </c>
+      <c r="G5">
+        <v>65</v>
+      </c>
+      <c r="H5">
+        <v>69</v>
+      </c>
+      <c r="I5">
+        <v>78</v>
+      </c>
+      <c r="J5">
+        <v>70</v>
+      </c>
+      <c r="K5">
+        <v>60</v>
+      </c>
+      <c r="L5">
+        <v>69</v>
+      </c>
+      <c r="M5">
+        <v>60</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5">
+        <v>53</v>
+      </c>
+      <c r="Q5">
+        <v>2</v>
+      </c>
+      <c r="R5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>844</v>
+      </c>
+      <c r="C6">
+        <v>58</v>
+      </c>
+      <c r="D6">
+        <v>56</v>
+      </c>
+      <c r="E6">
+        <v>54</v>
+      </c>
+      <c r="F6">
+        <v>62</v>
+      </c>
+      <c r="G6">
+        <v>64</v>
+      </c>
+      <c r="H6">
+        <v>68</v>
+      </c>
+      <c r="I6">
+        <v>78</v>
+      </c>
+      <c r="J6">
+        <v>70</v>
+      </c>
+      <c r="K6">
+        <v>60</v>
+      </c>
+      <c r="L6">
+        <v>70</v>
+      </c>
+      <c r="M6">
+        <v>60</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>70</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>21</v>
+      </c>
+      <c r="R6">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>892</v>
+      </c>
+      <c r="C7">
+        <v>58</v>
+      </c>
+      <c r="D7">
+        <v>56</v>
+      </c>
+      <c r="E7">
+        <v>54</v>
+      </c>
+      <c r="F7">
+        <v>62</v>
+      </c>
+      <c r="G7">
+        <v>65</v>
+      </c>
+      <c r="H7">
+        <v>44</v>
+      </c>
+      <c r="I7">
+        <v>78</v>
+      </c>
+      <c r="J7">
+        <v>70</v>
+      </c>
+      <c r="K7">
+        <v>60</v>
+      </c>
+      <c r="L7">
+        <v>43</v>
+      </c>
+      <c r="M7">
+        <v>52</v>
+      </c>
+      <c r="N7">
+        <v>67</v>
+      </c>
+      <c r="O7">
+        <v>70</v>
+      </c>
+      <c r="P7">
+        <v>52</v>
+      </c>
+      <c r="Q7">
+        <v>44</v>
+      </c>
+      <c r="R7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>853</v>
+      </c>
+      <c r="C8">
+        <v>58</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>54</v>
+      </c>
+      <c r="F8">
+        <v>62</v>
+      </c>
+      <c r="G8">
+        <v>17</v>
+      </c>
+      <c r="H8">
+        <v>69</v>
+      </c>
+      <c r="I8">
+        <v>78</v>
+      </c>
+      <c r="J8">
+        <v>47</v>
+      </c>
+      <c r="K8">
+        <v>56</v>
+      </c>
+      <c r="L8">
+        <v>70</v>
+      </c>
+      <c r="M8">
+        <v>60</v>
+      </c>
+      <c r="N8">
+        <v>67</v>
+      </c>
+      <c r="O8">
+        <v>70</v>
+      </c>
+      <c r="P8">
+        <v>45</v>
+      </c>
+      <c r="Q8">
+        <v>45</v>
+      </c>
+      <c r="R8">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="C9">
+        <v>58</v>
+      </c>
+      <c r="D9">
+        <v>55</v>
+      </c>
+      <c r="E9">
+        <v>54</v>
+      </c>
+      <c r="F9">
+        <v>61</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>68</v>
+      </c>
+      <c r="I9">
+        <v>78</v>
+      </c>
+      <c r="J9">
+        <v>22</v>
+      </c>
+      <c r="K9">
+        <v>37</v>
+      </c>
+      <c r="L9">
+        <v>45</v>
+      </c>
+      <c r="M9">
+        <v>60</v>
+      </c>
+      <c r="N9">
+        <v>67</v>
+      </c>
+      <c r="O9">
+        <v>69</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>73</v>
+      </c>
+      <c r="R9">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>782</v>
+      </c>
+      <c r="C10">
+        <v>58</v>
+      </c>
+      <c r="D10">
+        <v>55</v>
+      </c>
+      <c r="E10">
+        <v>32</v>
+      </c>
+      <c r="F10">
+        <v>61</v>
+      </c>
+      <c r="G10">
+        <v>63</v>
+      </c>
+      <c r="H10">
+        <v>69</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>51</v>
+      </c>
+      <c r="K10">
+        <v>59</v>
+      </c>
+      <c r="L10">
+        <v>21</v>
+      </c>
+      <c r="M10">
+        <v>60</v>
+      </c>
+      <c r="N10">
+        <v>66</v>
+      </c>
+      <c r="O10">
+        <v>69</v>
+      </c>
+      <c r="P10">
+        <v>24</v>
+      </c>
+      <c r="Q10">
+        <v>41</v>
+      </c>
+      <c r="R10">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>822</v>
+      </c>
+      <c r="C11">
+        <v>15</v>
+      </c>
+      <c r="D11">
+        <v>35</v>
+      </c>
+      <c r="E11">
+        <v>53</v>
+      </c>
+      <c r="F11">
+        <v>54</v>
+      </c>
+      <c r="G11">
+        <v>64</v>
+      </c>
+      <c r="H11">
+        <v>68</v>
+      </c>
+      <c r="I11">
+        <v>16</v>
+      </c>
+      <c r="J11">
+        <v>69</v>
+      </c>
+      <c r="K11">
+        <v>59</v>
+      </c>
+      <c r="L11">
+        <v>70</v>
+      </c>
+      <c r="M11">
+        <v>59</v>
+      </c>
+      <c r="N11">
+        <v>64</v>
+      </c>
+      <c r="O11">
+        <v>70</v>
+      </c>
+      <c r="P11">
+        <v>52</v>
+      </c>
+      <c r="Q11">
+        <v>21</v>
+      </c>
+      <c r="R11">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>639</v>
+      </c>
+      <c r="C12">
+        <v>58</v>
+      </c>
+      <c r="D12">
+        <v>55</v>
+      </c>
+      <c r="E12">
+        <v>54</v>
+      </c>
+      <c r="F12">
+        <v>61</v>
+      </c>
+      <c r="G12">
+        <v>38</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>6</v>
+      </c>
+      <c r="K12">
+        <v>59</v>
+      </c>
+      <c r="L12">
+        <v>68</v>
+      </c>
+      <c r="M12">
+        <v>60</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>47</v>
+      </c>
+      <c r="P12">
+        <v>50</v>
+      </c>
+      <c r="Q12">
+        <v>73</v>
+      </c>
+      <c r="R12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>752</v>
+      </c>
+      <c r="C13">
+        <v>52</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>54</v>
+      </c>
+      <c r="F13">
+        <v>57</v>
+      </c>
+      <c r="G13">
+        <v>43</v>
+      </c>
+      <c r="H13">
+        <v>60</v>
+      </c>
+      <c r="I13">
+        <v>77</v>
+      </c>
+      <c r="J13">
+        <v>20</v>
+      </c>
+      <c r="K13">
+        <v>58</v>
+      </c>
+      <c r="L13">
+        <v>42</v>
+      </c>
+      <c r="M13">
+        <v>44</v>
+      </c>
+      <c r="N13">
+        <v>60</v>
+      </c>
+      <c r="O13">
+        <v>28</v>
+      </c>
+      <c r="P13">
+        <v>52</v>
+      </c>
+      <c r="Q13">
+        <v>72</v>
+      </c>
+      <c r="R13">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>892</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+      <c r="D14">
+        <v>55</v>
+      </c>
+      <c r="E14">
+        <v>53</v>
+      </c>
+      <c r="F14">
+        <v>61</v>
+      </c>
+      <c r="G14">
+        <v>64</v>
+      </c>
+      <c r="H14">
+        <v>68</v>
+      </c>
+      <c r="I14">
+        <v>77</v>
+      </c>
+      <c r="J14">
+        <v>64</v>
+      </c>
+      <c r="K14">
+        <v>53</v>
+      </c>
+      <c r="L14">
+        <v>69</v>
+      </c>
+      <c r="M14">
+        <v>60</v>
+      </c>
+      <c r="N14">
+        <v>66</v>
+      </c>
+      <c r="O14">
+        <v>68</v>
+      </c>
+      <c r="P14">
+        <v>3</v>
+      </c>
+      <c r="Q14">
+        <v>71</v>
+      </c>
+      <c r="R14">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>873</v>
+      </c>
+      <c r="C15">
+        <v>20</v>
+      </c>
+      <c r="D15">
+        <v>55</v>
+      </c>
+      <c r="E15">
+        <v>8</v>
+      </c>
+      <c r="F15">
+        <v>61</v>
+      </c>
+      <c r="G15">
+        <v>63</v>
+      </c>
+      <c r="H15">
+        <v>46</v>
+      </c>
+      <c r="I15">
+        <v>76</v>
+      </c>
+      <c r="J15">
+        <v>47</v>
+      </c>
+      <c r="K15">
+        <v>59</v>
+      </c>
+      <c r="L15">
+        <v>68</v>
+      </c>
+      <c r="M15">
+        <v>58</v>
+      </c>
+      <c r="N15">
+        <v>65</v>
+      </c>
+      <c r="O15">
+        <v>69</v>
+      </c>
+      <c r="P15">
+        <v>52</v>
+      </c>
+      <c r="Q15">
+        <v>73</v>
+      </c>
+      <c r="R15">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>691</v>
+      </c>
+      <c r="C16">
+        <v>31</v>
+      </c>
+      <c r="D16">
+        <v>12</v>
+      </c>
+      <c r="E16">
+        <v>17</v>
+      </c>
+      <c r="F16">
+        <v>61</v>
+      </c>
+      <c r="G16">
+        <v>41</v>
+      </c>
+      <c r="H16">
+        <v>6</v>
+      </c>
+      <c r="I16">
+        <v>74</v>
+      </c>
+      <c r="J16">
+        <v>69</v>
+      </c>
+      <c r="K16">
+        <v>37</v>
+      </c>
+      <c r="L16">
+        <v>69</v>
+      </c>
+      <c r="M16">
+        <v>60</v>
+      </c>
+      <c r="N16">
+        <v>66</v>
+      </c>
+      <c r="O16">
+        <v>33</v>
+      </c>
+      <c r="P16">
+        <v>35</v>
+      </c>
+      <c r="Q16">
+        <v>27</v>
+      </c>
+      <c r="R16">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>662</v>
+      </c>
+      <c r="C17">
+        <v>58</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>54</v>
+      </c>
+      <c r="F17">
+        <v>19</v>
+      </c>
+      <c r="G17">
+        <v>12</v>
+      </c>
+      <c r="H17">
+        <v>68</v>
+      </c>
+      <c r="I17">
+        <v>63</v>
+      </c>
+      <c r="J17">
+        <v>14</v>
+      </c>
+      <c r="K17">
+        <v>51</v>
+      </c>
+      <c r="L17">
+        <v>69</v>
+      </c>
+      <c r="M17">
+        <v>60</v>
+      </c>
+      <c r="N17">
+        <v>65</v>
+      </c>
+      <c r="O17">
+        <v>14</v>
+      </c>
+      <c r="P17">
+        <v>52</v>
+      </c>
+      <c r="Q17">
+        <v>63</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>53</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>639</v>
+      </c>
+      <c r="C20">
+        <v>6</v>
+      </c>
+      <c r="D20">
+        <v>55</v>
+      </c>
+      <c r="E20">
+        <v>17</v>
+      </c>
+      <c r="F20">
+        <v>51</v>
+      </c>
+      <c r="G20">
+        <v>63</v>
+      </c>
+      <c r="H20">
+        <v>68</v>
+      </c>
+      <c r="I20">
+        <v>76</v>
+      </c>
+      <c r="J20">
+        <v>20</v>
+      </c>
+      <c r="K20">
+        <v>58</v>
+      </c>
+      <c r="L20">
+        <v>67</v>
+      </c>
+      <c r="M20">
+        <v>59</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>48</v>
+      </c>
+      <c r="R20">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>670</v>
+      </c>
+      <c r="C21">
+        <v>16</v>
+      </c>
+      <c r="D21">
+        <v>41</v>
+      </c>
+      <c r="E21">
+        <v>15</v>
+      </c>
+      <c r="F21">
+        <v>23</v>
+      </c>
+      <c r="G21">
+        <v>63</v>
+      </c>
+      <c r="H21">
+        <v>67</v>
+      </c>
+      <c r="I21">
+        <v>29</v>
+      </c>
+      <c r="J21">
+        <v>60</v>
+      </c>
+      <c r="K21">
+        <v>58</v>
+      </c>
+      <c r="L21">
+        <v>67</v>
+      </c>
+      <c r="M21">
+        <v>58</v>
+      </c>
+      <c r="N21">
+        <v>6</v>
+      </c>
+      <c r="O21">
+        <v>42</v>
+      </c>
+      <c r="P21">
+        <v>2</v>
+      </c>
+      <c r="Q21">
+        <v>71</v>
+      </c>
+      <c r="R21">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <f t="shared" si="0"/>
+        <v>482</v>
+      </c>
+      <c r="C22">
+        <v>52</v>
+      </c>
+      <c r="D22">
+        <v>42</v>
+      </c>
+      <c r="E22">
+        <v>24</v>
+      </c>
+      <c r="F22">
+        <v>60</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>68</v>
+      </c>
+      <c r="I22">
+        <v>10</v>
+      </c>
+      <c r="J22">
+        <v>66</v>
+      </c>
+      <c r="K22">
+        <v>59</v>
+      </c>
+      <c r="L22">
+        <v>69</v>
+      </c>
+      <c r="M22">
+        <v>32</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <f t="shared" si="0"/>
+        <v>753</v>
+      </c>
+      <c r="C23">
+        <v>57</v>
+      </c>
+      <c r="D23">
+        <v>52</v>
+      </c>
+      <c r="E23">
+        <v>30</v>
+      </c>
+      <c r="F23">
+        <v>38</v>
+      </c>
+      <c r="G23">
+        <v>62</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>28</v>
+      </c>
+      <c r="J23">
+        <v>68</v>
+      </c>
+      <c r="K23">
+        <v>57</v>
+      </c>
+      <c r="L23">
+        <v>66</v>
+      </c>
+      <c r="M23">
+        <v>58</v>
+      </c>
+      <c r="N23">
+        <v>23</v>
+      </c>
+      <c r="O23">
+        <v>67</v>
+      </c>
+      <c r="P23">
+        <v>27</v>
+      </c>
+      <c r="Q23">
+        <v>69</v>
+      </c>
+      <c r="R23">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <f t="shared" si="0"/>
+        <v>298</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>62</v>
+      </c>
+      <c r="O24">
+        <v>66</v>
+      </c>
+      <c r="P24">
+        <v>51</v>
+      </c>
+      <c r="Q24">
+        <v>69</v>
+      </c>
+      <c r="R24">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>34</v>
+      </c>
+      <c r="P25">
+        <v>51</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Files/Laps_Completed.xlsx
+++ b/Data_Files/Laps_Completed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FBA74C-54C4-45BD-BDE0-88A7D3B2C3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B661BDFD-BE9F-403A-87E3-49CCDD4B10E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="1500" windowWidth="16410" windowHeight="14145" firstSheet="6" activeTab="13" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Laps_Completed" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="150">
   <si>
     <t>Driver</t>
   </si>
@@ -206,16 +206,7 @@
     <t>Fernando Alonso</t>
   </si>
   <si>
-    <t>Ralph Firman</t>
-  </si>
-  <si>
-    <t>Antônio Pizzonia</t>
-  </si>
-  <si>
     <t>Jos Verstappen</t>
-  </si>
-  <si>
-    <t>Justin Wilson</t>
   </si>
   <si>
     <t>Cristiano da Matta</t>
@@ -1084,13 +1075,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>143</xdr:row>
+      <xdr:row>140</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1133,13 +1124,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>143</xdr:row>
+      <xdr:row>140</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1601,7 +1592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCEEE69D-1A9D-4213-BBC7-B7EBD153B749}">
-  <dimension ref="A1:AL124"/>
+  <dimension ref="A1:AL121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
@@ -1725,6 +1716,9 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
+      <c r="Z2">
+        <v>987</v>
+      </c>
       <c r="AA2">
         <v>1090</v>
       </c>
@@ -1766,6 +1760,9 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
+      <c r="Z3">
+        <v>767</v>
+      </c>
       <c r="AA3">
         <v>822</v>
       </c>
@@ -1807,6 +1804,9 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
+      <c r="Z4">
+        <v>851</v>
+      </c>
       <c r="AA4">
         <v>792</v>
       </c>
@@ -1848,6 +1848,9 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
+      <c r="Z5">
+        <v>853</v>
+      </c>
       <c r="AA5">
         <v>941</v>
       </c>
@@ -1889,6 +1892,9 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
+      <c r="Z6">
+        <v>903</v>
+      </c>
       <c r="AA6">
         <v>990</v>
       </c>
@@ -1930,6 +1936,9 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
+      <c r="Z7">
+        <v>844</v>
+      </c>
       <c r="AA7">
         <v>973</v>
       </c>
@@ -1971,6 +1980,9 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
       <c r="AA8">
         <v>726</v>
       </c>
@@ -2010,6 +2022,9 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
+      <c r="Z9">
+        <v>873</v>
+      </c>
       <c r="AA9">
         <v>965</v>
       </c>
@@ -2051,6 +2066,9 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
+      <c r="Z10">
+        <v>662</v>
+      </c>
       <c r="AA10">
         <v>794</v>
       </c>
@@ -2092,6 +2110,9 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
+      <c r="Z11">
+        <v>691</v>
+      </c>
       <c r="AA11">
         <v>697</v>
       </c>
@@ -2133,6 +2154,9 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
+      <c r="Z12">
+        <v>782</v>
+      </c>
       <c r="AA12">
         <v>862</v>
       </c>
@@ -2174,6 +2198,9 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
+      <c r="Z13">
+        <v>800</v>
+      </c>
       <c r="AA13">
         <v>834</v>
       </c>
@@ -2215,6 +2242,9 @@
       <c r="A14" t="s">
         <v>13</v>
       </c>
+      <c r="Z14">
+        <v>53</v>
+      </c>
       <c r="AA14">
         <v>760</v>
       </c>
@@ -2256,6 +2286,9 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
+      <c r="Z15">
+        <v>752</v>
+      </c>
       <c r="AA15">
         <v>722</v>
       </c>
@@ -2297,6 +2330,9 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
       <c r="AA16">
         <v>694</v>
       </c>
@@ -2338,6 +2374,9 @@
       <c r="A17" t="s">
         <v>16</v>
       </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
       <c r="AA17">
         <v>815</v>
       </c>
@@ -2379,6 +2418,9 @@
       <c r="A18" t="s">
         <v>17</v>
       </c>
+      <c r="Z18">
+        <v>822</v>
+      </c>
       <c r="AA18">
         <v>781</v>
       </c>
@@ -2418,7 +2460,10 @@
     </row>
     <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>82</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
       </c>
       <c r="AA19">
         <v>75</v>
@@ -2461,6 +2506,9 @@
       <c r="A20" t="s">
         <v>18</v>
       </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
       <c r="AA20">
         <v>513</v>
       </c>
@@ -2502,6 +2550,9 @@
       <c r="A21" t="s">
         <v>19</v>
       </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
       <c r="AA21">
         <v>358</v>
       </c>
@@ -2541,7 +2592,10 @@
     </row>
     <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="Z22">
+        <v>639</v>
       </c>
       <c r="AA22">
         <v>552</v>
@@ -2584,6 +2638,9 @@
       <c r="A23" t="s">
         <v>21</v>
       </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
       <c r="AA23">
         <v>924</v>
       </c>
@@ -2625,6 +2682,9 @@
       <c r="A24" t="s">
         <v>22</v>
       </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
       <c r="AA24">
         <v>639</v>
       </c>
@@ -2666,6 +2726,9 @@
       <c r="A25" t="s">
         <v>44</v>
       </c>
+      <c r="Z25">
+        <v>892</v>
+      </c>
       <c r="AA25">
         <v>0</v>
       </c>
@@ -2707,32 +2770,35 @@
       <c r="A26" t="s">
         <v>45</v>
       </c>
-      <c r="AA26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="1">
-        <v>0</v>
+      <c r="Z26">
+        <v>753</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>889</v>
+      </c>
+      <c r="AC26">
+        <v>695</v>
       </c>
       <c r="AD26" s="1">
         <v>0</v>
       </c>
-      <c r="AE26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="1">
-        <v>0</v>
+      <c r="AE26">
+        <v>389</v>
+      </c>
+      <c r="AF26">
+        <v>781</v>
+      </c>
+      <c r="AG26">
+        <v>480</v>
+      </c>
+      <c r="AH26">
+        <v>116</v>
+      </c>
+      <c r="AI26">
+        <v>394</v>
       </c>
       <c r="AJ26" s="1">
         <v>0</v>
@@ -2748,6 +2814,9 @@
       <c r="A27" t="s">
         <v>46</v>
       </c>
+      <c r="Z27">
+        <v>892</v>
+      </c>
       <c r="AA27" s="1">
         <v>0</v>
       </c>
@@ -2787,34 +2856,37 @@
     </row>
     <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="Z28">
+        <v>53</v>
       </c>
       <c r="AA28">
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>889</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>695</v>
-      </c>
-      <c r="AD28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>389</v>
-      </c>
-      <c r="AF28">
-        <v>781</v>
-      </c>
-      <c r="AG28">
-        <v>480</v>
-      </c>
-      <c r="AH28">
-        <v>116</v>
-      </c>
-      <c r="AI28">
-        <v>394</v>
+        <v>843</v>
+      </c>
+      <c r="AD28">
+        <v>712</v>
+      </c>
+      <c r="AE28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="1">
+        <v>0</v>
       </c>
       <c r="AJ28" s="1">
         <v>0</v>
@@ -2828,7 +2900,10 @@
     </row>
     <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>54</v>
+      </c>
+      <c r="Z29">
+        <v>639</v>
       </c>
       <c r="AA29" s="1">
         <v>0</v>
@@ -2869,7 +2944,10 @@
     </row>
     <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>49</v>
+        <v>55</v>
+      </c>
+      <c r="Z30">
+        <v>670</v>
       </c>
       <c r="AA30" s="1">
         <v>0</v>
@@ -2910,19 +2988,22 @@
     </row>
     <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA31">
-        <v>0</v>
-      </c>
-      <c r="AB31">
-        <v>0</v>
-      </c>
-      <c r="AC31">
-        <v>843</v>
-      </c>
-      <c r="AD31">
-        <v>712</v>
+        <v>56</v>
+      </c>
+      <c r="Z31">
+        <v>482</v>
+      </c>
+      <c r="AA31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="1">
+        <v>0</v>
       </c>
       <c r="AE31" s="1">
         <v>0</v>
@@ -2953,6 +3034,9 @@
       <c r="A32" t="s">
         <v>57</v>
       </c>
+      <c r="Z32">
+        <v>298</v>
+      </c>
       <c r="AA32" s="1">
         <v>0</v>
       </c>
@@ -2994,6 +3078,9 @@
       <c r="A33" t="s">
         <v>58</v>
       </c>
+      <c r="Z33">
+        <v>85</v>
+      </c>
       <c r="AA33" s="1">
         <v>0</v>
       </c>
@@ -3035,6 +3122,9 @@
       <c r="A34" t="s">
         <v>59</v>
       </c>
+      <c r="Z34" s="1">
+        <v>0</v>
+      </c>
       <c r="AA34" s="1">
         <v>0</v>
       </c>
@@ -3076,6 +3166,9 @@
       <c r="A35" t="s">
         <v>60</v>
       </c>
+      <c r="Z35" s="1">
+        <v>0</v>
+      </c>
       <c r="AA35" s="1">
         <v>0</v>
       </c>
@@ -3117,17 +3210,20 @@
       <c r="A36" t="s">
         <v>61</v>
       </c>
-      <c r="AA36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="1">
-        <v>0</v>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>75</v>
+      </c>
+      <c r="AC36">
+        <v>909</v>
+      </c>
+      <c r="AD36">
+        <v>502</v>
       </c>
       <c r="AE36" s="1">
         <v>0</v>
@@ -3158,7 +3254,9 @@
       <c r="A37" t="s">
         <v>62</v>
       </c>
-      <c r="Z37" s="1"/>
+      <c r="Z37" s="1">
+        <v>0</v>
+      </c>
       <c r="AA37" s="1">
         <v>0</v>
       </c>
@@ -3200,7 +3298,9 @@
       <c r="A38" t="s">
         <v>63</v>
       </c>
-      <c r="Z38" s="1"/>
+      <c r="Z38" s="1">
+        <v>0</v>
+      </c>
       <c r="AA38" s="1">
         <v>0</v>
       </c>
@@ -3242,17 +3342,21 @@
       <c r="A39" t="s">
         <v>64</v>
       </c>
-      <c r="AA39">
-        <v>0</v>
-      </c>
-      <c r="AB39">
-        <v>75</v>
-      </c>
-      <c r="AC39">
-        <v>909</v>
-      </c>
-      <c r="AD39">
-        <v>502</v>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="1">
+        <v>0</v>
       </c>
       <c r="AE39" s="1">
         <v>0</v>
@@ -3283,24 +3387,26 @@
       <c r="A40" t="s">
         <v>65</v>
       </c>
-      <c r="Z40" s="1"/>
-      <c r="AA40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF40" s="1">
-        <v>0</v>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>868</v>
+      </c>
+      <c r="AD40">
+        <v>685</v>
+      </c>
+      <c r="AE40">
+        <v>848</v>
+      </c>
+      <c r="AF40">
+        <v>154</v>
       </c>
       <c r="AG40" s="1">
         <v>0</v>
@@ -3325,7 +3431,10 @@
       <c r="A41" t="s">
         <v>66</v>
       </c>
-      <c r="Z41" s="1"/>
+      <c r="Y41" s="1"/>
+      <c r="Z41" s="1">
+        <v>0</v>
+      </c>
       <c r="AA41" s="1">
         <v>0</v>
       </c>
@@ -3368,7 +3477,9 @@
         <v>67</v>
       </c>
       <c r="Y42" s="1"/>
-      <c r="Z42" s="1"/>
+      <c r="Z42" s="1">
+        <v>0</v>
+      </c>
       <c r="AA42" s="1">
         <v>0</v>
       </c>
@@ -3410,23 +3521,27 @@
       <c r="A43" t="s">
         <v>68</v>
       </c>
-      <c r="AA43">
-        <v>0</v>
-      </c>
-      <c r="AB43">
-        <v>0</v>
-      </c>
-      <c r="AC43">
-        <v>868</v>
-      </c>
-      <c r="AD43">
-        <v>685</v>
-      </c>
-      <c r="AE43">
-        <v>848</v>
-      </c>
-      <c r="AF43">
-        <v>154</v>
+      <c r="Y43" s="1"/>
+      <c r="Z43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="1">
+        <v>0</v>
       </c>
       <c r="AG43" s="1">
         <v>0</v>
@@ -3452,7 +3567,9 @@
         <v>69</v>
       </c>
       <c r="Y44" s="1"/>
-      <c r="Z44" s="1"/>
+      <c r="Z44" s="1">
+        <v>0</v>
+      </c>
       <c r="AA44" s="1">
         <v>0</v>
       </c>
@@ -3495,7 +3612,9 @@
         <v>70</v>
       </c>
       <c r="Y45" s="1"/>
-      <c r="Z45" s="1"/>
+      <c r="Z45" s="1">
+        <v>0</v>
+      </c>
       <c r="AA45" s="1">
         <v>0</v>
       </c>
@@ -3537,8 +3656,11 @@
       <c r="A46" t="s">
         <v>71</v>
       </c>
+      <c r="X46" s="1"/>
       <c r="Y46" s="1"/>
-      <c r="Z46" s="1"/>
+      <c r="Z46" s="1">
+        <v>0</v>
+      </c>
       <c r="AA46" s="1">
         <v>0</v>
       </c>
@@ -3580,8 +3702,11 @@
       <c r="A47" t="s">
         <v>72</v>
       </c>
+      <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
-      <c r="Z47" s="1"/>
+      <c r="Z47" s="1">
+        <v>0</v>
+      </c>
       <c r="AA47" s="1">
         <v>0</v>
       </c>
@@ -3623,8 +3748,11 @@
       <c r="A48" t="s">
         <v>73</v>
       </c>
+      <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
-      <c r="Z48" s="1"/>
+      <c r="Z48" s="1">
+        <v>0</v>
+      </c>
       <c r="AA48" s="1">
         <v>0</v>
       </c>
@@ -3668,7 +3796,9 @@
       </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="1"/>
-      <c r="Z49" s="1"/>
+      <c r="Z49" s="1">
+        <v>0</v>
+      </c>
       <c r="AA49" s="1">
         <v>0</v>
       </c>
@@ -3712,7 +3842,9 @@
       </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="1"/>
-      <c r="Z50" s="1"/>
+      <c r="Z50" s="1">
+        <v>0</v>
+      </c>
       <c r="AA50" s="1">
         <v>0</v>
       </c>
@@ -3756,7 +3888,9 @@
       </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="1"/>
-      <c r="Z51" s="1"/>
+      <c r="Z51" s="1">
+        <v>0</v>
+      </c>
       <c r="AA51" s="1">
         <v>0</v>
       </c>
@@ -3798,9 +3932,12 @@
       <c r="A52" t="s">
         <v>77</v>
       </c>
+      <c r="W52" s="1"/>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
-      <c r="Z52" s="1"/>
+      <c r="Z52" s="1">
+        <v>0</v>
+      </c>
       <c r="AA52" s="1">
         <v>0</v>
       </c>
@@ -3842,9 +3979,12 @@
       <c r="A53" t="s">
         <v>78</v>
       </c>
+      <c r="W53" s="1"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
-      <c r="Z53" s="1"/>
+      <c r="Z53" s="1">
+        <v>0</v>
+      </c>
       <c r="AA53" s="1">
         <v>0</v>
       </c>
@@ -3886,9 +4026,12 @@
       <c r="A54" t="s">
         <v>79</v>
       </c>
+      <c r="W54" s="1"/>
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
-      <c r="Z54" s="1"/>
+      <c r="Z54" s="1">
+        <v>0</v>
+      </c>
       <c r="AA54" s="1">
         <v>0</v>
       </c>
@@ -3933,7 +4076,9 @@
       <c r="W55" s="1"/>
       <c r="X55" s="1"/>
       <c r="Y55" s="1"/>
-      <c r="Z55" s="1"/>
+      <c r="Z55" s="1">
+        <v>0</v>
+      </c>
       <c r="AA55" s="1">
         <v>0</v>
       </c>
@@ -3978,7 +4123,9 @@
       <c r="W56" s="1"/>
       <c r="X56" s="1"/>
       <c r="Y56" s="1"/>
-      <c r="Z56" s="1"/>
+      <c r="Z56" s="1">
+        <v>0</v>
+      </c>
       <c r="AA56" s="1">
         <v>0</v>
       </c>
@@ -4018,12 +4165,15 @@
     </row>
     <row r="57" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>82</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="V57" s="1"/>
       <c r="W57" s="1"/>
       <c r="X57" s="1"/>
       <c r="Y57" s="1"/>
-      <c r="Z57" s="1"/>
+      <c r="Z57" s="1">
+        <v>0</v>
+      </c>
       <c r="AA57" s="1">
         <v>0</v>
       </c>
@@ -4063,12 +4213,15 @@
     </row>
     <row r="58" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>83</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="V58" s="1"/>
       <c r="W58" s="1"/>
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
-      <c r="Z58" s="1"/>
+      <c r="Z58" s="1">
+        <v>0</v>
+      </c>
       <c r="AA58" s="1">
         <v>0</v>
       </c>
@@ -4108,12 +4261,16 @@
     </row>
     <row r="59" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>84</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="U59" s="1"/>
+      <c r="V59" s="1"/>
       <c r="W59" s="1"/>
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
-      <c r="Z59" s="1"/>
+      <c r="Z59" s="1">
+        <v>0</v>
+      </c>
       <c r="AA59" s="1">
         <v>0</v>
       </c>
@@ -4155,11 +4312,14 @@
       <c r="A60" t="s">
         <v>86</v>
       </c>
+      <c r="U60" s="1"/>
       <c r="V60" s="1"/>
       <c r="W60" s="1"/>
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
-      <c r="Z60" s="1"/>
+      <c r="Z60" s="1">
+        <v>0</v>
+      </c>
       <c r="AA60" s="1">
         <v>0</v>
       </c>
@@ -4201,11 +4361,14 @@
       <c r="A61" t="s">
         <v>87</v>
       </c>
+      <c r="U61" s="1"/>
       <c r="V61" s="1"/>
       <c r="W61" s="1"/>
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
-      <c r="Z61" s="1"/>
+      <c r="Z61" s="1">
+        <v>0</v>
+      </c>
       <c r="AA61" s="1">
         <v>0</v>
       </c>
@@ -4252,7 +4415,9 @@
       <c r="W62" s="1"/>
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
-      <c r="Z62" s="1"/>
+      <c r="Z62" s="1">
+        <v>0</v>
+      </c>
       <c r="AA62" s="1">
         <v>0</v>
       </c>
@@ -4294,12 +4459,24 @@
       <c r="A63" t="s">
         <v>89</v>
       </c>
-      <c r="U63" s="1"/>
-      <c r="V63" s="1"/>
-      <c r="W63" s="1"/>
-      <c r="X63" s="1"/>
-      <c r="Y63" s="1"/>
-      <c r="Z63" s="1"/>
+      <c r="U63" s="1">
+        <v>0</v>
+      </c>
+      <c r="V63" s="1">
+        <v>0</v>
+      </c>
+      <c r="W63" s="1">
+        <v>0</v>
+      </c>
+      <c r="X63" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="1">
+        <v>0</v>
+      </c>
       <c r="AA63" s="1">
         <v>0</v>
       </c>
@@ -4309,8 +4486,8 @@
       <c r="AC63" s="1">
         <v>0</v>
       </c>
-      <c r="AD63" s="1">
-        <v>0</v>
+      <c r="AD63">
+        <v>659</v>
       </c>
       <c r="AE63" s="1">
         <v>0</v>
@@ -4318,17 +4495,17 @@
       <c r="AF63" s="1">
         <v>0</v>
       </c>
-      <c r="AG63" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH63" s="1">
-        <v>0</v>
+      <c r="AG63">
+        <v>283</v>
+      </c>
+      <c r="AH63">
+        <v>807</v>
       </c>
       <c r="AI63" s="1">
         <v>0</v>
       </c>
-      <c r="AJ63" s="1">
-        <v>0</v>
+      <c r="AJ63">
+        <v>516</v>
       </c>
       <c r="AK63" s="1">
         <v>0</v>
@@ -4341,12 +4518,15 @@
       <c r="A64" t="s">
         <v>90</v>
       </c>
+      <c r="T64" s="1"/>
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
       <c r="W64" s="1"/>
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
-      <c r="Z64" s="1"/>
+      <c r="Z64" s="1">
+        <v>0</v>
+      </c>
       <c r="AA64" s="1">
         <v>0</v>
       </c>
@@ -4388,12 +4568,15 @@
       <c r="A65" t="s">
         <v>91</v>
       </c>
+      <c r="T65" s="1"/>
       <c r="U65" s="1"/>
       <c r="V65" s="1"/>
       <c r="W65" s="1"/>
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
-      <c r="Z65" s="1"/>
+      <c r="Z65" s="1">
+        <v>0</v>
+      </c>
       <c r="AA65" s="1">
         <v>0</v>
       </c>
@@ -4435,21 +4618,12 @@
       <c r="A66" t="s">
         <v>92</v>
       </c>
-      <c r="U66" s="1">
-        <v>0</v>
-      </c>
-      <c r="V66" s="1">
-        <v>0</v>
-      </c>
-      <c r="W66" s="1">
-        <v>0</v>
-      </c>
-      <c r="X66" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y66" s="1">
-        <v>0</v>
-      </c>
+      <c r="T66" s="1"/>
+      <c r="U66" s="1"/>
+      <c r="V66" s="1"/>
+      <c r="W66" s="1"/>
+      <c r="X66" s="1"/>
+      <c r="Y66" s="1"/>
       <c r="Z66" s="1">
         <v>0</v>
       </c>
@@ -4462,8 +4636,8 @@
       <c r="AC66" s="1">
         <v>0</v>
       </c>
-      <c r="AD66">
-        <v>659</v>
+      <c r="AD66" s="1">
+        <v>0</v>
       </c>
       <c r="AE66" s="1">
         <v>0</v>
@@ -4471,17 +4645,17 @@
       <c r="AF66" s="1">
         <v>0</v>
       </c>
-      <c r="AG66">
-        <v>283</v>
-      </c>
-      <c r="AH66">
-        <v>807</v>
+      <c r="AG66" s="1">
+        <v>0</v>
+      </c>
+      <c r="AH66" s="1">
+        <v>0</v>
       </c>
       <c r="AI66" s="1">
         <v>0</v>
       </c>
-      <c r="AJ66">
-        <v>516</v>
+      <c r="AJ66" s="1">
+        <v>0</v>
       </c>
       <c r="AK66" s="1">
         <v>0</v>
@@ -4500,7 +4674,9 @@
       <c r="W67" s="1"/>
       <c r="X67" s="1"/>
       <c r="Y67" s="1"/>
-      <c r="Z67" s="1"/>
+      <c r="Z67" s="1">
+        <v>0</v>
+      </c>
       <c r="AA67" s="1">
         <v>0</v>
       </c>
@@ -4548,7 +4724,9 @@
       <c r="W68" s="1"/>
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
-      <c r="Z68" s="1"/>
+      <c r="Z68" s="1">
+        <v>0</v>
+      </c>
       <c r="AA68" s="1">
         <v>0</v>
       </c>
@@ -4590,13 +4768,16 @@
       <c r="A69" t="s">
         <v>95</v>
       </c>
+      <c r="S69" s="1"/>
       <c r="T69" s="1"/>
       <c r="U69" s="1"/>
       <c r="V69" s="1"/>
       <c r="W69" s="1"/>
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
-      <c r="Z69" s="1"/>
+      <c r="Z69" s="1">
+        <v>0</v>
+      </c>
       <c r="AA69" s="1">
         <v>0</v>
       </c>
@@ -4638,13 +4819,16 @@
       <c r="A70" t="s">
         <v>96</v>
       </c>
+      <c r="S70" s="1"/>
       <c r="T70" s="1"/>
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
       <c r="W70" s="1"/>
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
-      <c r="Z70" s="1"/>
+      <c r="Z70" s="1">
+        <v>0</v>
+      </c>
       <c r="AA70" s="1">
         <v>0</v>
       </c>
@@ -4686,13 +4870,16 @@
       <c r="A71" t="s">
         <v>97</v>
       </c>
+      <c r="S71" s="1"/>
       <c r="T71" s="1"/>
       <c r="U71" s="1"/>
       <c r="V71" s="1"/>
       <c r="W71" s="1"/>
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
-      <c r="Z71" s="1"/>
+      <c r="Z71" s="1">
+        <v>0</v>
+      </c>
       <c r="AA71" s="1">
         <v>0</v>
       </c>
@@ -4741,7 +4928,9 @@
       <c r="W72" s="1"/>
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
-      <c r="Z72" s="1"/>
+      <c r="Z72" s="1">
+        <v>0</v>
+      </c>
       <c r="AA72" s="1">
         <v>0</v>
       </c>
@@ -4790,7 +4979,9 @@
       <c r="W73" s="1"/>
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
-      <c r="Z73" s="1"/>
+      <c r="Z73" s="1">
+        <v>0</v>
+      </c>
       <c r="AA73" s="1">
         <v>0</v>
       </c>
@@ -4832,6 +5023,7 @@
       <c r="A74" t="s">
         <v>100</v>
       </c>
+      <c r="R74" s="1"/>
       <c r="S74" s="1"/>
       <c r="T74" s="1"/>
       <c r="U74" s="1"/>
@@ -4839,7 +5031,9 @@
       <c r="W74" s="1"/>
       <c r="X74" s="1"/>
       <c r="Y74" s="1"/>
-      <c r="Z74" s="1"/>
+      <c r="Z74" s="1">
+        <v>0</v>
+      </c>
       <c r="AA74" s="1">
         <v>0</v>
       </c>
@@ -4881,6 +5075,7 @@
       <c r="A75" t="s">
         <v>101</v>
       </c>
+      <c r="R75" s="1"/>
       <c r="S75" s="1"/>
       <c r="T75" s="1"/>
       <c r="U75" s="1"/>
@@ -4888,7 +5083,9 @@
       <c r="W75" s="1"/>
       <c r="X75" s="1"/>
       <c r="Y75" s="1"/>
-      <c r="Z75" s="1"/>
+      <c r="Z75" s="1">
+        <v>0</v>
+      </c>
       <c r="AA75" s="1">
         <v>0</v>
       </c>
@@ -4930,6 +5127,8 @@
       <c r="A76" t="s">
         <v>102</v>
       </c>
+      <c r="Q76" s="1"/>
+      <c r="R76" s="1"/>
       <c r="S76" s="1"/>
       <c r="T76" s="1"/>
       <c r="U76" s="1"/>
@@ -4937,7 +5136,9 @@
       <c r="W76" s="1"/>
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
-      <c r="Z76" s="1"/>
+      <c r="Z76" s="1">
+        <v>0</v>
+      </c>
       <c r="AA76" s="1">
         <v>0</v>
       </c>
@@ -4979,6 +5180,7 @@
       <c r="A77" t="s">
         <v>103</v>
       </c>
+      <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
       <c r="S77" s="1"/>
       <c r="T77" s="1"/>
@@ -4987,7 +5189,9 @@
       <c r="W77" s="1"/>
       <c r="X77" s="1"/>
       <c r="Y77" s="1"/>
-      <c r="Z77" s="1"/>
+      <c r="Z77" s="1">
+        <v>0</v>
+      </c>
       <c r="AA77" s="1">
         <v>0</v>
       </c>
@@ -5029,6 +5233,7 @@
       <c r="A78" t="s">
         <v>104</v>
       </c>
+      <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
       <c r="S78" s="1"/>
       <c r="T78" s="1"/>
@@ -5037,7 +5242,9 @@
       <c r="W78" s="1"/>
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
-      <c r="Z78" s="1"/>
+      <c r="Z78" s="1">
+        <v>0</v>
+      </c>
       <c r="AA78" s="1">
         <v>0</v>
       </c>
@@ -5088,7 +5295,9 @@
       <c r="W79" s="1"/>
       <c r="X79" s="1"/>
       <c r="Y79" s="1"/>
-      <c r="Z79" s="1"/>
+      <c r="Z79" s="1">
+        <v>0</v>
+      </c>
       <c r="AA79" s="1">
         <v>0</v>
       </c>
@@ -5139,7 +5348,9 @@
       <c r="W80" s="1"/>
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
-      <c r="Z80" s="1"/>
+      <c r="Z80" s="1">
+        <v>0</v>
+      </c>
       <c r="AA80" s="1">
         <v>0</v>
       </c>
@@ -5181,6 +5392,7 @@
       <c r="A81" t="s">
         <v>107</v>
       </c>
+      <c r="P81" s="1"/>
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
@@ -5190,7 +5402,9 @@
       <c r="W81" s="1"/>
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
-      <c r="Z81" s="1"/>
+      <c r="Z81" s="1">
+        <v>0</v>
+      </c>
       <c r="AA81" s="1">
         <v>0</v>
       </c>
@@ -5232,6 +5446,7 @@
       <c r="A82" t="s">
         <v>108</v>
       </c>
+      <c r="P82" s="1"/>
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
@@ -5241,7 +5456,9 @@
       <c r="W82" s="1"/>
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
-      <c r="Z82" s="1"/>
+      <c r="Z82" s="1">
+        <v>0</v>
+      </c>
       <c r="AA82" s="1">
         <v>0</v>
       </c>
@@ -5283,6 +5500,7 @@
       <c r="A83" t="s">
         <v>109</v>
       </c>
+      <c r="P83" s="1"/>
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
@@ -5292,7 +5510,9 @@
       <c r="W83" s="1"/>
       <c r="X83" s="1"/>
       <c r="Y83" s="1"/>
-      <c r="Z83" s="1"/>
+      <c r="Z83" s="1">
+        <v>0</v>
+      </c>
       <c r="AA83" s="1">
         <v>0</v>
       </c>
@@ -5344,7 +5564,9 @@
       <c r="W84" s="1"/>
       <c r="X84" s="1"/>
       <c r="Y84" s="1"/>
-      <c r="Z84" s="1"/>
+      <c r="Z84" s="1">
+        <v>0</v>
+      </c>
       <c r="AA84" s="1">
         <v>0</v>
       </c>
@@ -5386,6 +5608,7 @@
       <c r="A85" t="s">
         <v>111</v>
       </c>
+      <c r="O85" s="1"/>
       <c r="P85" s="1"/>
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
@@ -5396,7 +5619,9 @@
       <c r="W85" s="1"/>
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
-      <c r="Z85" s="1"/>
+      <c r="Z85" s="1">
+        <v>0</v>
+      </c>
       <c r="AA85" s="1">
         <v>0</v>
       </c>
@@ -5438,6 +5663,7 @@
       <c r="A86" t="s">
         <v>112</v>
       </c>
+      <c r="O86" s="1"/>
       <c r="P86" s="1"/>
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
@@ -5448,7 +5674,9 @@
       <c r="W86" s="1"/>
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
-      <c r="Z86" s="1"/>
+      <c r="Z86" s="1">
+        <v>0</v>
+      </c>
       <c r="AA86" s="1">
         <v>0</v>
       </c>
@@ -5490,6 +5718,7 @@
       <c r="A87" t="s">
         <v>113</v>
       </c>
+      <c r="O87" s="1"/>
       <c r="P87" s="1"/>
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
@@ -5500,7 +5729,9 @@
       <c r="W87" s="1"/>
       <c r="X87" s="1"/>
       <c r="Y87" s="1"/>
-      <c r="Z87" s="1"/>
+      <c r="Z87" s="1">
+        <v>0</v>
+      </c>
       <c r="AA87" s="1">
         <v>0</v>
       </c>
@@ -5553,7 +5784,9 @@
       <c r="W88" s="1"/>
       <c r="X88" s="1"/>
       <c r="Y88" s="1"/>
-      <c r="Z88" s="1"/>
+      <c r="Z88" s="1">
+        <v>0</v>
+      </c>
       <c r="AA88" s="1">
         <v>0</v>
       </c>
@@ -5606,7 +5839,9 @@
       <c r="W89" s="1"/>
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
-      <c r="Z89" s="1"/>
+      <c r="Z89" s="1">
+        <v>0</v>
+      </c>
       <c r="AA89" s="1">
         <v>0</v>
       </c>
@@ -5648,6 +5883,7 @@
       <c r="A90" t="s">
         <v>116</v>
       </c>
+      <c r="N90" s="1"/>
       <c r="O90" s="1"/>
       <c r="P90" s="1"/>
       <c r="Q90" s="1"/>
@@ -5659,7 +5895,9 @@
       <c r="W90" s="1"/>
       <c r="X90" s="1"/>
       <c r="Y90" s="1"/>
-      <c r="Z90" s="1"/>
+      <c r="Z90" s="1">
+        <v>0</v>
+      </c>
       <c r="AA90" s="1">
         <v>0</v>
       </c>
@@ -5701,6 +5939,7 @@
       <c r="A91" t="s">
         <v>117</v>
       </c>
+      <c r="N91" s="1"/>
       <c r="O91" s="1"/>
       <c r="P91" s="1"/>
       <c r="Q91" s="1"/>
@@ -5712,7 +5951,9 @@
       <c r="W91" s="1"/>
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
-      <c r="Z91" s="1"/>
+      <c r="Z91" s="1">
+        <v>0</v>
+      </c>
       <c r="AA91" s="1">
         <v>0</v>
       </c>
@@ -5754,6 +5995,7 @@
       <c r="A92" t="s">
         <v>118</v>
       </c>
+      <c r="N92" s="1"/>
       <c r="O92" s="1"/>
       <c r="P92" s="1"/>
       <c r="Q92" s="1"/>
@@ -5765,7 +6007,9 @@
       <c r="W92" s="1"/>
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
-      <c r="Z92" s="1"/>
+      <c r="Z92" s="1">
+        <v>0</v>
+      </c>
       <c r="AA92" s="1">
         <v>0</v>
       </c>
@@ -5819,7 +6063,9 @@
       <c r="W93" s="1"/>
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
-      <c r="Z93" s="1"/>
+      <c r="Z93" s="1">
+        <v>0</v>
+      </c>
       <c r="AA93" s="1">
         <v>0</v>
       </c>
@@ -5873,7 +6119,9 @@
       <c r="W94" s="1"/>
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
-      <c r="Z94" s="1"/>
+      <c r="Z94" s="1">
+        <v>0</v>
+      </c>
       <c r="AA94" s="1">
         <v>0</v>
       </c>
@@ -5915,6 +6163,7 @@
       <c r="A95" t="s">
         <v>121</v>
       </c>
+      <c r="M95" s="1"/>
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
       <c r="P95" s="1"/>
@@ -5927,7 +6176,9 @@
       <c r="W95" s="1"/>
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
-      <c r="Z95" s="1"/>
+      <c r="Z95" s="1">
+        <v>0</v>
+      </c>
       <c r="AA95" s="1">
         <v>0</v>
       </c>
@@ -5969,6 +6220,7 @@
       <c r="A96" t="s">
         <v>122</v>
       </c>
+      <c r="M96" s="1"/>
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
       <c r="P96" s="1"/>
@@ -5981,7 +6233,9 @@
       <c r="W96" s="1"/>
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
-      <c r="Z96" s="1"/>
+      <c r="Z96" s="1">
+        <v>0</v>
+      </c>
       <c r="AA96" s="1">
         <v>0</v>
       </c>
@@ -6023,6 +6277,7 @@
       <c r="A97" t="s">
         <v>123</v>
       </c>
+      <c r="M97" s="1"/>
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
       <c r="P97" s="1"/>
@@ -6035,7 +6290,9 @@
       <c r="W97" s="1"/>
       <c r="X97" s="1"/>
       <c r="Y97" s="1"/>
-      <c r="Z97" s="1"/>
+      <c r="Z97" s="1">
+        <v>0</v>
+      </c>
       <c r="AA97" s="1">
         <v>0</v>
       </c>
@@ -6090,7 +6347,9 @@
       <c r="W98" s="1"/>
       <c r="X98" s="1"/>
       <c r="Y98" s="1"/>
-      <c r="Z98" s="1"/>
+      <c r="Z98" s="1">
+        <v>0</v>
+      </c>
       <c r="AA98" s="1">
         <v>0</v>
       </c>
@@ -6132,6 +6391,7 @@
       <c r="A99" t="s">
         <v>125</v>
       </c>
+      <c r="L99" s="1"/>
       <c r="M99" s="1"/>
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
@@ -6145,7 +6405,9 @@
       <c r="W99" s="1"/>
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
-      <c r="Z99" s="1"/>
+      <c r="Z99" s="1">
+        <v>0</v>
+      </c>
       <c r="AA99" s="1">
         <v>0</v>
       </c>
@@ -6187,6 +6449,7 @@
       <c r="A100" t="s">
         <v>126</v>
       </c>
+      <c r="L100" s="1"/>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
       <c r="O100" s="1"/>
@@ -6200,7 +6463,9 @@
       <c r="W100" s="1"/>
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
-      <c r="Z100" s="1"/>
+      <c r="Z100" s="1">
+        <v>0</v>
+      </c>
       <c r="AA100" s="1">
         <v>0</v>
       </c>
@@ -6242,6 +6507,8 @@
       <c r="A101" t="s">
         <v>127</v>
       </c>
+      <c r="K101" s="1"/>
+      <c r="L101" s="1"/>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
@@ -6255,7 +6522,9 @@
       <c r="W101" s="1"/>
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
-      <c r="Z101" s="1"/>
+      <c r="Z101" s="1">
+        <v>0</v>
+      </c>
       <c r="AA101" s="1">
         <v>0</v>
       </c>
@@ -6297,6 +6566,7 @@
       <c r="A102" t="s">
         <v>128</v>
       </c>
+      <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
@@ -6311,7 +6581,9 @@
       <c r="W102" s="1"/>
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
-      <c r="Z102" s="1"/>
+      <c r="Z102" s="1">
+        <v>0</v>
+      </c>
       <c r="AA102" s="1">
         <v>0</v>
       </c>
@@ -6353,6 +6625,7 @@
       <c r="A103" t="s">
         <v>129</v>
       </c>
+      <c r="K103" s="1"/>
       <c r="L103" s="1"/>
       <c r="M103" s="1"/>
       <c r="N103" s="1"/>
@@ -6367,7 +6640,9 @@
       <c r="W103" s="1"/>
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
-      <c r="Z103" s="1"/>
+      <c r="Z103" s="1">
+        <v>0</v>
+      </c>
       <c r="AA103" s="1">
         <v>0</v>
       </c>
@@ -6409,6 +6684,7 @@
       <c r="A104" t="s">
         <v>130</v>
       </c>
+      <c r="J104" s="1"/>
       <c r="K104" s="1"/>
       <c r="L104" s="1"/>
       <c r="M104" s="1"/>
@@ -6424,7 +6700,9 @@
       <c r="W104" s="1"/>
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
-      <c r="Z104" s="1"/>
+      <c r="Z104" s="1">
+        <v>0</v>
+      </c>
       <c r="AA104" s="1">
         <v>0</v>
       </c>
@@ -6466,6 +6744,7 @@
       <c r="A105" t="s">
         <v>131</v>
       </c>
+      <c r="J105" s="1"/>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="1"/>
@@ -6481,7 +6760,9 @@
       <c r="W105" s="1"/>
       <c r="X105" s="1"/>
       <c r="Y105" s="1"/>
-      <c r="Z105" s="1"/>
+      <c r="Z105" s="1">
+        <v>0</v>
+      </c>
       <c r="AA105" s="1">
         <v>0</v>
       </c>
@@ -6523,6 +6804,7 @@
       <c r="A106" t="s">
         <v>132</v>
       </c>
+      <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
       <c r="M106" s="1"/>
@@ -6538,7 +6820,9 @@
       <c r="W106" s="1"/>
       <c r="X106" s="1"/>
       <c r="Y106" s="1"/>
-      <c r="Z106" s="1"/>
+      <c r="Z106" s="1">
+        <v>0</v>
+      </c>
       <c r="AA106" s="1">
         <v>0</v>
       </c>
@@ -6580,6 +6864,7 @@
       <c r="A107" t="s">
         <v>133</v>
       </c>
+      <c r="I107" s="1"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
@@ -6596,7 +6881,9 @@
       <c r="W107" s="1"/>
       <c r="X107" s="1"/>
       <c r="Y107" s="1"/>
-      <c r="Z107" s="1"/>
+      <c r="Z107" s="1">
+        <v>0</v>
+      </c>
       <c r="AA107" s="1">
         <v>0</v>
       </c>
@@ -6638,6 +6925,7 @@
       <c r="A108" t="s">
         <v>134</v>
       </c>
+      <c r="I108" s="1"/>
       <c r="J108" s="1"/>
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
@@ -6654,7 +6942,9 @@
       <c r="W108" s="1"/>
       <c r="X108" s="1"/>
       <c r="Y108" s="1"/>
-      <c r="Z108" s="1"/>
+      <c r="Z108" s="1">
+        <v>0</v>
+      </c>
       <c r="AA108" s="1">
         <v>0</v>
       </c>
@@ -6696,6 +6986,7 @@
       <c r="A109" t="s">
         <v>135</v>
       </c>
+      <c r="I109" s="1"/>
       <c r="J109" s="1"/>
       <c r="K109" s="1"/>
       <c r="L109" s="1"/>
@@ -6712,7 +7003,9 @@
       <c r="W109" s="1"/>
       <c r="X109" s="1"/>
       <c r="Y109" s="1"/>
-      <c r="Z109" s="1"/>
+      <c r="Z109" s="1">
+        <v>0</v>
+      </c>
       <c r="AA109" s="1">
         <v>0</v>
       </c>
@@ -6754,6 +7047,7 @@
       <c r="A110" t="s">
         <v>136</v>
       </c>
+      <c r="H110" s="1"/>
       <c r="I110" s="1"/>
       <c r="J110" s="1"/>
       <c r="K110" s="1"/>
@@ -6771,7 +7065,9 @@
       <c r="W110" s="1"/>
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
-      <c r="Z110" s="1"/>
+      <c r="Z110" s="1">
+        <v>0</v>
+      </c>
       <c r="AA110" s="1">
         <v>0</v>
       </c>
@@ -6813,6 +7109,7 @@
       <c r="A111" t="s">
         <v>137</v>
       </c>
+      <c r="H111" s="1"/>
       <c r="I111" s="1"/>
       <c r="J111" s="1"/>
       <c r="K111" s="1"/>
@@ -6830,7 +7127,9 @@
       <c r="W111" s="1"/>
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
-      <c r="Z111" s="1"/>
+      <c r="Z111" s="1">
+        <v>0</v>
+      </c>
       <c r="AA111" s="1">
         <v>0</v>
       </c>
@@ -6872,6 +7171,8 @@
       <c r="A112" t="s">
         <v>138</v>
       </c>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
       <c r="I112" s="1"/>
       <c r="J112" s="1"/>
       <c r="K112" s="1"/>
@@ -6889,7 +7190,9 @@
       <c r="W112" s="1"/>
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
-      <c r="Z112" s="1"/>
+      <c r="Z112" s="1">
+        <v>0</v>
+      </c>
       <c r="AA112" s="1">
         <v>0</v>
       </c>
@@ -6931,6 +7234,7 @@
       <c r="A113" t="s">
         <v>139</v>
       </c>
+      <c r="G113" s="1"/>
       <c r="H113" s="1"/>
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
@@ -6949,7 +7253,9 @@
       <c r="W113" s="1"/>
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
-      <c r="Z113" s="1"/>
+      <c r="Z113" s="1">
+        <v>0</v>
+      </c>
       <c r="AA113" s="1">
         <v>0</v>
       </c>
@@ -6991,6 +7297,7 @@
       <c r="A114" t="s">
         <v>140</v>
       </c>
+      <c r="G114" s="1"/>
       <c r="H114" s="1"/>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
@@ -7009,7 +7316,9 @@
       <c r="W114" s="1"/>
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
-      <c r="Z114" s="1"/>
+      <c r="Z114" s="1">
+        <v>0</v>
+      </c>
       <c r="AA114" s="1">
         <v>0</v>
       </c>
@@ -7051,6 +7360,7 @@
       <c r="A115" t="s">
         <v>141</v>
       </c>
+      <c r="F115" s="1"/>
       <c r="G115" s="1"/>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
@@ -7070,7 +7380,9 @@
       <c r="W115" s="1"/>
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
-      <c r="Z115" s="1"/>
+      <c r="Z115" s="1">
+        <v>0</v>
+      </c>
       <c r="AA115" s="1">
         <v>0</v>
       </c>
@@ -7112,6 +7424,7 @@
       <c r="A116" t="s">
         <v>142</v>
       </c>
+      <c r="F116" s="1"/>
       <c r="G116" s="1"/>
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
@@ -7131,7 +7444,9 @@
       <c r="W116" s="1"/>
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
-      <c r="Z116" s="1"/>
+      <c r="Z116" s="1">
+        <v>0</v>
+      </c>
       <c r="AA116" s="1">
         <v>0</v>
       </c>
@@ -7173,6 +7488,7 @@
       <c r="A117" t="s">
         <v>143</v>
       </c>
+      <c r="F117" s="1"/>
       <c r="G117" s="1"/>
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
@@ -7192,7 +7508,9 @@
       <c r="W117" s="1"/>
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
-      <c r="Z117" s="1"/>
+      <c r="Z117" s="1">
+        <v>0</v>
+      </c>
       <c r="AA117" s="1">
         <v>0</v>
       </c>
@@ -7234,6 +7552,7 @@
       <c r="A118" t="s">
         <v>144</v>
       </c>
+      <c r="E118" s="1"/>
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
@@ -7254,7 +7573,9 @@
       <c r="W118" s="1"/>
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
-      <c r="Z118" s="1"/>
+      <c r="Z118" s="1">
+        <v>0</v>
+      </c>
       <c r="AA118" s="1">
         <v>0</v>
       </c>
@@ -7296,6 +7617,7 @@
       <c r="A119" t="s">
         <v>145</v>
       </c>
+      <c r="E119" s="1"/>
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
       <c r="H119" s="1"/>
@@ -7316,7 +7638,9 @@
       <c r="W119" s="1"/>
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
-      <c r="Z119" s="1"/>
+      <c r="Z119" s="1">
+        <v>0</v>
+      </c>
       <c r="AA119" s="1">
         <v>0</v>
       </c>
@@ -7358,6 +7682,7 @@
       <c r="A120" t="s">
         <v>146</v>
       </c>
+      <c r="E120" s="1"/>
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
       <c r="H120" s="1"/>
@@ -7378,7 +7703,9 @@
       <c r="W120" s="1"/>
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
-      <c r="Z120" s="1"/>
+      <c r="Z120" s="1">
+        <v>0</v>
+      </c>
       <c r="AA120" s="1">
         <v>0</v>
       </c>
@@ -7420,6 +7747,7 @@
       <c r="A121" t="s">
         <v>147</v>
       </c>
+      <c r="D121" s="1"/>
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
@@ -7441,7 +7769,9 @@
       <c r="W121" s="1"/>
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
-      <c r="Z121" s="1"/>
+      <c r="Z121" s="1">
+        <v>0</v>
+      </c>
       <c r="AA121" s="1">
         <v>0</v>
       </c>
@@ -7476,196 +7806,6 @@
         <v>0</v>
       </c>
       <c r="AL121" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>148</v>
-      </c>
-      <c r="E122" s="1"/>
-      <c r="F122" s="1"/>
-      <c r="G122" s="1"/>
-      <c r="H122" s="1"/>
-      <c r="I122" s="1"/>
-      <c r="J122" s="1"/>
-      <c r="K122" s="1"/>
-      <c r="L122" s="1"/>
-      <c r="M122" s="1"/>
-      <c r="N122" s="1"/>
-      <c r="O122" s="1"/>
-      <c r="P122" s="1"/>
-      <c r="Q122" s="1"/>
-      <c r="R122" s="1"/>
-      <c r="S122" s="1"/>
-      <c r="T122" s="1"/>
-      <c r="U122" s="1"/>
-      <c r="V122" s="1"/>
-      <c r="W122" s="1"/>
-      <c r="X122" s="1"/>
-      <c r="Y122" s="1"/>
-      <c r="Z122" s="1"/>
-      <c r="AA122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK122" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL122" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>149</v>
-      </c>
-      <c r="E123" s="1"/>
-      <c r="F123" s="1"/>
-      <c r="G123" s="1"/>
-      <c r="H123" s="1"/>
-      <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
-      <c r="K123" s="1"/>
-      <c r="L123" s="1"/>
-      <c r="M123" s="1"/>
-      <c r="N123" s="1"/>
-      <c r="O123" s="1"/>
-      <c r="P123" s="1"/>
-      <c r="Q123" s="1"/>
-      <c r="R123" s="1"/>
-      <c r="S123" s="1"/>
-      <c r="T123" s="1"/>
-      <c r="U123" s="1"/>
-      <c r="V123" s="1"/>
-      <c r="W123" s="1"/>
-      <c r="X123" s="1"/>
-      <c r="Y123" s="1"/>
-      <c r="Z123" s="1"/>
-      <c r="AA123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK123" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL123" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>150</v>
-      </c>
-      <c r="D124" s="1"/>
-      <c r="E124" s="1"/>
-      <c r="F124" s="1"/>
-      <c r="G124" s="1"/>
-      <c r="H124" s="1"/>
-      <c r="I124" s="1"/>
-      <c r="J124" s="1"/>
-      <c r="K124" s="1"/>
-      <c r="L124" s="1"/>
-      <c r="M124" s="1"/>
-      <c r="N124" s="1"/>
-      <c r="O124" s="1"/>
-      <c r="P124" s="1"/>
-      <c r="Q124" s="1"/>
-      <c r="R124" s="1"/>
-      <c r="S124" s="1"/>
-      <c r="T124" s="1"/>
-      <c r="U124" s="1"/>
-      <c r="V124" s="1"/>
-      <c r="W124" s="1"/>
-      <c r="X124" s="1"/>
-      <c r="Y124" s="1"/>
-      <c r="Z124" s="1"/>
-      <c r="AA124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AJ124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK124" s="1">
-        <v>0</v>
-      </c>
-      <c r="AL124" s="1">
         <v>0</v>
       </c>
     </row>
@@ -8325,7 +8465,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
@@ -8439,7 +8579,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
@@ -8496,7 +8636,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
@@ -8553,7 +8693,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
@@ -8610,7 +8750,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
@@ -9417,7 +9557,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
@@ -9537,7 +9677,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B15">
         <f t="shared" si="0"/>
@@ -9597,7 +9737,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B16">
         <f t="shared" si="0"/>
@@ -9657,7 +9797,7 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B17">
         <f t="shared" si="0"/>
@@ -9717,7 +9857,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
@@ -10825,7 +10965,7 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
@@ -10945,7 +11085,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
@@ -11005,7 +11145,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
@@ -12173,7 +12313,7 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B19">
         <f>SUM(C19:C19:S19)</f>
@@ -12903,7 +13043,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
@@ -13188,7 +13328,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
@@ -13302,7 +13442,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
@@ -13530,7 +13670,7 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B18">
         <f t="shared" si="0"/>
@@ -13644,7 +13784,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B20">
         <f t="shared" si="0"/>
@@ -13701,7 +13841,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B21">
         <f t="shared" si="0"/>
@@ -13758,7 +13898,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B22">
         <f t="shared" si="0"/>
@@ -13815,7 +13955,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B23">
         <f t="shared" si="0"/>
@@ -13872,7 +14012,7 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B24">
         <f t="shared" si="0"/>
@@ -13929,7 +14069,7 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B25">
         <f t="shared" si="0"/>
@@ -14022,7 +14162,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -14077,17 +14217,17 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -14097,12 +14237,12 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -14112,22 +14252,22 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -14150,7 +14290,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -14220,27 +14360,27 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
@@ -14250,12 +14390,12 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -14265,12 +14405,12 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -14293,7 +14433,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -14368,37 +14508,37 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -14408,22 +14548,22 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -14451,12 +14591,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -14471,12 +14611,12 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -14486,7 +14626,7 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -14496,7 +14636,7 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -14511,7 +14651,7 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
@@ -14531,12 +14671,12 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
@@ -14546,27 +14686,27 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -14589,7 +14729,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -14604,12 +14744,12 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -14619,12 +14759,12 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
@@ -14634,7 +14774,7 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -14644,12 +14784,12 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -14659,7 +14799,7 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -14669,7 +14809,7 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -14684,7 +14824,7 @@
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -14694,7 +14834,7 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -14852,7 +14992,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -14867,7 +15007,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -14877,7 +15017,7 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -14887,12 +15027,12 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -14902,7 +15042,7 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -14912,7 +15052,7 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
@@ -14922,52 +15062,52 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -14990,12 +15130,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -15005,7 +15145,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -15020,12 +15160,12 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
@@ -15040,32 +15180,32 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -15080,12 +15220,12 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -15095,32 +15235,32 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -15143,7 +15283,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -15158,12 +15298,12 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -15173,7 +15313,7 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -15183,12 +15323,12 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -15198,27 +15338,27 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -15228,12 +15368,12 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
@@ -15248,37 +15388,37 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -15301,12 +15441,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -15316,7 +15456,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -15336,27 +15476,27 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -15366,57 +15506,57 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
@@ -15444,12 +15584,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -15459,7 +15599,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -15469,12 +15609,12 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -15489,72 +15629,72 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -15577,32 +15717,32 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -15617,17 +15757,17 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -15637,57 +15777,57 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -15710,17 +15850,17 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -15730,7 +15870,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -15740,47 +15880,47 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -15790,27 +15930,27 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -15833,27 +15973,27 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -15863,22 +16003,22 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -15888,17 +16028,17 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
@@ -15908,47 +16048,47 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -15971,17 +16111,17 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -15991,32 +16131,32 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -16026,62 +16166,62 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -16104,12 +16244,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -16119,87 +16259,87 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -16353,57 +16493,57 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -16413,42 +16553,42 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -16471,77 +16611,77 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -16551,37 +16691,37 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -16604,77 +16744,77 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -16684,27 +16824,27 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -16727,112 +16867,112 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -16855,112 +16995,112 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -16983,122 +17123,122 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -17122,107 +17262,107 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -17245,112 +17385,112 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -17600,7 +17740,7 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
@@ -17682,7 +17822,7 @@
         <v>26</v>
       </c>
       <c r="D1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E1" t="s">
         <v>27</v>
@@ -18014,7 +18154,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
@@ -18128,7 +18268,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
@@ -18208,7 +18348,7 @@
         <v>26</v>
       </c>
       <c r="D1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E1" t="s">
         <v>27</v>
@@ -18247,7 +18387,7 @@
         <v>32</v>
       </c>
       <c r="Q1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="R1" t="s">
         <v>40</v>
@@ -18558,7 +18698,7 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
@@ -18678,7 +18818,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
@@ -18738,7 +18878,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B10">
         <f t="shared" si="0"/>
@@ -18823,7 +18963,7 @@
         <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s">
         <v>32</v>
@@ -19266,7 +19406,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
@@ -19380,7 +19520,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
@@ -19437,7 +19577,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
@@ -19519,7 +19659,7 @@
         <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s">
         <v>27</v>
@@ -19555,7 +19695,7 @@
         <v>29</v>
       </c>
       <c r="Q1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="R1" t="s">
         <v>40</v>
@@ -20106,7 +20246,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
@@ -20226,7 +20366,7 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
@@ -20286,7 +20426,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
@@ -20375,7 +20515,7 @@
         <v>26</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s">
         <v>27</v>
@@ -20411,7 +20551,7 @@
         <v>38</v>
       </c>
       <c r="Q1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="R1" t="s">
         <v>40</v>
@@ -20932,7 +21072,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
@@ -21046,7 +21186,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
@@ -21103,7 +21243,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>

--- a/Data_Files/Laps_Completed.xlsx
+++ b/Data_Files/Laps_Completed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\Data_Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B661BDFD-BE9F-403A-87E3-49CCDD4B10E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F092F77D-87DE-49E0-8FEB-5C8600C70931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28695" yWindow="1500" windowWidth="16410" windowHeight="14145" firstSheet="7" activeTab="14" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Laps_Completed" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="153">
   <si>
     <t>Driver</t>
   </si>
@@ -519,6 +519,15 @@
   </si>
   <si>
     <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>Bahrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy </t>
+  </si>
+  <si>
+    <t>China</t>
   </si>
 </sst>
 </file>
@@ -14131,143 +14140,687 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E80DB57-1D34-4995-8AA7-BD186A2BDBE8}">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>151</v>
+      </c>
+      <c r="R1" t="s">
+        <v>152</v>
+      </c>
+      <c r="S1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <f>SUM(C2:T2)</f>
+        <v>299</v>
+      </c>
+      <c r="C2">
+        <v>58</v>
+      </c>
+      <c r="D2">
+        <v>56</v>
+      </c>
+      <c r="E2">
+        <v>57</v>
+      </c>
+      <c r="F2">
+        <v>62</v>
+      </c>
+      <c r="G2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <f t="shared" ref="B3:B26" si="0">SUM(C3:T3)</f>
+        <v>299</v>
+      </c>
+      <c r="C3">
+        <v>58</v>
+      </c>
+      <c r="D3">
+        <v>56</v>
+      </c>
+      <c r="E3">
+        <v>57</v>
+      </c>
+      <c r="F3">
+        <v>62</v>
+      </c>
+      <c r="G3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>298</v>
+      </c>
+      <c r="C4">
+        <v>58</v>
+      </c>
+      <c r="D4">
+        <v>56</v>
+      </c>
+      <c r="E4">
+        <v>57</v>
+      </c>
+      <c r="F4">
+        <v>62</v>
+      </c>
+      <c r="G4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>299</v>
+      </c>
+      <c r="C5">
+        <v>58</v>
+      </c>
+      <c r="D5">
+        <v>56</v>
+      </c>
+      <c r="E5">
+        <v>57</v>
+      </c>
+      <c r="F5">
+        <v>62</v>
+      </c>
+      <c r="G5">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>278</v>
+      </c>
+      <c r="C6">
+        <v>58</v>
+      </c>
+      <c r="D6">
+        <v>56</v>
+      </c>
+      <c r="E6">
+        <v>56</v>
+      </c>
+      <c r="F6">
+        <v>62</v>
+      </c>
+      <c r="G6">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>298</v>
+      </c>
+      <c r="C7">
+        <v>57</v>
+      </c>
+      <c r="D7">
+        <v>56</v>
+      </c>
+      <c r="E7">
+        <v>57</v>
+      </c>
+      <c r="F7">
+        <v>62</v>
+      </c>
+      <c r="G7">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>182</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>40</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+      <c r="F8">
+        <v>61</v>
+      </c>
+      <c r="G8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>288</v>
+      </c>
+      <c r="C9">
+        <v>57</v>
+      </c>
+      <c r="D9">
+        <v>52</v>
+      </c>
+      <c r="E9">
+        <v>57</v>
+      </c>
+      <c r="F9">
+        <v>56</v>
+      </c>
+      <c r="G9">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>270</v>
+      </c>
+      <c r="C10">
+        <v>58</v>
+      </c>
+      <c r="D10">
+        <v>27</v>
+      </c>
+      <c r="E10">
+        <v>57</v>
+      </c>
+      <c r="F10">
+        <v>62</v>
+      </c>
+      <c r="G10">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>289</v>
+      </c>
+      <c r="C11">
+        <v>57</v>
+      </c>
+      <c r="D11">
+        <v>56</v>
+      </c>
+      <c r="E11">
+        <v>50</v>
+      </c>
+      <c r="F11">
+        <v>61</v>
+      </c>
+      <c r="G11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>295</v>
+      </c>
+      <c r="C12">
+        <v>57</v>
+      </c>
+      <c r="D12">
+        <v>55</v>
+      </c>
+      <c r="E12">
+        <v>56</v>
+      </c>
+      <c r="F12">
+        <v>61</v>
+      </c>
+      <c r="G12">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>281</v>
+      </c>
+      <c r="C13">
+        <v>44</v>
+      </c>
+      <c r="D13">
+        <v>55</v>
+      </c>
+      <c r="E13">
+        <v>56</v>
+      </c>
+      <c r="F13">
+        <v>61</v>
+      </c>
+      <c r="G13">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>234</v>
+      </c>
+      <c r="C14">
+        <v>29</v>
+      </c>
+      <c r="D14">
+        <v>23</v>
+      </c>
+      <c r="E14">
+        <v>56</v>
+      </c>
+      <c r="F14">
+        <v>61</v>
+      </c>
+      <c r="G14">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>261</v>
+      </c>
+      <c r="C15">
+        <v>56</v>
+      </c>
+      <c r="D15">
+        <v>55</v>
+      </c>
+      <c r="E15">
+        <v>56</v>
+      </c>
+      <c r="F15">
+        <v>61</v>
+      </c>
+      <c r="G15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>270</v>
+      </c>
+      <c r="C17">
+        <v>56</v>
+      </c>
+      <c r="D17">
+        <v>55</v>
+      </c>
+      <c r="E17">
+        <v>56</v>
+      </c>
+      <c r="F17">
+        <v>60</v>
+      </c>
+      <c r="G17">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>264</v>
+      </c>
+      <c r="C18">
+        <v>56</v>
+      </c>
+      <c r="D18">
+        <v>55</v>
+      </c>
+      <c r="E18">
+        <v>56</v>
+      </c>
+      <c r="F18">
+        <v>32</v>
+      </c>
+      <c r="G18">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>214</v>
+      </c>
+      <c r="C19">
+        <v>43</v>
+      </c>
+      <c r="D19">
+        <v>34</v>
+      </c>
+      <c r="E19">
+        <v>56</v>
+      </c>
+      <c r="F19">
+        <v>48</v>
+      </c>
+      <c r="G19">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>184</v>
+      </c>
+      <c r="C21">
+        <v>13</v>
+      </c>
+      <c r="D21">
+        <v>52</v>
+      </c>
+      <c r="E21">
+        <v>44</v>
+      </c>
+      <c r="F21">
+        <v>58</v>
+      </c>
+      <c r="G21">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <f t="shared" si="0"/>
+        <v>221</v>
+      </c>
+      <c r="C25">
+        <v>55</v>
+      </c>
+      <c r="D25">
+        <v>54</v>
+      </c>
+      <c r="E25">
+        <v>55</v>
+      </c>
+      <c r="F25">
+        <v>6</v>
+      </c>
+      <c r="G25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>63</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="0"/>
+        <v>201</v>
+      </c>
+      <c r="C26">
+        <v>43</v>
+      </c>
+      <c r="D26">
+        <v>53</v>
+      </c>
+      <c r="E26">
+        <v>52</v>
+      </c>
+      <c r="F26">
+        <v>22</v>
+      </c>
+      <c r="G26">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Files/Laps_Completed.xlsx
+++ b/Data_Files/Laps_Completed.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
